--- a/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
+++ b/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Цена по чертежу'!$A$4:$O$80</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Цена по типу'!$A$4:$O$148</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Оценка по килограмму'!$A$4:$O$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Оценка по килограмму'!$A$4:$O$70</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -635,7 +635,7 @@
         <v>7542925</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.1518108748387328</v>
+        <v>0.1534343630619679</v>
       </c>
     </row>
     <row r="7">
@@ -651,13 +651,13 @@
         <v>1175</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>16948</v>
+        <v>17117</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>29179750</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.5872792550735308</v>
+        <v>0.5935597073492652</v>
       </c>
     </row>
     <row r="8">
@@ -667,19 +667,19 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>7086</v>
+        <v>6914</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>12963653.51903911</v>
+        <v>12437922.72707907</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.2609098700877371</v>
+        <v>0.2530059295887672</v>
       </c>
     </row>
     <row r="9">
@@ -711,16 +711,16 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>27299</v>
+        <v>27295</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>49686328.51903908</v>
+        <v>49160597.72707906</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>1</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>39105750</v>
+        <v>38705750</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>49686329</v>
+        <v>49160598</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>10580579</v>
+        <v>10454848</v>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         <v>401000</v>
       </c>
       <c r="C22" s="23" t="n">
-        <v>49686329</v>
+        <v>49160598</v>
       </c>
       <c r="D22" s="24" t="n">
-        <v>0.008070630532629164</v>
+        <v>0.008156939063804707</v>
       </c>
       <c r="E22" s="25" t="n">
         <v>14.7</v>
@@ -878,10 +878,10 @@
         <v>632000</v>
       </c>
       <c r="C23" s="27" t="n">
-        <v>49686329</v>
+        <v>49160598</v>
       </c>
       <c r="D23" s="28" t="n">
-        <v>0.01271979674967988</v>
+        <v>0.01285582416041041</v>
       </c>
       <c r="E23" s="29" t="n">
         <v>23.2</v>
@@ -897,10 +897,10 @@
         <v>541000</v>
       </c>
       <c r="C24" s="27" t="n">
-        <v>49686329</v>
+        <v>49160598</v>
       </c>
       <c r="D24" s="28" t="n">
-        <v>0.01088830702781142</v>
+        <v>0.01100474821326271</v>
       </c>
       <c r="E24" s="29" t="n">
         <v>19.8</v>
@@ -909,7 +909,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>За базу взят весь перечень — 27.30 т на 49.7 млн. В усиленный контейнер входит 26,35 т из них, на долю логистики эта разница не влияет.</t>
+          <t>За базу взят весь перечень — 27.30 т на 49.2 млн. В усиленный контейнер входит 26,35 т из них, на долю логистики эта разница не влияет.</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="30" t="inlineStr">
         <is>
-          <t>— Вся арматура и фильтры на складе по ценам конкурента — 49.7 млн руб при весе 27.3 т. По нашим учетным ценам те же позиции стоят 39.1 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
+          <t>— Вся арматура и фильтры на складе по ценам конкурента — 49.2 млн руб при весе 27.3 т. По нашим учетным ценам те же позиции стоят 38.7 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 817 руб  а довезти его до Петербурга стоит 14.7 руб. Отсюда и доля.</t>
+          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 802 руб  а довезти его до Петербурга стоит 14.7 руб. Отсюда и доля.</t>
         </is>
       </c>
     </row>
@@ -1205,16 +1205,16 @@
         <v>106</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>192584</v>
+        <v>190991</v>
       </c>
       <c r="F9" s="27" t="n">
         <v>74250</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="H9" s="27" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="I9" s="26" t="n">
         <v>0</v>
@@ -1233,19 +1233,19 @@
         <v>225</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>10392</v>
+        <v>10703</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>16731070</v>
+        <v>16440392</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>12313500</v>
       </c>
       <c r="G10" s="31" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="H10" s="27" t="n">
-        <v>1610</v>
+        <v>1536</v>
       </c>
       <c r="I10" s="26" t="n">
         <v>0</v>
@@ -1258,25 +1258,25 @@
         </is>
       </c>
       <c r="B11" s="26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>2141</v>
+        <v>1828</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>3557106</v>
+        <v>3343718</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>2908000</v>
+        <v>2508000</v>
       </c>
       <c r="G11" s="31" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="H11" s="27" t="n">
-        <v>1661</v>
+        <v>1829</v>
       </c>
       <c r="I11" s="26" t="n">
         <v>0</v>
@@ -1329,14 +1329,14 @@
         <v>363</v>
       </c>
       <c r="E13" s="27" t="n">
-        <v>659147</v>
+        <v>653693</v>
       </c>
       <c r="F13" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="31" t="n"/>
       <c r="H13" s="27" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="I13" s="26" t="n">
         <v>0</v>
@@ -1480,14 +1480,14 @@
         <v>52</v>
       </c>
       <c r="E18" s="27" t="n">
-        <v>94657</v>
+        <v>93874</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="31" t="n"/>
       <c r="H18" s="27" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="I18" s="26" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         <v>110</v>
       </c>
       <c r="E19" s="27" t="n">
-        <v>199125</v>
+        <v>197477</v>
       </c>
       <c r="F19" s="27" t="n">
         <v>415000</v>
@@ -1518,7 +1518,7 @@
         <v>0.48</v>
       </c>
       <c r="H19" s="27" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="I19" s="26" t="n">
         <v>0</v>
@@ -1540,16 +1540,16 @@
         <v>258</v>
       </c>
       <c r="E20" s="27" t="n">
-        <v>468743</v>
+        <v>464865</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>345000</v>
       </c>
       <c r="G20" s="31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H20" s="27" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="I20" s="26" t="n">
         <v>0</v>
@@ -1571,16 +1571,16 @@
         <v>33</v>
       </c>
       <c r="E21" s="27" t="n">
-        <v>59229</v>
+        <v>58739</v>
       </c>
       <c r="F21" s="27" t="n">
         <v>55000</v>
       </c>
       <c r="G21" s="31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="H21" s="27" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="I21" s="26" t="n">
         <v>0</v>
@@ -1633,16 +1633,16 @@
         <v>346</v>
       </c>
       <c r="E23" s="27" t="n">
-        <v>629533</v>
+        <v>624324</v>
       </c>
       <c r="F23" s="27" t="n">
         <v>945000</v>
       </c>
       <c r="G23" s="31" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H23" s="27" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="I23" s="26" t="n">
         <v>0</v>
@@ -1664,14 +1664,14 @@
         <v>4</v>
       </c>
       <c r="E24" s="27" t="n">
-        <v>7267</v>
+        <v>7207</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="31" t="n"/>
       <c r="H24" s="27" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="I24" s="26" t="n">
         <v>0</v>
@@ -1693,16 +1693,16 @@
         <v>170</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>308231</v>
+        <v>305681</v>
       </c>
       <c r="F25" s="27" t="n">
         <v>47000</v>
       </c>
       <c r="G25" s="31" t="n">
-        <v>6.56</v>
+        <v>6.5</v>
       </c>
       <c r="H25" s="27" t="n">
-        <v>1817</v>
+        <v>1802</v>
       </c>
       <c r="I25" s="26" t="n">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="32" t="n">
-        <v>19.2</v>
+        <v>45</v>
       </c>
       <c r="I23" s="34" t="n">
         <v>37500</v>
@@ -8111,7 +8111,7 @@
         <v>2</v>
       </c>
       <c r="H36" s="32" t="n">
-        <v>43.5</v>
+        <v>8</v>
       </c>
       <c r="I36" s="34" t="n">
         <v>87500</v>
@@ -8166,7 +8166,7 @@
         <v>2</v>
       </c>
       <c r="H37" s="32" t="n">
-        <v>43.5</v>
+        <v>8</v>
       </c>
       <c r="I37" s="34" t="n">
         <v>87500</v>
@@ -10361,7 +10361,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="32" t="n">
-        <v>19.2</v>
+        <v>45</v>
       </c>
       <c r="I76" s="34" t="n">
         <v>37500</v>
@@ -13034,7 +13034,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="32" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I123" s="34" t="n">
         <v>9600</v>
@@ -14523,7 +14523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14664,10 +14664,10 @@
         <v>192</v>
       </c>
       <c r="I5" s="34" t="n">
-        <v>309107</v>
+        <v>294934</v>
       </c>
       <c r="J5" s="34" t="n">
-        <v>4018390</v>
+        <v>3834142</v>
       </c>
       <c r="K5" s="34" t="n">
         <v>185000</v>
@@ -14676,7 +14676,7 @@
         <v>2405000</v>
       </c>
       <c r="M5" s="35" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="N5" s="38" t="inlineStr">
         <is>
@@ -14719,10 +14719,10 @@
         <v>192</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>309107</v>
+        <v>294934</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>927321</v>
+        <v>884802</v>
       </c>
       <c r="K6" s="34" t="n">
         <v>250000</v>
@@ -14731,7 +14731,7 @@
         <v>750000</v>
       </c>
       <c r="M6" s="35" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="N6" s="38" t="inlineStr">
         <is>
@@ -14776,10 +14776,10 @@
         <v>40</v>
       </c>
       <c r="I7" s="34" t="n">
-        <v>64397</v>
+        <v>61445</v>
       </c>
       <c r="J7" s="34" t="n">
-        <v>837165</v>
+        <v>798780</v>
       </c>
       <c r="K7" s="34" t="n"/>
       <c r="L7" s="34" t="n"/>
@@ -14937,10 +14937,10 @@
         <v>5.5</v>
       </c>
       <c r="I10" s="34" t="n">
-        <v>9993</v>
+        <v>9910</v>
       </c>
       <c r="J10" s="34" t="n">
-        <v>619540</v>
+        <v>614414</v>
       </c>
       <c r="K10" s="34" t="n">
         <v>15000</v>
@@ -14949,7 +14949,7 @@
         <v>930000</v>
       </c>
       <c r="M10" s="35" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="N10" s="38" t="inlineStr">
         <is>
@@ -14992,10 +14992,10 @@
         <v>64</v>
       </c>
       <c r="I11" s="34" t="n">
-        <v>106313</v>
+        <v>117078</v>
       </c>
       <c r="J11" s="34" t="n">
-        <v>531565</v>
+        <v>585390</v>
       </c>
       <c r="K11" s="34" t="n">
         <v>82500</v>
@@ -15004,7 +15004,7 @@
         <v>412500</v>
       </c>
       <c r="M11" s="35" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="N11" s="38" t="inlineStr">
         <is>
@@ -15051,10 +15051,10 @@
         <v>27</v>
       </c>
       <c r="I12" s="34" t="n">
-        <v>49054</v>
+        <v>48649</v>
       </c>
       <c r="J12" s="34" t="n">
-        <v>441490</v>
+        <v>437838</v>
       </c>
       <c r="K12" s="34" t="n">
         <v>35000</v>
@@ -15063,7 +15063,7 @@
         <v>315000</v>
       </c>
       <c r="M12" s="35" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="N12" s="38" t="inlineStr">
         <is>
@@ -15110,10 +15110,10 @@
         <v>11.2</v>
       </c>
       <c r="I13" s="34" t="n">
-        <v>20349</v>
+        <v>20180</v>
       </c>
       <c r="J13" s="34" t="n">
-        <v>386622</v>
+        <v>383423</v>
       </c>
       <c r="K13" s="34" t="n"/>
       <c r="L13" s="34" t="n"/>
@@ -15218,10 +15218,10 @@
         <v>228</v>
       </c>
       <c r="I15" s="34" t="n">
-        <v>367064</v>
+        <v>350234</v>
       </c>
       <c r="J15" s="34" t="n">
-        <v>367064</v>
+        <v>350234</v>
       </c>
       <c r="K15" s="34" t="n">
         <v>275000</v>
@@ -15230,7 +15230,7 @@
         <v>275000</v>
       </c>
       <c r="M15" s="35" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="N15" s="38" t="inlineStr">
         <is>
@@ -15249,16 +15249,16 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 300</t>
+          <t>Клапан проходной ДУ 125 корпус</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr"/>
       <c r="D16" s="32" t="n">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="E16" s="32" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F16" s="32" t="inlineStr">
@@ -15270,22 +15270,22 @@
         <v>1</v>
       </c>
       <c r="H16" s="32" t="n">
-        <v>172</v>
+        <v>135.3</v>
       </c>
       <c r="I16" s="34" t="n">
-        <v>285716</v>
+        <v>243699</v>
       </c>
       <c r="J16" s="34" t="n">
-        <v>285716</v>
+        <v>243699</v>
       </c>
       <c r="K16" s="34" t="n">
-        <v>400000</v>
+        <v>37000</v>
       </c>
       <c r="L16" s="34" t="n">
-        <v>400000</v>
+        <v>37000</v>
       </c>
       <c r="M16" s="35" t="n">
-        <v>0.71</v>
+        <v>6.59</v>
       </c>
       <c r="N16" s="38" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="O16" s="32" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -15304,16 +15304,16 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>Клапан проходной ДУ 125 корпус</t>
+          <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr"/>
       <c r="D17" s="32" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="E17" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F17" s="32" t="inlineStr">
@@ -15325,22 +15325,22 @@
         <v>1</v>
       </c>
       <c r="H17" s="32" t="n">
-        <v>135.3</v>
+        <v>110</v>
       </c>
       <c r="I17" s="34" t="n">
-        <v>245732</v>
+        <v>213834</v>
       </c>
       <c r="J17" s="34" t="n">
-        <v>245732</v>
+        <v>213834</v>
       </c>
       <c r="K17" s="34" t="n">
-        <v>37000</v>
+        <v>150000</v>
       </c>
       <c r="L17" s="34" t="n">
-        <v>37000</v>
+        <v>150000</v>
       </c>
       <c r="M17" s="35" t="n">
-        <v>6.64</v>
+        <v>1.43</v>
       </c>
       <c r="N17" s="38" t="inlineStr">
         <is>
@@ -15359,16 +15359,16 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200</t>
+          <t>Фильтр заборной воды ДУ 80</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr"/>
       <c r="D18" s="32" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="E18" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="F18" s="32" t="inlineStr">
@@ -15377,26 +15377,20 @@
         </is>
       </c>
       <c r="G18" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H18" s="32" t="n">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>213834</v>
+        <v>40246</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>213834</v>
-      </c>
-      <c r="K18" s="34" t="n">
-        <v>150000</v>
-      </c>
-      <c r="L18" s="34" t="n">
-        <v>150000</v>
-      </c>
-      <c r="M18" s="35" t="n">
-        <v>1.43</v>
-      </c>
+        <v>201228</v>
+      </c>
+      <c r="K18" s="34" t="n"/>
+      <c r="L18" s="34" t="n"/>
+      <c r="M18" s="35" t="n"/>
       <c r="N18" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15404,7 +15398,7 @@
       </c>
       <c r="O18" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -15442,10 +15436,10 @@
         <v>18.2</v>
       </c>
       <c r="I19" s="34" t="n">
-        <v>33066</v>
+        <v>32793</v>
       </c>
       <c r="J19" s="34" t="n">
-        <v>198398</v>
+        <v>196757</v>
       </c>
       <c r="K19" s="34" t="n"/>
       <c r="L19" s="34" t="n"/>
@@ -15467,16 +15461,20 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 80</t>
-        </is>
-      </c>
-      <c r="C20" s="32" t="inlineStr"/>
+          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>529-03.074</t>
+        </is>
+      </c>
       <c r="D20" s="32" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F20" s="32" t="inlineStr">
@@ -15485,20 +15483,26 @@
         </is>
       </c>
       <c r="G20" s="34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="32" t="n">
         <v>22</v>
       </c>
       <c r="I20" s="34" t="n">
-        <v>36545</v>
+        <v>50691</v>
       </c>
       <c r="J20" s="34" t="n">
-        <v>182725</v>
-      </c>
-      <c r="K20" s="34" t="n"/>
-      <c r="L20" s="34" t="n"/>
-      <c r="M20" s="35" t="n"/>
+        <v>152074</v>
+      </c>
+      <c r="K20" s="34" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L20" s="34" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M20" s="35" t="n">
+        <v>1.27</v>
+      </c>
       <c r="N20" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15516,20 +15520,20 @@
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
+          <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
-          <t>529-03.074</t>
+          <t>587-03.082</t>
         </is>
       </c>
       <c r="D21" s="32" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Пусковые клапаны</t>
         </is>
       </c>
       <c r="F21" s="32" t="inlineStr">
@@ -15538,25 +15542,25 @@
         </is>
       </c>
       <c r="G21" s="34" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H21" s="32" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I21" s="34" t="n">
-        <v>50691</v>
+        <v>15856</v>
       </c>
       <c r="J21" s="34" t="n">
-        <v>152074</v>
+        <v>126847</v>
       </c>
       <c r="K21" s="34" t="n">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="L21" s="34" t="n">
-        <v>120000</v>
+        <v>240000</v>
       </c>
       <c r="M21" s="35" t="n">
-        <v>1.27</v>
+        <v>0.53</v>
       </c>
       <c r="N21" s="38" t="inlineStr">
         <is>
@@ -15575,20 +15579,16 @@
       </c>
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду32Ру125</t>
-        </is>
-      </c>
-      <c r="C22" s="32" t="inlineStr">
-        <is>
-          <t>587-03.082</t>
-        </is>
-      </c>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr"/>
       <c r="D22" s="32" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E22" s="32" t="inlineStr">
         <is>
-          <t>Пусковые клапаны</t>
+          <t>Фланцевая, угол или проход не указан</t>
         </is>
       </c>
       <c r="F22" s="32" t="inlineStr">
@@ -15597,25 +15597,25 @@
         </is>
       </c>
       <c r="G22" s="34" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H22" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I22" s="34" t="n">
-        <v>15988</v>
+        <v>16517</v>
       </c>
       <c r="J22" s="34" t="n">
-        <v>127905</v>
+        <v>99099</v>
       </c>
       <c r="K22" s="34" t="n">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="L22" s="34" t="n">
-        <v>240000</v>
+        <v>45000</v>
       </c>
       <c r="M22" s="35" t="n">
-        <v>0.53</v>
+        <v>2.2</v>
       </c>
       <c r="N22" s="38" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="O22" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -15634,16 +15634,20 @@
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
-        </is>
-      </c>
-      <c r="C23" s="32" t="inlineStr"/>
+          <t>Клапан фланцевый угловой Ду25</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>521-3М539</t>
+        </is>
+      </c>
       <c r="D23" s="32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая, угол или проход не указан</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
@@ -15652,25 +15656,25 @@
         </is>
       </c>
       <c r="G23" s="34" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H23" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="I23" s="34" t="n">
-        <v>16654</v>
+        <v>7614</v>
       </c>
       <c r="J23" s="34" t="n">
-        <v>99926</v>
+        <v>98980</v>
       </c>
       <c r="K23" s="34" t="n">
-        <v>7500</v>
+        <v>20000</v>
       </c>
       <c r="L23" s="34" t="n">
-        <v>45000</v>
+        <v>260000</v>
       </c>
       <c r="M23" s="35" t="n">
-        <v>2.22</v>
+        <v>0.38</v>
       </c>
       <c r="N23" s="38" t="inlineStr">
         <is>
@@ -15679,7 +15683,7 @@
       </c>
       <c r="O23" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -15689,20 +15693,16 @@
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
-        </is>
-      </c>
-      <c r="C24" s="32" t="inlineStr">
-        <is>
-          <t>521-3М539</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr"/>
       <c r="D24" s="32" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F24" s="32" t="inlineStr">
@@ -15711,25 +15711,25 @@
         </is>
       </c>
       <c r="G24" s="34" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H24" s="32" t="n">
-        <v>5.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>7614</v>
+        <v>13423</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>98980</v>
+        <v>93962</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="L24" s="34" t="n">
-        <v>260000</v>
+        <v>189000</v>
       </c>
       <c r="M24" s="35" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="N24" s="38" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
       </c>
       <c r="O24" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -15748,16 +15748,18 @@
       </c>
       <c r="B25" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
-        </is>
-      </c>
-      <c r="C25" s="32" t="inlineStr"/>
-      <c r="D25" s="32" t="n">
-        <v>70</v>
-      </c>
+          <t>Клапан для манометра штуцерный сальниковый</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>521-34.3404-03</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="n"/>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
@@ -15766,25 +15768,25 @@
         </is>
       </c>
       <c r="G25" s="34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H25" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="I25" s="34" t="n">
-        <v>14068</v>
+        <v>8581</v>
       </c>
       <c r="J25" s="34" t="n">
-        <v>98478</v>
+        <v>85814</v>
       </c>
       <c r="K25" s="34" t="n">
-        <v>27000</v>
+        <v>6000</v>
       </c>
       <c r="L25" s="34" t="n">
-        <v>189000</v>
+        <v>60000</v>
       </c>
       <c r="M25" s="35" t="n">
-        <v>0.52</v>
+        <v>1.43</v>
       </c>
       <c r="N25" s="38" t="inlineStr">
         <is>
@@ -15793,7 +15795,7 @@
       </c>
       <c r="O25" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -15803,18 +15805,20 @@
       </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>Клапан для манометра штуцерный сальниковый</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="C26" s="32" t="inlineStr">
         <is>
-          <t>521-34.3404-03</t>
-        </is>
-      </c>
-      <c r="D26" s="32" t="n"/>
+          <t>527-03.055</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="n">
+        <v>80</v>
+      </c>
       <c r="E26" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="F26" s="32" t="inlineStr">
@@ -15823,25 +15827,25 @@
         </is>
       </c>
       <c r="G26" s="34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H26" s="32" t="n">
-        <v>1.3</v>
+        <v>19</v>
       </c>
       <c r="I26" s="34" t="n">
-        <v>8581</v>
+        <v>40587</v>
       </c>
       <c r="J26" s="34" t="n">
-        <v>85814</v>
+        <v>81174</v>
       </c>
       <c r="K26" s="34" t="n">
-        <v>6000</v>
+        <v>30000</v>
       </c>
       <c r="L26" s="34" t="n">
         <v>60000</v>
       </c>
       <c r="M26" s="35" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="N26" s="38" t="inlineStr">
         <is>
@@ -15850,7 +15854,7 @@
       </c>
       <c r="O26" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -15860,47 +15864,41 @@
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="n">
-        <v>80</v>
-      </c>
+          <t>Клапан проходной фланцевый сталь</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr"/>
+      <c r="D27" s="32" t="n"/>
       <c r="E27" s="32" t="inlineStr">
         <is>
-          <t>Кингстоны</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G27" s="34" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I27" s="34" t="n">
-        <v>40587</v>
+        <v>38879</v>
       </c>
       <c r="J27" s="34" t="n">
-        <v>81174</v>
+        <v>77758</v>
       </c>
       <c r="K27" s="34" t="n">
-        <v>30000</v>
+        <v>18000</v>
       </c>
       <c r="L27" s="34" t="n">
-        <v>60000</v>
+        <v>36000</v>
       </c>
       <c r="M27" s="35" t="n">
-        <v>1.35</v>
+        <v>2.16</v>
       </c>
       <c r="N27" s="38" t="inlineStr">
         <is>
@@ -15909,7 +15907,7 @@
       </c>
       <c r="O27" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -15919,42 +15917,42 @@
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый сталь</t>
-        </is>
-      </c>
-      <c r="C28" s="32" t="inlineStr"/>
-      <c r="D28" s="32" t="n"/>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>529-03.003</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="n">
+        <v>100</v>
+      </c>
       <c r="E28" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G28" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="32" t="n">
-        <v>20</v>
+        <v>33.7</v>
       </c>
       <c r="I28" s="34" t="n">
-        <v>38879</v>
+        <v>77650</v>
       </c>
       <c r="J28" s="34" t="n">
-        <v>77758</v>
-      </c>
-      <c r="K28" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L28" s="34" t="n">
-        <v>36000</v>
-      </c>
-      <c r="M28" s="35" t="n">
-        <v>2.16</v>
-      </c>
+        <v>77650</v>
+      </c>
+      <c r="K28" s="34" t="n"/>
+      <c r="L28" s="34" t="n"/>
+      <c r="M28" s="35" t="n"/>
       <c r="N28" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15962,7 +15960,7 @@
       </c>
       <c r="O28" s="32" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -15972,20 +15970,20 @@
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
+          <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
         <is>
-          <t>529-03.003</t>
+          <t>587-03.080</t>
         </is>
       </c>
       <c r="D29" s="32" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Пусковые клапаны</t>
         </is>
       </c>
       <c r="F29" s="32" t="inlineStr">
@@ -15994,20 +15992,26 @@
         </is>
       </c>
       <c r="G29" s="34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H29" s="32" t="n">
-        <v>33.7</v>
+        <v>5.6</v>
       </c>
       <c r="I29" s="34" t="n">
-        <v>77650</v>
+        <v>10090</v>
       </c>
       <c r="J29" s="34" t="n">
-        <v>77650</v>
-      </c>
-      <c r="K29" s="34" t="n"/>
-      <c r="L29" s="34" t="n"/>
-      <c r="M29" s="35" t="n"/>
+        <v>70631</v>
+      </c>
+      <c r="K29" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L29" s="34" t="n">
+        <v>175000</v>
+      </c>
+      <c r="M29" s="35" t="n">
+        <v>0.4</v>
+      </c>
       <c r="N29" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16015,7 +16019,7 @@
       </c>
       <c r="O29" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16025,12 +16029,12 @@
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду20Ру125</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
         <is>
-          <t>587-03.080</t>
+          <t>554-03.905-06</t>
         </is>
       </c>
       <c r="D30" s="32" t="n">
@@ -16038,7 +16042,7 @@
       </c>
       <c r="E30" s="32" t="inlineStr">
         <is>
-          <t>Пусковые клапаны</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="F30" s="32" t="inlineStr">
@@ -16047,26 +16051,20 @@
         </is>
       </c>
       <c r="G30" s="34" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H30" s="32" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="I30" s="34" t="n">
-        <v>10174</v>
+        <v>2703</v>
       </c>
       <c r="J30" s="34" t="n">
-        <v>71220</v>
-      </c>
-      <c r="K30" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="L30" s="34" t="n">
-        <v>175000</v>
-      </c>
-      <c r="M30" s="35" t="n">
-        <v>0.41</v>
-      </c>
+        <v>70270</v>
+      </c>
+      <c r="K30" s="34" t="n"/>
+      <c r="L30" s="34" t="n"/>
+      <c r="M30" s="35" t="n"/>
       <c r="N30" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16074,7 +16072,7 @@
       </c>
       <c r="O30" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -16084,20 +16082,14 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>554-03.905-06</t>
-        </is>
-      </c>
-      <c r="D31" s="32" t="n">
-        <v>20</v>
-      </c>
+          <t>Электропривод к задвижке</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr"/>
+      <c r="D31" s="32" t="n"/>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F31" s="32" t="inlineStr">
@@ -16106,20 +16098,26 @@
         </is>
       </c>
       <c r="G31" s="34" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H31" s="32" t="n">
-        <v>1.5</v>
+        <v>40</v>
       </c>
       <c r="I31" s="34" t="n">
-        <v>2725</v>
+        <v>61445</v>
       </c>
       <c r="J31" s="34" t="n">
-        <v>70856</v>
-      </c>
-      <c r="K31" s="34" t="n"/>
-      <c r="L31" s="34" t="n"/>
-      <c r="M31" s="35" t="n"/>
+        <v>61445</v>
+      </c>
+      <c r="K31" s="34" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L31" s="34" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M31" s="35" t="n">
+        <v>1.23</v>
+      </c>
       <c r="N31" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16127,7 +16125,7 @@
       </c>
       <c r="O31" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -16137,14 +16135,16 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
         </is>
       </c>
       <c r="C32" s="32" t="inlineStr"/>
-      <c r="D32" s="32" t="n"/>
+      <c r="D32" s="32" t="n">
+        <v>65</v>
+      </c>
       <c r="E32" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Фланцевая, угол или проход не указан</t>
         </is>
       </c>
       <c r="F32" s="32" t="inlineStr">
@@ -16153,25 +16153,25 @@
         </is>
       </c>
       <c r="G32" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="32" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I32" s="34" t="n">
-        <v>64397</v>
+        <v>30631</v>
       </c>
       <c r="J32" s="34" t="n">
-        <v>64397</v>
+        <v>61261</v>
       </c>
       <c r="K32" s="34" t="n">
-        <v>50000</v>
+        <v>9750</v>
       </c>
       <c r="L32" s="34" t="n">
-        <v>50000</v>
+        <v>19500</v>
       </c>
       <c r="M32" s="35" t="n">
-        <v>1.29</v>
+        <v>3.14</v>
       </c>
       <c r="N32" s="38" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
       </c>
       <c r="O32" s="32" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -16190,16 +16190,20 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr"/>
+          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>529-35-1405-01</t>
+        </is>
+      </c>
       <c r="D33" s="32" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая, угол или проход не указан</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
@@ -16208,25 +16212,25 @@
         </is>
       </c>
       <c r="G33" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="32" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I33" s="34" t="n">
-        <v>30886</v>
+        <v>59908</v>
       </c>
       <c r="J33" s="34" t="n">
-        <v>61772</v>
+        <v>59908</v>
       </c>
       <c r="K33" s="34" t="n">
-        <v>9750</v>
+        <v>40000</v>
       </c>
       <c r="L33" s="34" t="n">
-        <v>19500</v>
+        <v>40000</v>
       </c>
       <c r="M33" s="35" t="n">
-        <v>3.17</v>
+        <v>1.5</v>
       </c>
       <c r="N33" s="38" t="inlineStr">
         <is>
@@ -16235,7 +16239,7 @@
       </c>
       <c r="O33" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16245,47 +16249,47 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
+          <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
         <is>
-          <t>529-35-1405-01</t>
+          <t>581-03.034</t>
         </is>
       </c>
       <c r="D34" s="32" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E34" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Паровые клапаны</t>
         </is>
       </c>
       <c r="F34" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G34" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="32" t="n">
-        <v>26</v>
+        <v>32.6</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>59908</v>
+        <v>58739</v>
       </c>
       <c r="J34" s="34" t="n">
-        <v>59908</v>
+        <v>58739</v>
       </c>
       <c r="K34" s="34" t="n">
-        <v>40000</v>
+        <v>55000</v>
       </c>
       <c r="L34" s="34" t="n">
-        <v>40000</v>
+        <v>55000</v>
       </c>
       <c r="M34" s="35" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="N34" s="38" t="inlineStr">
         <is>
@@ -16304,47 +16308,41 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
-        </is>
-      </c>
-      <c r="C35" s="32" t="inlineStr">
-        <is>
-          <t>581-03.034</t>
-        </is>
-      </c>
-      <c r="D35" s="32" t="n">
-        <v>65</v>
-      </c>
+          <t>Коробка 2-х клапанная корпус</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr"/>
+      <c r="D35" s="32" t="n"/>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Паровые клапаны</t>
+          <t>Коробки клапанные</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G35" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="32" t="n">
-        <v>32.6</v>
+        <v>40</v>
       </c>
       <c r="I35" s="34" t="n">
-        <v>59229</v>
+        <v>57434</v>
       </c>
       <c r="J35" s="34" t="n">
-        <v>59229</v>
+        <v>57434</v>
       </c>
       <c r="K35" s="34" t="n">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="L35" s="34" t="n">
-        <v>55000</v>
+        <v>20000</v>
       </c>
       <c r="M35" s="35" t="n">
-        <v>1.08</v>
+        <v>2.87</v>
       </c>
       <c r="N35" s="38" t="inlineStr">
         <is>
@@ -16353,7 +16351,7 @@
       </c>
       <c r="O35" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -16363,14 +16361,20 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
-        </is>
-      </c>
-      <c r="C36" s="32" t="inlineStr"/>
-      <c r="D36" s="32" t="n"/>
+          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>529-35.1406-01</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="n">
+        <v>100</v>
+      </c>
       <c r="E36" s="32" t="inlineStr">
         <is>
-          <t>Коробки клапанные</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F36" s="32" t="inlineStr">
@@ -16382,22 +16386,22 @@
         <v>1</v>
       </c>
       <c r="H36" s="32" t="n">
-        <v>40</v>
+        <v>23.6</v>
       </c>
       <c r="I36" s="34" t="n">
-        <v>57434</v>
+        <v>54378</v>
       </c>
       <c r="J36" s="34" t="n">
-        <v>57434</v>
+        <v>54378</v>
       </c>
       <c r="K36" s="34" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="L36" s="34" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="M36" s="35" t="n">
-        <v>2.87</v>
+        <v>1.36</v>
       </c>
       <c r="N36" s="38" t="inlineStr">
         <is>
@@ -16406,7 +16410,7 @@
       </c>
       <c r="O36" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16416,20 +16420,20 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="C37" s="32" t="inlineStr">
         <is>
-          <t>529-35.1406-01</t>
+          <t>527-03.055</t>
         </is>
       </c>
       <c r="D37" s="32" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E37" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="F37" s="32" t="inlineStr">
@@ -16441,23 +16445,17 @@
         <v>1</v>
       </c>
       <c r="H37" s="32" t="n">
-        <v>23.6</v>
+        <v>19</v>
       </c>
       <c r="I37" s="34" t="n">
-        <v>54378</v>
+        <v>40587</v>
       </c>
       <c r="J37" s="34" t="n">
-        <v>54378</v>
-      </c>
-      <c r="K37" s="34" t="n">
-        <v>40000</v>
-      </c>
-      <c r="L37" s="34" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M37" s="35" t="n">
-        <v>1.36</v>
-      </c>
+        <v>40587</v>
+      </c>
+      <c r="K37" s="34" t="n"/>
+      <c r="L37" s="34" t="n"/>
+      <c r="M37" s="35" t="n"/>
       <c r="N37" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16475,20 +16473,14 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="C38" s="32" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
-      <c r="D38" s="32" t="n">
-        <v>80</v>
-      </c>
+          <t>Клапан электромагнитный б/у</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr"/>
+      <c r="D38" s="32" t="n"/>
       <c r="E38" s="32" t="inlineStr">
         <is>
-          <t>Кингстоны</t>
+          <t>Электромагнитные клапаны</t>
         </is>
       </c>
       <c r="F38" s="32" t="inlineStr">
@@ -16497,16 +16489,16 @@
         </is>
       </c>
       <c r="G38" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38" s="32" t="n">
-        <v>19</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="34" t="n">
-        <v>40587</v>
+        <v>12724</v>
       </c>
       <c r="J38" s="34" t="n">
-        <v>40587</v>
+        <v>38172</v>
       </c>
       <c r="K38" s="34" t="n"/>
       <c r="L38" s="34" t="n"/>
@@ -16518,7 +16510,7 @@
       </c>
       <c r="O38" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -16528,14 +16520,18 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>Клапан электромагнитный б/у</t>
-        </is>
-      </c>
-      <c r="C39" s="32" t="inlineStr"/>
+          <t>Клапан штуцерный угловой Рр150/10</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>521-ц22п</t>
+        </is>
+      </c>
       <c r="D39" s="32" t="n"/>
       <c r="E39" s="32" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F39" s="32" t="inlineStr">
@@ -16544,20 +16540,26 @@
         </is>
       </c>
       <c r="G39" s="34" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H39" s="32" t="n">
-        <v>12.3</v>
+        <v>1.3</v>
       </c>
       <c r="I39" s="34" t="n">
-        <v>12724</v>
+        <v>3954</v>
       </c>
       <c r="J39" s="34" t="n">
-        <v>38172</v>
-      </c>
-      <c r="K39" s="34" t="n"/>
-      <c r="L39" s="34" t="n"/>
-      <c r="M39" s="35" t="n"/>
+        <v>31636</v>
+      </c>
+      <c r="K39" s="34" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L39" s="34" t="n">
+        <v>32000</v>
+      </c>
+      <c r="M39" s="35" t="n">
+        <v>0.99</v>
+      </c>
       <c r="N39" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16565,7 +16567,7 @@
       </c>
       <c r="O39" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -16575,18 +16577,16 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
-        </is>
-      </c>
-      <c r="C40" s="32" t="inlineStr">
-        <is>
-          <t>521-ц22п</t>
-        </is>
-      </c>
-      <c r="D40" s="32" t="n"/>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="inlineStr"/>
+      <c r="D40" s="32" t="n">
+        <v>65</v>
+      </c>
       <c r="E40" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Фланцевая, угол или проход не указан</t>
         </is>
       </c>
       <c r="F40" s="32" t="inlineStr">
@@ -16595,25 +16595,25 @@
         </is>
       </c>
       <c r="G40" s="34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H40" s="32" t="n">
-        <v>1.3</v>
+        <v>17</v>
       </c>
       <c r="I40" s="34" t="n">
-        <v>3954</v>
+        <v>30631</v>
       </c>
       <c r="J40" s="34" t="n">
-        <v>31636</v>
+        <v>30631</v>
       </c>
       <c r="K40" s="34" t="n">
-        <v>4000</v>
+        <v>9750</v>
       </c>
       <c r="L40" s="34" t="n">
-        <v>32000</v>
+        <v>9750</v>
       </c>
       <c r="M40" s="35" t="n">
-        <v>0.99</v>
+        <v>3.14</v>
       </c>
       <c r="N40" s="38" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
       </c>
       <c r="O40" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -16632,16 +16632,14 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+          <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
       <c r="C41" s="32" t="inlineStr"/>
-      <c r="D41" s="32" t="n">
-        <v>65</v>
-      </c>
+      <c r="D41" s="32" t="n"/>
       <c r="E41" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая, угол или проход не указан</t>
+          <t>Электромагнитные клапаны</t>
         </is>
       </c>
       <c r="F41" s="32" t="inlineStr">
@@ -16650,26 +16648,20 @@
         </is>
       </c>
       <c r="G41" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="32" t="n">
-        <v>17</v>
+        <v>12.3</v>
       </c>
       <c r="I41" s="34" t="n">
-        <v>30886</v>
+        <v>12724</v>
       </c>
       <c r="J41" s="34" t="n">
-        <v>30886</v>
-      </c>
-      <c r="K41" s="34" t="n">
-        <v>9750</v>
-      </c>
-      <c r="L41" s="34" t="n">
-        <v>9750</v>
-      </c>
-      <c r="M41" s="35" t="n">
-        <v>3.17</v>
-      </c>
+        <v>25448</v>
+      </c>
+      <c r="K41" s="34" t="n"/>
+      <c r="L41" s="34" t="n"/>
+      <c r="M41" s="35" t="n"/>
       <c r="N41" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16677,7 +16669,7 @@
       </c>
       <c r="O41" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -16687,14 +16679,18 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
-        </is>
-      </c>
-      <c r="C42" s="32" t="inlineStr"/>
+          <t>Клапан штуцерный угловой Рр150/10</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>521-ц22п</t>
+        </is>
+      </c>
       <c r="D42" s="32" t="n"/>
       <c r="E42" s="32" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F42" s="32" t="inlineStr">
@@ -16703,20 +16699,26 @@
         </is>
       </c>
       <c r="G42" s="34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H42" s="32" t="n">
-        <v>12.3</v>
+        <v>1</v>
       </c>
       <c r="I42" s="34" t="n">
-        <v>12724</v>
+        <v>3126</v>
       </c>
       <c r="J42" s="34" t="n">
-        <v>25448</v>
-      </c>
-      <c r="K42" s="34" t="n"/>
-      <c r="L42" s="34" t="n"/>
-      <c r="M42" s="35" t="n"/>
+        <v>25008</v>
+      </c>
+      <c r="K42" s="34" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L42" s="34" t="n">
+        <v>24000</v>
+      </c>
+      <c r="M42" s="35" t="n">
+        <v>1.04</v>
+      </c>
       <c r="N42" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16724,7 +16726,7 @@
       </c>
       <c r="O42" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16734,18 +16736,20 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
         <is>
-          <t>521-ц22п</t>
-        </is>
-      </c>
-      <c r="D43" s="32" t="n"/>
+          <t>524-35.2423-01</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="n">
+        <v>6</v>
+      </c>
       <c r="E43" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F43" s="32" t="inlineStr">
@@ -16754,25 +16758,25 @@
         </is>
       </c>
       <c r="G43" s="34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H43" s="32" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="I43" s="34" t="n">
-        <v>3126</v>
+        <v>23743</v>
       </c>
       <c r="J43" s="34" t="n">
-        <v>25008</v>
+        <v>23743</v>
       </c>
       <c r="K43" s="34" t="n">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="L43" s="34" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="M43" s="35" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="N43" s="38" t="inlineStr">
         <is>
@@ -16791,20 +16795,20 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
         <is>
-          <t>524-35.2423-01</t>
+          <t>(541-03.232)</t>
         </is>
       </c>
       <c r="D44" s="32" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E44" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F44" s="32" t="inlineStr">
@@ -16813,26 +16817,20 @@
         </is>
       </c>
       <c r="G44" s="34" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H44" s="32" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="I44" s="34" t="n">
-        <v>23743</v>
+        <v>2883</v>
       </c>
       <c r="J44" s="34" t="n">
-        <v>23743</v>
-      </c>
-      <c r="K44" s="34" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L44" s="34" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M44" s="35" t="n">
-        <v>1.19</v>
-      </c>
+        <v>23063</v>
+      </c>
+      <c r="K44" s="34" t="n"/>
+      <c r="L44" s="34" t="n"/>
+      <c r="M44" s="35" t="n"/>
       <c r="N44" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16840,7 +16838,7 @@
       </c>
       <c r="O44" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -16850,16 +16848,16 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
+          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
         <is>
-          <t>(541-03.232)</t>
+          <t>(541-03.316-04)</t>
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E45" s="32" t="inlineStr">
         <is>
@@ -16872,16 +16870,16 @@
         </is>
       </c>
       <c r="G45" s="34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H45" s="32" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="I45" s="34" t="n">
-        <v>2907</v>
+        <v>8468</v>
       </c>
       <c r="J45" s="34" t="n">
-        <v>23255</v>
+        <v>16937</v>
       </c>
       <c r="K45" s="34" t="n"/>
       <c r="L45" s="34" t="n"/>
@@ -16903,20 +16901,20 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
+          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
         <is>
-          <t>(541-03.316-04)</t>
+          <t>521-03.445-04</t>
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E46" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F46" s="32" t="inlineStr">
@@ -16925,20 +16923,26 @@
         </is>
       </c>
       <c r="G46" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H46" s="32" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="I46" s="34" t="n">
-        <v>8539</v>
+        <v>4064</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>17078</v>
-      </c>
-      <c r="K46" s="34" t="n"/>
-      <c r="L46" s="34" t="n"/>
-      <c r="M46" s="35" t="n"/>
+        <v>16255</v>
+      </c>
+      <c r="K46" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L46" s="34" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M46" s="35" t="n">
+        <v>0.27</v>
+      </c>
       <c r="N46" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16946,7 +16950,7 @@
       </c>
       <c r="O46" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16956,20 +16960,20 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
+          <t>Грибки АМГ Ду 150 (верхние)</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
         <is>
-          <t>521-03.445-04</t>
+          <t>(541-03.315-02)</t>
         </is>
       </c>
       <c r="D47" s="32" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="E47" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F47" s="32" t="inlineStr">
@@ -16978,26 +16982,20 @@
         </is>
       </c>
       <c r="G47" s="34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47" s="32" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="I47" s="34" t="n">
-        <v>4064</v>
+        <v>5225</v>
       </c>
       <c r="J47" s="34" t="n">
-        <v>16255</v>
-      </c>
-      <c r="K47" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="L47" s="34" t="n">
-        <v>60000</v>
-      </c>
-      <c r="M47" s="35" t="n">
-        <v>0.27</v>
-      </c>
+        <v>15676</v>
+      </c>
+      <c r="K47" s="34" t="n"/>
+      <c r="L47" s="34" t="n"/>
+      <c r="M47" s="35" t="n"/>
       <c r="N47" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17005,7 +17003,7 @@
       </c>
       <c r="O47" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17015,42 +17013,48 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 150 (верхние)</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
         <is>
-          <t>(541-03.315-02)</t>
+          <t>522-35.445-19</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="E48" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F48" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G48" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="32" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="I48" s="34" t="n">
-        <v>5269</v>
+        <v>7767</v>
       </c>
       <c r="J48" s="34" t="n">
-        <v>15806</v>
-      </c>
-      <c r="K48" s="34" t="n"/>
-      <c r="L48" s="34" t="n"/>
-      <c r="M48" s="35" t="n"/>
+        <v>15534</v>
+      </c>
+      <c r="K48" s="34" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L48" s="34" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M48" s="35" t="n">
+        <v>0.43</v>
+      </c>
       <c r="N48" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17058,7 +17062,7 @@
       </c>
       <c r="O48" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -17068,20 +17072,20 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
         <is>
-          <t>522-35.445-19</t>
+          <t>525-35.2634</t>
         </is>
       </c>
       <c r="D49" s="32" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E49" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Редукционные клапаны</t>
         </is>
       </c>
       <c r="F49" s="32" t="inlineStr">
@@ -17090,25 +17094,25 @@
         </is>
       </c>
       <c r="G49" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" s="32" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="I49" s="34" t="n">
-        <v>7767</v>
+        <v>13514</v>
       </c>
       <c r="J49" s="34" t="n">
-        <v>15534</v>
+        <v>13514</v>
       </c>
       <c r="K49" s="34" t="n">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="L49" s="34" t="n">
-        <v>36000</v>
+        <v>15000</v>
       </c>
       <c r="M49" s="35" t="n">
-        <v>0.43</v>
+        <v>0.9</v>
       </c>
       <c r="N49" s="38" t="inlineStr">
         <is>
@@ -17117,7 +17121,7 @@
       </c>
       <c r="O49" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -17132,7 +17136,7 @@
       </c>
       <c r="C50" s="32" t="inlineStr">
         <is>
-          <t>525-35.2634</t>
+          <t>525-35.2634-04</t>
         </is>
       </c>
       <c r="D50" s="32" t="n">
@@ -17155,10 +17159,10 @@
         <v>7.5</v>
       </c>
       <c r="I50" s="34" t="n">
-        <v>13626</v>
+        <v>13514</v>
       </c>
       <c r="J50" s="34" t="n">
-        <v>13626</v>
+        <v>13514</v>
       </c>
       <c r="K50" s="34" t="n">
         <v>15000</v>
@@ -17167,7 +17171,7 @@
         <v>15000</v>
       </c>
       <c r="M50" s="35" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="N50" s="38" t="inlineStr">
         <is>
@@ -17186,48 +17190,42 @@
       </c>
       <c r="B51" s="33" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Клапан Ду20/10</t>
         </is>
       </c>
       <c r="C51" s="32" t="inlineStr">
         <is>
-          <t>525-35.2634-04</t>
+          <t>581-С6.73</t>
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E51" s="32" t="inlineStr">
         <is>
-          <t>Редукционные клапаны</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F51" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G51" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="32" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="I51" s="34" t="n">
-        <v>13626</v>
+        <v>4324</v>
       </c>
       <c r="J51" s="34" t="n">
-        <v>13626</v>
-      </c>
-      <c r="K51" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="L51" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M51" s="35" t="n">
-        <v>0.91</v>
-      </c>
+        <v>12973</v>
+      </c>
+      <c r="K51" s="34" t="n"/>
+      <c r="L51" s="34" t="n"/>
+      <c r="M51" s="35" t="n"/>
       <c r="N51" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17235,7 +17233,7 @@
       </c>
       <c r="O51" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17245,20 +17243,18 @@
       </c>
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>Клапан Ду20/10</t>
+          <t>Клапан с электромагнитным ручным управлением</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
         <is>
-          <t>581-С6.73</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="n">
-        <v>20</v>
-      </c>
+          <t>587-182.126</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="n"/>
       <c r="E52" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Электромагнитные клапаны</t>
         </is>
       </c>
       <c r="F52" s="32" t="inlineStr">
@@ -17267,16 +17263,16 @@
         </is>
       </c>
       <c r="G52" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52" s="32" t="n">
-        <v>2.4</v>
+        <v>12.3</v>
       </c>
       <c r="I52" s="34" t="n">
-        <v>4360</v>
+        <v>12724</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>13081</v>
+        <v>12724</v>
       </c>
       <c r="K52" s="34" t="n"/>
       <c r="L52" s="34" t="n"/>
@@ -17298,18 +17294,18 @@
       </c>
       <c r="B53" s="33" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
         <is>
-          <t>587-182.126</t>
+          <t>2619802505</t>
         </is>
       </c>
       <c r="D53" s="32" t="n"/>
       <c r="E53" s="32" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F53" s="32" t="inlineStr">
@@ -17321,13 +17317,13 @@
         <v>1</v>
       </c>
       <c r="H53" s="32" t="n">
-        <v>12.3</v>
+        <v>6.8</v>
       </c>
       <c r="I53" s="34" t="n">
-        <v>12724</v>
+        <v>12252</v>
       </c>
       <c r="J53" s="34" t="n">
-        <v>12724</v>
+        <v>12252</v>
       </c>
       <c r="K53" s="34" t="n"/>
       <c r="L53" s="34" t="n"/>
@@ -17349,14 +17345,10 @@
       </c>
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
-        </is>
-      </c>
-      <c r="C54" s="32" t="inlineStr">
-        <is>
-          <t>2619802505</t>
-        </is>
-      </c>
+          <t>Судовая запорная арматура</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr"/>
       <c r="D54" s="32" t="n"/>
       <c r="E54" s="32" t="inlineStr">
         <is>
@@ -17375,14 +17367,20 @@
         <v>6.8</v>
       </c>
       <c r="I54" s="34" t="n">
-        <v>12354</v>
+        <v>12252</v>
       </c>
       <c r="J54" s="34" t="n">
-        <v>12354</v>
-      </c>
-      <c r="K54" s="34" t="n"/>
-      <c r="L54" s="34" t="n"/>
-      <c r="M54" s="35" t="n"/>
+        <v>12252</v>
+      </c>
+      <c r="K54" s="34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L54" s="34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M54" s="35" t="n">
+        <v>1.23</v>
+      </c>
       <c r="N54" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17390,7 +17388,7 @@
       </c>
       <c r="O54" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -17400,10 +17398,14 @@
       </c>
       <c r="B55" s="33" t="inlineStr">
         <is>
-          <t>Судовая запорная арматура</t>
-        </is>
-      </c>
-      <c r="C55" s="32" t="inlineStr"/>
+          <t>Клапан</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>587-182.126</t>
+        </is>
+      </c>
       <c r="D55" s="32" t="n"/>
       <c r="E55" s="32" t="inlineStr">
         <is>
@@ -17422,20 +17424,14 @@
         <v>6.8</v>
       </c>
       <c r="I55" s="34" t="n">
-        <v>12354</v>
+        <v>12252</v>
       </c>
       <c r="J55" s="34" t="n">
-        <v>12354</v>
-      </c>
-      <c r="K55" s="34" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L55" s="34" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M55" s="35" t="n">
-        <v>1.24</v>
-      </c>
+        <v>12252</v>
+      </c>
+      <c r="K55" s="34" t="n"/>
+      <c r="L55" s="34" t="n"/>
+      <c r="M55" s="35" t="n"/>
       <c r="N55" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17443,7 +17439,7 @@
       </c>
       <c r="O55" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -17453,12 +17449,12 @@
       </c>
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
         <is>
-          <t>587-182.126</t>
+          <t>2619802505</t>
         </is>
       </c>
       <c r="D56" s="32" t="n"/>
@@ -17479,10 +17475,10 @@
         <v>6.8</v>
       </c>
       <c r="I56" s="34" t="n">
-        <v>12354</v>
+        <v>12252</v>
       </c>
       <c r="J56" s="34" t="n">
-        <v>12354</v>
+        <v>12252</v>
       </c>
       <c r="K56" s="34" t="n"/>
       <c r="L56" s="34" t="n"/>
@@ -17504,18 +17500,20 @@
       </c>
       <c r="B57" s="33" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
         </is>
       </c>
       <c r="C57" s="32" t="inlineStr">
         <is>
-          <t>2619802505</t>
-        </is>
-      </c>
-      <c r="D57" s="32" t="n"/>
+          <t>522-03.124-04</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="n">
+        <v>50</v>
+      </c>
       <c r="E57" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F57" s="32" t="inlineStr">
@@ -17527,17 +17525,23 @@
         <v>1</v>
       </c>
       <c r="H57" s="32" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="I57" s="34" t="n">
-        <v>12354</v>
+        <v>10311</v>
       </c>
       <c r="J57" s="34" t="n">
-        <v>12354</v>
-      </c>
-      <c r="K57" s="34" t="n"/>
-      <c r="L57" s="34" t="n"/>
-      <c r="M57" s="35" t="n"/>
+        <v>10311</v>
+      </c>
+      <c r="K57" s="34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L57" s="34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M57" s="35" t="n">
+        <v>0.52</v>
+      </c>
       <c r="N57" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17545,7 +17549,7 @@
       </c>
       <c r="O57" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -17555,20 +17559,20 @@
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
+          <t>Клапан педальный Ду25</t>
         </is>
       </c>
       <c r="C58" s="32" t="inlineStr">
         <is>
-          <t>522-03.124-04</t>
+          <t>М528-03.001</t>
         </is>
       </c>
       <c r="D58" s="32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Педальные клапаны</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -17580,22 +17584,22 @@
         <v>1</v>
       </c>
       <c r="H58" s="32" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="I58" s="34" t="n">
-        <v>10311</v>
+        <v>9910</v>
       </c>
       <c r="J58" s="34" t="n">
-        <v>10311</v>
+        <v>9910</v>
       </c>
       <c r="K58" s="34" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="L58" s="34" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="M58" s="35" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="N58" s="38" t="inlineStr">
         <is>
@@ -17614,16 +17618,20 @@
       </c>
       <c r="B59" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
-        </is>
-      </c>
-      <c r="C59" s="32" t="inlineStr"/>
+          <t>Грибки АМГ Ду 150 (нижние)</t>
+        </is>
+      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>(541-03.316-02)</t>
+        </is>
+      </c>
       <c r="D59" s="32" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -17632,26 +17640,20 @@
         </is>
       </c>
       <c r="G59" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" s="32" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="I59" s="34" t="n">
-        <v>10022</v>
+        <v>4865</v>
       </c>
       <c r="J59" s="34" t="n">
-        <v>10022</v>
-      </c>
-      <c r="K59" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L59" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="M59" s="35" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+        <v>9730</v>
+      </c>
+      <c r="K59" s="34" t="n"/>
+      <c r="L59" s="34" t="n"/>
+      <c r="M59" s="35" t="n"/>
       <c r="N59" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17659,7 +17661,7 @@
       </c>
       <c r="O59" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17693,10 +17695,10 @@
         <v>6.2</v>
       </c>
       <c r="I60" s="34" t="n">
-        <v>10022</v>
+        <v>9563</v>
       </c>
       <c r="J60" s="34" t="n">
-        <v>10022</v>
+        <v>9563</v>
       </c>
       <c r="K60" s="34" t="n">
         <v>18000</v>
@@ -17705,7 +17707,7 @@
         <v>18000</v>
       </c>
       <c r="M60" s="35" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="N60" s="38" t="inlineStr">
         <is>
@@ -17714,7 +17716,7 @@
       </c>
       <c r="O60" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -17724,20 +17726,16 @@
       </c>
       <c r="B61" s="33" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25</t>
-        </is>
-      </c>
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t>М528-03.001</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду60</t>
+        </is>
+      </c>
+      <c r="C61" s="32" t="inlineStr"/>
       <c r="D61" s="32" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>Педальные клапаны</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F61" s="32" t="inlineStr">
@@ -17749,22 +17747,22 @@
         <v>1</v>
       </c>
       <c r="H61" s="32" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I61" s="34" t="n">
-        <v>9993</v>
+        <v>9563</v>
       </c>
       <c r="J61" s="34" t="n">
-        <v>9993</v>
+        <v>9563</v>
       </c>
       <c r="K61" s="34" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="L61" s="34" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="M61" s="35" t="n">
-        <v>0.67</v>
+        <v>0.53</v>
       </c>
       <c r="N61" s="38" t="inlineStr">
         <is>
@@ -17773,7 +17771,7 @@
       </c>
       <c r="O61" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -17783,20 +17781,20 @@
       </c>
       <c r="B62" s="33" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 150 (нижние)</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>(541-03.316-02)</t>
+          <t>554-03.909-03</t>
         </is>
       </c>
       <c r="D62" s="32" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="F62" s="32" t="inlineStr">
@@ -17805,16 +17803,16 @@
         </is>
       </c>
       <c r="G62" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="32" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="I62" s="34" t="n">
-        <v>4905</v>
+        <v>3063</v>
       </c>
       <c r="J62" s="34" t="n">
-        <v>9811</v>
+        <v>9189</v>
       </c>
       <c r="K62" s="34" t="n"/>
       <c r="L62" s="34" t="n"/>
@@ -17836,16 +17834,16 @@
       </c>
       <c r="B63" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Стакан переборочный Ду25Ру100</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>554-03.909-03</t>
+          <t>554-35.156</t>
         </is>
       </c>
       <c r="D63" s="32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E63" s="32" t="inlineStr">
         <is>
@@ -17858,16 +17856,16 @@
         </is>
       </c>
       <c r="G63" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63" s="32" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="I63" s="34" t="n">
-        <v>3089</v>
+        <v>4505</v>
       </c>
       <c r="J63" s="34" t="n">
-        <v>9266</v>
+        <v>9009</v>
       </c>
       <c r="K63" s="34" t="n"/>
       <c r="L63" s="34" t="n"/>
@@ -17889,20 +17887,20 @@
       </c>
       <c r="B64" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду25Ру100</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
         </is>
       </c>
       <c r="C64" s="32" t="inlineStr">
         <is>
-          <t>554-35.156</t>
+          <t>541-03.224</t>
         </is>
       </c>
       <c r="D64" s="32" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E64" s="32" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F64" s="32" t="inlineStr">
@@ -17911,16 +17909,16 @@
         </is>
       </c>
       <c r="G64" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64" s="32" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="I64" s="34" t="n">
-        <v>4542</v>
+        <v>2703</v>
       </c>
       <c r="J64" s="34" t="n">
-        <v>9084</v>
+        <v>8108</v>
       </c>
       <c r="K64" s="34" t="n"/>
       <c r="L64" s="34" t="n"/>
@@ -17942,20 +17940,20 @@
       </c>
       <c r="B65" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr">
         <is>
-          <t>541-03.224</t>
+          <t>521-3М.123</t>
         </is>
       </c>
       <c r="D65" s="32" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E65" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F65" s="32" t="inlineStr">
@@ -17964,16 +17962,16 @@
         </is>
       </c>
       <c r="G65" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H65" s="32" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="I65" s="34" t="n">
-        <v>2725</v>
+        <v>7614</v>
       </c>
       <c r="J65" s="34" t="n">
-        <v>8176</v>
+        <v>7614</v>
       </c>
       <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
@@ -17985,7 +17983,7 @@
       </c>
       <c r="O65" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -18000,7 +17998,7 @@
       </c>
       <c r="C66" s="32" t="inlineStr">
         <is>
-          <t>521-3М.123</t>
+          <t>521-3М539</t>
         </is>
       </c>
       <c r="D66" s="32" t="n">
@@ -18028,9 +18026,15 @@
       <c r="J66" s="34" t="n">
         <v>7614</v>
       </c>
-      <c r="K66" s="34" t="n"/>
-      <c r="L66" s="34" t="n"/>
-      <c r="M66" s="35" t="n"/>
+      <c r="K66" s="34" t="n">
+        <v>9600</v>
+      </c>
+      <c r="L66" s="34" t="n">
+        <v>9600</v>
+      </c>
+      <c r="M66" s="35" t="n">
+        <v>0.79</v>
+      </c>
       <c r="N66" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -18038,7 +18042,7 @@
       </c>
       <c r="O66" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -18048,20 +18052,14 @@
       </c>
       <c r="B67" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
-        </is>
-      </c>
-      <c r="C67" s="32" t="inlineStr">
-        <is>
-          <t>521-3М539</t>
-        </is>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>25</v>
-      </c>
+          <t>Эжектор ВЭЖ 6,3</t>
+        </is>
+      </c>
+      <c r="C67" s="32" t="inlineStr"/>
+      <c r="D67" s="32" t="n"/>
       <c r="E67" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Эжекторы</t>
         </is>
       </c>
       <c r="F67" s="32" t="inlineStr">
@@ -18073,23 +18071,17 @@
         <v>1</v>
       </c>
       <c r="H67" s="32" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="I67" s="34" t="n">
-        <v>7614</v>
+        <v>7207</v>
       </c>
       <c r="J67" s="34" t="n">
-        <v>7614</v>
-      </c>
-      <c r="K67" s="34" t="n">
-        <v>9600</v>
-      </c>
-      <c r="L67" s="34" t="n">
-        <v>9600</v>
-      </c>
-      <c r="M67" s="35" t="n">
-        <v>0.79</v>
-      </c>
+        <v>7207</v>
+      </c>
+      <c r="K67" s="34" t="n"/>
+      <c r="L67" s="34" t="n"/>
+      <c r="M67" s="35" t="n"/>
       <c r="N67" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -18097,7 +18089,7 @@
       </c>
       <c r="O67" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -18107,14 +18099,16 @@
       </c>
       <c r="B68" s="33" t="inlineStr">
         <is>
-          <t>Эжектор ВЭЖ 6,3</t>
+          <t>Задвижка клинкетная Ду 50, без клиньев</t>
         </is>
       </c>
       <c r="C68" s="32" t="inlineStr"/>
-      <c r="D68" s="32" t="n"/>
+      <c r="D68" s="32" t="n">
+        <v>50</v>
+      </c>
       <c r="E68" s="32" t="inlineStr">
         <is>
-          <t>Эжекторы</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F68" s="32" t="inlineStr">
@@ -18126,17 +18120,23 @@
         <v>1</v>
       </c>
       <c r="H68" s="32" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I68" s="34" t="n">
-        <v>7267</v>
+        <v>6403</v>
       </c>
       <c r="J68" s="34" t="n">
-        <v>7267</v>
-      </c>
-      <c r="K68" s="34" t="n"/>
-      <c r="L68" s="34" t="n"/>
-      <c r="M68" s="35" t="n"/>
+        <v>6403</v>
+      </c>
+      <c r="K68" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L68" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M68" s="35" t="n">
+        <v>0.26</v>
+      </c>
       <c r="N68" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -18144,7 +18144,7 @@
       </c>
       <c r="O68" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -18154,16 +18154,20 @@
       </c>
       <c r="B69" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 50, без клиньев</t>
-        </is>
-      </c>
-      <c r="C69" s="32" t="inlineStr"/>
+          <t>Стакан переборочный Ду10Ру100</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>554-35.265</t>
+        </is>
+      </c>
       <c r="D69" s="32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E69" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="F69" s="32" t="inlineStr">
@@ -18172,26 +18176,20 @@
         </is>
       </c>
       <c r="G69" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H69" s="32" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="I69" s="34" t="n">
-        <v>6711</v>
+        <v>1081</v>
       </c>
       <c r="J69" s="34" t="n">
-        <v>6711</v>
-      </c>
-      <c r="K69" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="L69" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M69" s="35" t="n">
-        <v>0.27</v>
-      </c>
+        <v>5405</v>
+      </c>
+      <c r="K69" s="34" t="n"/>
+      <c r="L69" s="34" t="n"/>
+      <c r="M69" s="35" t="n"/>
       <c r="N69" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -18199,7 +18197,7 @@
       </c>
       <c r="O69" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -18209,38 +18207,36 @@
       </c>
       <c r="B70" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду10Ру100</t>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
-          <t>554-35.265</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>10</v>
-      </c>
+          <t>521-03.472-01</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="n"/>
       <c r="E70" s="32" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F70" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>нержавейка</t>
         </is>
       </c>
       <c r="G70" s="34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H70" s="32" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="I70" s="34" t="n">
-        <v>1090</v>
+        <v>3954</v>
       </c>
       <c r="J70" s="34" t="n">
-        <v>5450</v>
+        <v>3954</v>
       </c>
       <c r="K70" s="34" t="n"/>
       <c r="L70" s="34" t="n"/>
@@ -18252,63 +18248,12 @@
       </c>
       <c r="O70" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="32" t="n">
-        <v>67</v>
-      </c>
-      <c r="B71" s="33" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
-        </is>
-      </c>
-      <c r="C71" s="32" t="inlineStr">
-        <is>
-          <t>521-03.472-01</t>
-        </is>
-      </c>
-      <c r="D71" s="32" t="n"/>
-      <c r="E71" s="32" t="inlineStr">
-        <is>
-          <t>Штуцерная угловая</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>нержавейка</t>
-        </is>
-      </c>
-      <c r="G71" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I71" s="34" t="n">
-        <v>3954</v>
-      </c>
-      <c r="J71" s="34" t="n">
-        <v>3954</v>
-      </c>
-      <c r="K71" s="34" t="n"/>
-      <c r="L71" s="34" t="n"/>
-      <c r="M71" s="35" t="n"/>
-      <c r="N71" s="38" t="inlineStr">
-        <is>
-          <t>оценка по цене килограмма</t>
-        </is>
-      </c>
-      <c r="O71" s="32" t="inlineStr">
-        <is>
           <t>Склад 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O71"/>
+  <autoFilter ref="A4:O70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
+++ b/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -803,153 +803,198 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
+          <t>ВЕСЬ СКЛАД В ЛОМЕ, руб</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>13213185</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>латунь 500, бронза 600, сталь 9 руб за кг. Считаем по латуни — осторожнее</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Он же по бронзе 600 руб за кг</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>16377129</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>верхняя граница лома</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Во сколько раз рынок дороже лома</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>запас между ценой приемки и ценой рынка</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
           <t>Позиций без согласованной цены у нас</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B21" s="18" t="n">
         <v>58</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>вес у них есть, а рублей в учете нет — наша сумма занижена именно на них</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Отгрузка в Петербург: сколько съедает логистика</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Расходы на доставку, руб</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Везем товара на, руб</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Доля логистики</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Руб на килограмм товара</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Усиленный двадцатифутовый, 27 т</t>
         </is>
       </c>
-      <c r="B22" s="23" t="n">
+      <c r="B25" s="23" t="n">
         <v>401000</v>
       </c>
-      <c r="C22" s="23" t="n">
+      <c r="C25" s="23" t="n">
         <v>49160598</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D25" s="24" t="n">
         <v>0.008156939063804707</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E25" s="25" t="n">
         <v>14.7</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B26" s="27" t="n">
         <v>632000</v>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C26" s="27" t="n">
         <v>49160598</v>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D26" s="28" t="n">
         <v>0.01285582416041041</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E26" s="29" t="n">
         <v>23.2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Один сорокафутовый</t>
         </is>
       </c>
-      <c r="B24" s="27" t="n">
+      <c r="B27" s="27" t="n">
         <v>541000</v>
       </c>
-      <c r="C24" s="27" t="n">
+      <c r="C27" s="27" t="n">
         <v>49160598</v>
       </c>
-      <c r="D24" s="28" t="n">
+      <c r="D27" s="28" t="n">
         <v>0.01100474821326271</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E27" s="29" t="n">
         <v>19.8</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>За базу взят весь перечень — 27.30 т на 49.2 млн. В усиленный контейнер входит 26,35 т из них, на долю логистики эта разница не влияет.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Что из этого следует</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>— Вся арматура и фильтры на складе по ценам конкурента — 49.2 млн руб при весе 27.3 т. По нашим учетным ценам те же позиции стоят 38.7 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>— Доставка в Петербург стоит от 401 000 руб и съедает 0.8% стоимости отгружаемого товара. Для товара  который едет через всю страну  это немного: транспортная компания на том же весе взяла бы в несколько раз больше.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 802 руб  а довезти его до Петербурга стоит 14.7 руб. Отсюда и доля.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>— Твердая часть оценки — 220 позиций на 36.7 млн, это цены по чертежу и по типу. Остальное оценено по цене килограмма и годится для прикидки, а не для переговоров.</t>
+          <t>— Вся арматура и фильтры на складе по ценам конкурента — 49.2 млн руб при весе 27.3 т. По нашим учетным ценам те же позиции стоят 38.7 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>— Доставка в Петербург стоит от 401 000 руб и съедает 0.8% стоимости отгружаемого товара. Для товара  который едет через всю страну  это немного: транспортная компания на том же весе взяла бы в несколько раз больше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 802 руб  а довезти его до Петербурга стоит 14.7 руб. Отсюда и доля.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>— Твердая часть оценки — 220 позиций на 36.7 млн, это цены по чертежу и по типу. Остальное оценено по цене килограмма и годится для прикидки, а не для переговоров.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>— Цены конкурента — это его прайс, а не сделки. Реальная цена продажи обычно ниже прайса, и до инвентаризации эти суммы покупателю не называем.</t>
         </is>

--- a/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
+++ b/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>38705750</v>
+        <v>40033750</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>10454848</v>
+        <v>9126848</v>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B16" s="21" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>— Вся арматура и фильтры на складе по ценам конкурента — 49.2 млн руб при весе 27.3 т. По нашим учетным ценам те же позиции стоят 38.7 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
+          <t>— Вся арматура и фильтры на складе по ценам конкурента — 49.2 млн руб при весе 27.3 т. По нашим учетным ценам те же позиции стоят 40.0 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
         </is>
       </c>
     </row>
@@ -1129,10 +1129,10 @@
         <v>6151400</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>7685500</v>
+        <v>8483500</v>
       </c>
       <c r="G5" s="31" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>2512</v>
@@ -1160,10 +1160,10 @@
         <v>1783447</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>1318500</v>
+        <v>1343500</v>
       </c>
       <c r="G6" s="31" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>6784</v>
@@ -1222,10 +1222,10 @@
         <v>8161695</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>6666600</v>
+        <v>6826600</v>
       </c>
       <c r="G8" s="31" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>1944</v>
@@ -1284,10 +1284,10 @@
         <v>16440392</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>12313500</v>
+        <v>12761000</v>
       </c>
       <c r="G10" s="31" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>1536</v>
@@ -1315,10 +1315,10 @@
         <v>3343718</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>2508000</v>
+        <v>2328000</v>
       </c>
       <c r="G11" s="31" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>1829</v>
@@ -1466,10 +1466,10 @@
         <v>5011434</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>1677500</v>
+        <v>1750000</v>
       </c>
       <c r="G16" s="31" t="n">
-        <v>2.99</v>
+        <v>2.86</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>1436</v>
@@ -1619,10 +1619,10 @@
         <v>58739</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="G21" s="31" t="n">
-        <v>1.07</v>
+        <v>0.98</v>
       </c>
       <c r="H21" s="27" t="n">
         <v>1802</v>
@@ -1915,13 +1915,13 @@
         <v>2593500</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>3192000</v>
+        <v>3990000</v>
       </c>
       <c r="M5" s="35" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="N5" s="36" t="inlineStr">
         <is>
@@ -6468,13 +6468,13 @@
         <v>2850000</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>140000</v>
+        <v>150000</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>2660000</v>
+        <v>2850000</v>
       </c>
       <c r="M5" s="35" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="N5" s="37" t="inlineStr">
         <is>
@@ -6578,13 +6578,13 @@
         <v>2250000</v>
       </c>
       <c r="K7" s="34" t="n">
-        <v>87500</v>
+        <v>90000</v>
       </c>
       <c r="L7" s="34" t="n">
-        <v>1312500</v>
+        <v>1350000</v>
       </c>
       <c r="M7" s="35" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="N7" s="37" t="inlineStr">
         <is>
@@ -6633,13 +6633,13 @@
         <v>1800000</v>
       </c>
       <c r="K8" s="34" t="n">
-        <v>160000</v>
+        <v>170000</v>
       </c>
       <c r="L8" s="34" t="n">
-        <v>1280000</v>
+        <v>1360000</v>
       </c>
       <c r="M8" s="35" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="N8" s="37" t="inlineStr">
         <is>
@@ -6853,13 +6853,13 @@
         <v>1173000</v>
       </c>
       <c r="K12" s="34" t="n">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="L12" s="34" t="n">
-        <v>892500</v>
+        <v>1020000</v>
       </c>
       <c r="M12" s="35" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="N12" s="37" t="inlineStr">
         <is>
@@ -6957,13 +6957,13 @@
         <v>1008000</v>
       </c>
       <c r="K14" s="34" t="n">
-        <v>50000</v>
+        <v>55000</v>
       </c>
       <c r="L14" s="34" t="n">
-        <v>600000</v>
+        <v>660000</v>
       </c>
       <c r="M14" s="35" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="N14" s="37" t="inlineStr">
         <is>
@@ -7772,13 +7772,13 @@
         <v>250000</v>
       </c>
       <c r="K29" s="34" t="n">
-        <v>32500</v>
+        <v>35000</v>
       </c>
       <c r="L29" s="34" t="n">
-        <v>162500</v>
+        <v>175000</v>
       </c>
       <c r="M29" s="35" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="N29" s="37" t="inlineStr">
         <is>
@@ -8564,13 +8564,13 @@
         <v>115000</v>
       </c>
       <c r="K43" s="34" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="L43" s="34" t="n">
-        <v>150000</v>
+        <v>175000</v>
       </c>
       <c r="M43" s="35" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="N43" s="37" t="inlineStr">
         <is>
@@ -8890,13 +8890,13 @@
         <v>87500</v>
       </c>
       <c r="K49" s="34" t="n">
-        <v>352500</v>
+        <v>55000</v>
       </c>
       <c r="L49" s="34" t="n">
-        <v>352500</v>
+        <v>55000</v>
       </c>
       <c r="M49" s="35" t="n">
-        <v>0.25</v>
+        <v>1.59</v>
       </c>
       <c r="N49" s="37" t="inlineStr">
         <is>
@@ -10474,13 +10474,13 @@
         <v>36000</v>
       </c>
       <c r="K77" s="34" t="n">
-        <v>47500</v>
+        <v>55000</v>
       </c>
       <c r="L77" s="34" t="n">
-        <v>47500</v>
+        <v>55000</v>
       </c>
       <c r="M77" s="35" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="N77" s="37" t="inlineStr">
         <is>
@@ -14715,13 +14715,13 @@
         <v>3834142</v>
       </c>
       <c r="K5" s="34" t="n">
-        <v>185000</v>
+        <v>200000</v>
       </c>
       <c r="L5" s="34" t="n">
-        <v>2405000</v>
+        <v>2600000</v>
       </c>
       <c r="M5" s="35" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="N5" s="38" t="inlineStr">
         <is>
@@ -15043,13 +15043,13 @@
         <v>585390</v>
       </c>
       <c r="K11" s="34" t="n">
-        <v>82500</v>
+        <v>90000</v>
       </c>
       <c r="L11" s="34" t="n">
-        <v>412500</v>
+        <v>450000</v>
       </c>
       <c r="M11" s="35" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="N11" s="38" t="inlineStr">
         <is>
@@ -15214,13 +15214,13 @@
         <v>373106</v>
       </c>
       <c r="K14" s="34" t="n">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="L14" s="34" t="n">
-        <v>175000</v>
+        <v>200000</v>
       </c>
       <c r="M14" s="35" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="N14" s="38" t="inlineStr">
         <is>
@@ -15269,13 +15269,13 @@
         <v>350234</v>
       </c>
       <c r="K15" s="34" t="n">
-        <v>275000</v>
+        <v>300000</v>
       </c>
       <c r="L15" s="34" t="n">
-        <v>275000</v>
+        <v>300000</v>
       </c>
       <c r="M15" s="35" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="N15" s="38" t="inlineStr">
         <is>
@@ -16328,13 +16328,13 @@
         <v>58739</v>
       </c>
       <c r="K34" s="34" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="L34" s="34" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="M34" s="35" t="n">
-        <v>1.07</v>
+        <v>0.98</v>
       </c>
       <c r="N34" s="38" t="inlineStr">
         <is>

--- a/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
+++ b/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>40033750</v>
+        <v>40043750</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>9126848</v>
+        <v>9116848</v>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
     </row>
@@ -1315,10 +1315,10 @@
         <v>3343718</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>2328000</v>
+        <v>2338000</v>
       </c>
       <c r="G11" s="31" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>1829</v>
@@ -8890,13 +8890,13 @@
         <v>87500</v>
       </c>
       <c r="K49" s="34" t="n">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="L49" s="34" t="n">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="M49" s="35" t="n">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="N49" s="37" t="inlineStr">
         <is>

--- a/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
+++ b/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>13213185</v>
+        <v>12948348</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G7" s="34" t="n">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G13" s="34" t="n">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G19" s="34" t="n">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="F44" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G44" s="34" t="n">
@@ -16911,7 +16911,7 @@
       </c>
       <c r="F45" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G45" s="34" t="n">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="F47" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G47" s="34" t="n">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="F59" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G59" s="34" t="n">
@@ -17950,7 +17950,7 @@
       </c>
       <c r="F64" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G64" s="34" t="n">

--- a/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
+++ b/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Цена по чертежу'!$A$4:$O$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Цена по типу'!$A$4:$O$148</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Оценка по килограмму'!$A$4:$O$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Цена по типу'!$A$4:$O$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Оценка по килограмму'!$A$4:$O$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -635,7 +635,7 @@
         <v>7542925</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.1534343630619679</v>
+        <v>0.1547868514052207</v>
       </c>
     </row>
     <row r="7">
@@ -645,19 +645,19 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1175</v>
+        <v>1184</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>17117</v>
+        <v>17360</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>29179750</v>
+        <v>29233750</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.5935597073492652</v>
+        <v>0.5998999217501658</v>
       </c>
     </row>
     <row r="8">
@@ -667,19 +667,19 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>6914</v>
+        <v>6671</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>12437922.72707907</v>
+        <v>11954369.86280412</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.2530059295887672</v>
+        <v>0.245313226844614</v>
       </c>
     </row>
     <row r="9">
@@ -720,7 +720,7 @@
         <v>27295</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>49160597.72707906</v>
+        <v>48731044.8628041</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>49160598</v>
+        <v>48731045</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>9116848</v>
+        <v>8687295</v>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B16" s="21" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>1802</v>
+        <v>1783</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         <v>401000</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>49160598</v>
+        <v>48731045</v>
       </c>
       <c r="D25" s="24" t="n">
-        <v>0.008156939063804707</v>
+        <v>0.008228840590817684</v>
       </c>
       <c r="E25" s="25" t="n">
         <v>14.7</v>
@@ -923,10 +923,10 @@
         <v>632000</v>
       </c>
       <c r="C26" s="27" t="n">
-        <v>49160598</v>
+        <v>48731045</v>
       </c>
       <c r="D26" s="28" t="n">
-        <v>0.01285582416041041</v>
+        <v>0.01296914527031615</v>
       </c>
       <c r="E26" s="29" t="n">
         <v>23.2</v>
@@ -942,10 +942,10 @@
         <v>541000</v>
       </c>
       <c r="C27" s="27" t="n">
-        <v>49160598</v>
+        <v>48731045</v>
       </c>
       <c r="D27" s="28" t="n">
-        <v>0.01100474821326271</v>
+        <v>0.01110175251778645</v>
       </c>
       <c r="E27" s="29" t="n">
         <v>19.8</v>
@@ -954,7 +954,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>За базу взят весь перечень — 27.30 т на 49.2 млн. В усиленный контейнер входит 26,35 т из них, на долю логистики эта разница не влияет.</t>
+          <t>За базу взят весь перечень — 27.30 т на 48.7 млн. В усиленный контейнер входит 26,35 т из них, на долю логистики эта разница не влияет.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>— Вся арматура и фильтры на складе по ценам конкурента — 49.2 млн руб при весе 27.3 т. По нашим учетным ценам те же позиции стоят 40.0 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
+          <t>— Вся арматура и фильтры на складе по ценам конкурента — 48.7 млн руб при весе 27.3 т. По нашим учетным ценам те же позиции стоят 40.0 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
         </is>
       </c>
     </row>
@@ -982,14 +982,14 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="30" t="inlineStr">
         <is>
-          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 802 руб  а довезти его до Петербурга стоит 14.7 руб. Отсюда и доля.</t>
+          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 783 руб  а довезти его до Петербурга стоит 14.7 руб. Отсюда и доля.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t>— Твердая часть оценки — 220 позиций на 36.7 млн, это цены по чертежу и по типу. Остальное оценено по цене килограмма и годится для прикидки, а не для переговоров.</t>
+          <t>— Твердая часть оценки — 221 позиция на 36.8 млн, это цены по чертежу и по типу. Остальное оценено по цене килограмма и годится для прикидки, а не для переговоров.</t>
         </is>
       </c>
     </row>
@@ -1250,16 +1250,16 @@
         <v>106</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>190991</v>
+        <v>189018</v>
       </c>
       <c r="F9" s="27" t="n">
         <v>74250</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="H9" s="27" t="n">
-        <v>1802</v>
+        <v>1783</v>
       </c>
       <c r="I9" s="26" t="n">
         <v>0</v>
@@ -1374,14 +1374,14 @@
         <v>363</v>
       </c>
       <c r="E13" s="27" t="n">
-        <v>653693</v>
+        <v>646941</v>
       </c>
       <c r="F13" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="31" t="n"/>
       <c r="H13" s="27" t="n">
-        <v>1802</v>
+        <v>1783</v>
       </c>
       <c r="I13" s="26" t="n">
         <v>0</v>
@@ -1525,14 +1525,14 @@
         <v>52</v>
       </c>
       <c r="E18" s="27" t="n">
-        <v>93874</v>
+        <v>92904</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="31" t="n"/>
       <c r="H18" s="27" t="n">
-        <v>1802</v>
+        <v>1783</v>
       </c>
       <c r="I18" s="26" t="n">
         <v>0</v>
@@ -1554,16 +1554,16 @@
         <v>110</v>
       </c>
       <c r="E19" s="27" t="n">
-        <v>197477</v>
+        <v>195438</v>
       </c>
       <c r="F19" s="27" t="n">
         <v>415000</v>
       </c>
       <c r="G19" s="31" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H19" s="27" t="n">
-        <v>1802</v>
+        <v>1783</v>
       </c>
       <c r="I19" s="26" t="n">
         <v>0</v>
@@ -1585,16 +1585,16 @@
         <v>258</v>
       </c>
       <c r="E20" s="27" t="n">
-        <v>464865</v>
+        <v>57333</v>
       </c>
       <c r="F20" s="27" t="n">
         <v>345000</v>
       </c>
       <c r="G20" s="31" t="n">
-        <v>1.35</v>
+        <v>0.17</v>
       </c>
       <c r="H20" s="27" t="n">
-        <v>1802</v>
+        <v>222</v>
       </c>
       <c r="I20" s="26" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>33</v>
       </c>
       <c r="E21" s="27" t="n">
-        <v>58739</v>
+        <v>58132</v>
       </c>
       <c r="F21" s="27" t="n">
         <v>60000</v>
       </c>
       <c r="G21" s="31" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="H21" s="27" t="n">
-        <v>1802</v>
+        <v>1783</v>
       </c>
       <c r="I21" s="26" t="n">
         <v>0</v>
@@ -1678,16 +1678,16 @@
         <v>346</v>
       </c>
       <c r="E23" s="27" t="n">
-        <v>624324</v>
+        <v>617875</v>
       </c>
       <c r="F23" s="27" t="n">
         <v>945000</v>
       </c>
       <c r="G23" s="31" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H23" s="27" t="n">
-        <v>1802</v>
+        <v>1783</v>
       </c>
       <c r="I23" s="26" t="n">
         <v>0</v>
@@ -1709,14 +1709,14 @@
         <v>4</v>
       </c>
       <c r="E24" s="27" t="n">
-        <v>7207</v>
+        <v>7133</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="31" t="n"/>
       <c r="H24" s="27" t="n">
-        <v>1802</v>
+        <v>1783</v>
       </c>
       <c r="I24" s="26" t="n">
         <v>0</v>
@@ -1738,16 +1738,16 @@
         <v>170</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>305681</v>
+        <v>302524</v>
       </c>
       <c r="F25" s="27" t="n">
         <v>47000</v>
       </c>
       <c r="G25" s="31" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="H25" s="27" t="n">
-        <v>1802</v>
+        <v>1783</v>
       </c>
       <c r="I25" s="26" t="n">
         <v>0</v>
@@ -6321,7 +6321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O148"/>
+  <dimension ref="A1:O149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9813,42 +9813,48 @@
       </c>
       <c r="B66" s="33" t="inlineStr">
         <is>
-          <t>Клапан для колонки указательной Ду10 Ру16</t>
+          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
         <is>
-          <t>598-03.022-06</t>
+          <t>525-03.044</t>
         </is>
       </c>
       <c r="D66" s="32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E66" s="32" t="inlineStr">
         <is>
-          <t>Колонка смотровая</t>
+          <t>Редукционные клапаны</t>
         </is>
       </c>
       <c r="F66" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G66" s="34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H66" s="32" t="n">
-        <v>1.5</v>
+        <v>27</v>
       </c>
       <c r="I66" s="34" t="n">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="J66" s="34" t="n">
         <v>54000</v>
       </c>
-      <c r="K66" s="34" t="n"/>
-      <c r="L66" s="34" t="n"/>
-      <c r="M66" s="35" t="n"/>
+      <c r="K66" s="34" t="n">
+        <v>35000</v>
+      </c>
+      <c r="L66" s="34" t="n">
+        <v>315000</v>
+      </c>
+      <c r="M66" s="35" t="n">
+        <v>0.17</v>
+      </c>
       <c r="N66" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -9856,7 +9862,7 @@
       </c>
       <c r="O66" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -9866,20 +9872,20 @@
       </c>
       <c r="B67" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан для колонки указательной Ду10 Ру16</t>
         </is>
       </c>
       <c r="C67" s="32" t="inlineStr">
         <is>
-          <t>522-01500-05</t>
+          <t>598-03.022-06</t>
         </is>
       </c>
       <c r="D67" s="32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E67" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Колонка смотровая</t>
         </is>
       </c>
       <c r="F67" s="32" t="inlineStr">
@@ -9888,26 +9894,20 @@
         </is>
       </c>
       <c r="G67" s="34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H67" s="32" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="I67" s="34" t="n">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="J67" s="34" t="n">
         <v>54000</v>
       </c>
-      <c r="K67" s="34" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L67" s="34" t="n">
-        <v>54000</v>
-      </c>
-      <c r="M67" s="35" t="n">
-        <v>1</v>
-      </c>
+      <c r="K67" s="34" t="n"/>
+      <c r="L67" s="34" t="n"/>
+      <c r="M67" s="35" t="n"/>
       <c r="N67" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O67" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -9925,16 +9925,20 @@
       </c>
       <c r="B68" s="33" t="inlineStr">
         <is>
-          <t>Фильтр забортной воды Ду 50</t>
-        </is>
-      </c>
-      <c r="C68" s="32" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>522-01500-05</t>
+        </is>
+      </c>
       <c r="D68" s="32" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E68" s="32" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F68" s="32" t="inlineStr">
@@ -9943,26 +9947,26 @@
         </is>
       </c>
       <c r="G68" s="34" t="n">
+        <v>9</v>
+      </c>
+      <c r="H68" s="32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I68" s="34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J68" s="34" t="n">
+        <v>54000</v>
+      </c>
+      <c r="K68" s="34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L68" s="34" t="n">
+        <v>54000</v>
+      </c>
+      <c r="M68" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H68" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I68" s="34" t="n">
-        <v>47500</v>
-      </c>
-      <c r="J68" s="34" t="n">
-        <v>47500</v>
-      </c>
-      <c r="K68" s="34" t="n">
-        <v>60000</v>
-      </c>
-      <c r="L68" s="34" t="n">
-        <v>60000</v>
-      </c>
-      <c r="M68" s="35" t="n">
-        <v>0.79</v>
-      </c>
       <c r="N68" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -9970,7 +9974,7 @@
       </c>
       <c r="O68" s="32" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -9980,20 +9984,16 @@
       </c>
       <c r="B69" s="33" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
-        </is>
-      </c>
-      <c r="C69" s="32" t="inlineStr">
-        <is>
-          <t>536-35.695</t>
-        </is>
-      </c>
+          <t>Фильтр забортной воды Ду 50</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="inlineStr"/>
       <c r="D69" s="32" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E69" s="32" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="F69" s="32" t="inlineStr">
@@ -10002,25 +10002,25 @@
         </is>
       </c>
       <c r="G69" s="34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H69" s="32" t="n">
-        <v>2.8</v>
+        <v>7.8</v>
       </c>
       <c r="I69" s="34" t="n">
-        <v>6000</v>
+        <v>47500</v>
       </c>
       <c r="J69" s="34" t="n">
-        <v>42000</v>
+        <v>47500</v>
       </c>
       <c r="K69" s="34" t="n">
-        <v>5000</v>
+        <v>60000</v>
       </c>
       <c r="L69" s="34" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="M69" s="35" t="n">
-        <v>1.2</v>
+        <v>0.79</v>
       </c>
       <c r="N69" s="37" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
       </c>
       <c r="O69" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="B70" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Кран трехходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="C70" s="32" t="inlineStr">
         <is>
-          <t>521-01464-03</t>
+          <t>536-35.695</t>
         </is>
       </c>
       <c r="D70" s="32" t="n">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="E70" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="F70" s="32" t="inlineStr">
@@ -10064,7 +10064,7 @@
         <v>7</v>
       </c>
       <c r="H70" s="32" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="I70" s="34" t="n">
         <v>6000</v>
@@ -10073,13 +10073,13 @@
         <v>42000</v>
       </c>
       <c r="K70" s="34" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="L70" s="34" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="M70" s="35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N70" s="37" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="O70" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -10098,20 +10098,20 @@
       </c>
       <c r="B71" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15Ру100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C71" s="32" t="inlineStr">
         <is>
-          <t>521-01.468</t>
+          <t>521-01464-03</t>
         </is>
       </c>
       <c r="D71" s="32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E71" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F71" s="32" t="inlineStr">
@@ -10123,7 +10123,7 @@
         <v>7</v>
       </c>
       <c r="H71" s="32" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="I71" s="34" t="n">
         <v>6000</v>
@@ -10157,20 +10157,20 @@
       </c>
       <c r="B72" s="33" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Клапан штуцерный угловой Ду15Ру100</t>
         </is>
       </c>
       <c r="C72" s="32" t="inlineStr">
         <is>
-          <t>без чертежа</t>
+          <t>521-01.468</t>
         </is>
       </c>
       <c r="D72" s="32" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="E72" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F72" s="32" t="inlineStr">
@@ -10179,25 +10179,25 @@
         </is>
       </c>
       <c r="G72" s="34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H72" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="I72" s="34" t="n">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="J72" s="34" t="n">
-        <v>40000</v>
+        <v>42000</v>
       </c>
       <c r="K72" s="34" t="n">
-        <v>25000</v>
+        <v>6000</v>
       </c>
       <c r="L72" s="34" t="n">
-        <v>50000</v>
+        <v>42000</v>
       </c>
       <c r="M72" s="35" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N72" s="37" t="inlineStr">
         <is>
@@ -10216,28 +10216,32 @@
       </c>
       <c r="B73" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
-        </is>
-      </c>
-      <c r="C73" s="32" t="inlineStr"/>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+        </is>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>без чертежа</t>
+        </is>
+      </c>
       <c r="D73" s="32" t="n">
         <v>50</v>
       </c>
       <c r="E73" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F73" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G73" s="34" t="n">
         <v>2</v>
       </c>
       <c r="H73" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I73" s="34" t="n">
         <v>20000</v>
@@ -10246,13 +10250,13 @@
         <v>40000</v>
       </c>
       <c r="K73" s="34" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="L73" s="34" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="M73" s="35" t="n">
-        <v>1.33</v>
+        <v>0.8</v>
       </c>
       <c r="N73" s="37" t="inlineStr">
         <is>
@@ -10261,7 +10265,7 @@
       </c>
       <c r="O73" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10271,16 +10275,16 @@
       </c>
       <c r="B74" s="33" t="inlineStr">
         <is>
-          <t>Клинкет Ду 100, сталь</t>
+          <t>Клапан фланцевый проходной Ду50 Ру 40 сталь (522-01-322)</t>
         </is>
       </c>
       <c r="C74" s="32" t="inlineStr"/>
       <c r="D74" s="32" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E74" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F74" s="32" t="inlineStr">
@@ -10292,7 +10296,7 @@
         <v>2</v>
       </c>
       <c r="H74" s="32" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I74" s="34" t="n">
         <v>20000</v>
@@ -10301,13 +10305,13 @@
         <v>40000</v>
       </c>
       <c r="K74" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L74" s="34" t="n">
         <v>30000</v>
       </c>
-      <c r="L74" s="34" t="n">
-        <v>60000</v>
-      </c>
       <c r="M74" s="35" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="N74" s="37" t="inlineStr">
         <is>
@@ -10316,7 +10320,7 @@
       </c>
       <c r="O74" s="32" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -10326,47 +10330,43 @@
       </c>
       <c r="B75" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду125 Ру 10</t>
-        </is>
-      </c>
-      <c r="C75" s="32" t="inlineStr">
-        <is>
-          <t>без чертежа</t>
-        </is>
-      </c>
+          <t>Клинкет Ду 100, сталь</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="inlineStr"/>
       <c r="D75" s="32" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E75" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F75" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G75" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" s="32" t="n">
-        <v>46</v>
+        <v>19.2</v>
       </c>
       <c r="I75" s="34" t="n">
-        <v>37500</v>
+        <v>20000</v>
       </c>
       <c r="J75" s="34" t="n">
-        <v>37500</v>
+        <v>40000</v>
       </c>
       <c r="K75" s="34" t="n">
-        <v>55000</v>
+        <v>30000</v>
       </c>
       <c r="L75" s="34" t="n">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="M75" s="35" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="N75" s="37" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="O75" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -10385,16 +10385,20 @@
       </c>
       <c r="B76" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
-        </is>
-      </c>
-      <c r="C76" s="32" t="inlineStr"/>
+          <t>Клапан фланцевый проходной Ду125 Ру 10</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>без чертежа</t>
+        </is>
+      </c>
       <c r="D76" s="32" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E76" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F76" s="32" t="inlineStr">
@@ -10406,7 +10410,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="32" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I76" s="34" t="n">
         <v>37500</v>
@@ -10415,13 +10419,13 @@
         <v>37500</v>
       </c>
       <c r="K76" s="34" t="n">
-        <v>35000</v>
+        <v>55000</v>
       </c>
       <c r="L76" s="34" t="n">
-        <v>35000</v>
+        <v>55000</v>
       </c>
       <c r="M76" s="35" t="n">
-        <v>1.07</v>
+        <v>0.68</v>
       </c>
       <c r="N76" s="37" t="inlineStr">
         <is>
@@ -10430,7 +10434,7 @@
       </c>
       <c r="O76" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -10440,47 +10444,43 @@
       </c>
       <c r="B77" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
-        </is>
-      </c>
-      <c r="C77" s="32" t="inlineStr">
-        <is>
-          <t>521-182.116</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду100 без штока и блинов ( в разборе)</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="inlineStr"/>
       <c r="D77" s="32" t="n">
         <v>100</v>
       </c>
       <c r="E77" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F77" s="32" t="inlineStr">
         <is>
-          <t>титан</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G77" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="32" t="n">
-        <v>9.699999999999999</v>
+        <v>45</v>
       </c>
       <c r="I77" s="34" t="n">
-        <v>36000</v>
+        <v>37500</v>
       </c>
       <c r="J77" s="34" t="n">
-        <v>36000</v>
+        <v>37500</v>
       </c>
       <c r="K77" s="34" t="n">
-        <v>55000</v>
+        <v>35000</v>
       </c>
       <c r="L77" s="34" t="n">
-        <v>55000</v>
+        <v>35000</v>
       </c>
       <c r="M77" s="35" t="n">
-        <v>0.65</v>
+        <v>1.07</v>
       </c>
       <c r="N77" s="37" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
       </c>
       <c r="O77" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -10499,47 +10499,47 @@
       </c>
       <c r="B78" s="33" t="inlineStr">
         <is>
-          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
+          <t>Клапан фланцевый проходной титановые Ду100Ру10</t>
         </is>
       </c>
       <c r="C78" s="32" t="inlineStr">
         <is>
-          <t>536-3М5</t>
+          <t>521-182.116</t>
         </is>
       </c>
       <c r="D78" s="32" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E78" s="32" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F78" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>титан</t>
         </is>
       </c>
       <c r="G78" s="34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H78" s="32" t="n">
-        <v>1.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I78" s="34" t="n">
-        <v>6000</v>
+        <v>36000</v>
       </c>
       <c r="J78" s="34" t="n">
         <v>36000</v>
       </c>
       <c r="K78" s="34" t="n">
-        <v>5000</v>
+        <v>55000</v>
       </c>
       <c r="L78" s="34" t="n">
-        <v>30000</v>
+        <v>55000</v>
       </c>
       <c r="M78" s="35" t="n">
-        <v>1.2</v>
+        <v>0.65</v>
       </c>
       <c r="N78" s="37" t="inlineStr">
         <is>
@@ -10558,12 +10558,12 @@
       </c>
       <c r="B79" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
+          <t>Кран двухходовой штуцерный Ду20 Ру16</t>
         </is>
       </c>
       <c r="C79" s="32" t="inlineStr">
         <is>
-          <t>Без чертежа</t>
+          <t>536-3М5</t>
         </is>
       </c>
       <c r="D79" s="32" t="n">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="E79" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="F79" s="32" t="inlineStr">
@@ -10580,25 +10580,25 @@
         </is>
       </c>
       <c r="G79" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H79" s="32" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="I79" s="34" t="n">
         <v>6000</v>
       </c>
       <c r="J79" s="34" t="n">
-        <v>30000</v>
+        <v>36000</v>
       </c>
       <c r="K79" s="34" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="L79" s="34" t="n">
         <v>30000</v>
       </c>
       <c r="M79" s="35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N79" s="37" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="O79" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -10617,16 +10617,16 @@
       </c>
       <c r="B80" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру10</t>
         </is>
       </c>
       <c r="C80" s="32" t="inlineStr">
         <is>
-          <t>521.3м.660</t>
+          <t>Без чертежа</t>
         </is>
       </c>
       <c r="D80" s="32" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E80" s="32" t="inlineStr">
         <is>
@@ -10639,25 +10639,25 @@
         </is>
       </c>
       <c r="G80" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H80" s="32" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="I80" s="34" t="n">
-        <v>9600</v>
+        <v>6000</v>
       </c>
       <c r="J80" s="34" t="n">
-        <v>28800</v>
+        <v>30000</v>
       </c>
       <c r="K80" s="34" t="n">
-        <v>12500</v>
+        <v>6000</v>
       </c>
       <c r="L80" s="34" t="n">
-        <v>37500</v>
+        <v>30000</v>
       </c>
       <c r="M80" s="35" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="N80" s="37" t="inlineStr">
         <is>
@@ -10676,12 +10676,12 @@
       </c>
       <c r="B81" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
+          <t>Клапан штуцерный проходной Ду 32 Ру 40</t>
         </is>
       </c>
       <c r="C81" s="32" t="inlineStr">
         <is>
-          <t>УН522-3М38</t>
+          <t>521.3м.660</t>
         </is>
       </c>
       <c r="D81" s="32" t="n">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="E81" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F81" s="32" t="inlineStr">
@@ -10698,25 +10698,25 @@
         </is>
       </c>
       <c r="G81" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H81" s="32" t="n">
-        <v>9.5</v>
+        <v>3.3</v>
       </c>
       <c r="I81" s="34" t="n">
-        <v>14000</v>
+        <v>9600</v>
       </c>
       <c r="J81" s="34" t="n">
-        <v>28000</v>
+        <v>28800</v>
       </c>
       <c r="K81" s="34" t="n">
-        <v>14000</v>
+        <v>12500</v>
       </c>
       <c r="L81" s="34" t="n">
-        <v>28000</v>
+        <v>37500</v>
       </c>
       <c r="M81" s="35" t="n">
-        <v>1</v>
+        <v>0.77</v>
       </c>
       <c r="N81" s="37" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="O81" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -10735,20 +10735,20 @@
       </c>
       <c r="B82" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Р160</t>
+          <t>Клапан фланцевый проходной ДУ32 Ру25</t>
         </is>
       </c>
       <c r="C82" s="32" t="inlineStr">
         <is>
-          <t>522-03.149</t>
+          <t>УН522-3М38</t>
         </is>
       </c>
       <c r="D82" s="32" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E82" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F82" s="32" t="inlineStr">
@@ -10757,25 +10757,25 @@
         </is>
       </c>
       <c r="G82" s="34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H82" s="32" t="n">
-        <v>0.7</v>
+        <v>9.5</v>
       </c>
       <c r="I82" s="34" t="n">
-        <v>4500</v>
+        <v>14000</v>
       </c>
       <c r="J82" s="34" t="n">
-        <v>27000</v>
+        <v>28000</v>
       </c>
       <c r="K82" s="34" t="n">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="L82" s="34" t="n">
-        <v>18000</v>
+        <v>28000</v>
       </c>
       <c r="M82" s="35" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N82" s="37" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
       </c>
       <c r="O82" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="C83" s="32" t="inlineStr">
         <is>
-          <t>522-03,149</t>
+          <t>522-03.149</t>
         </is>
       </c>
       <c r="D83" s="32" t="n">
@@ -10819,7 +10819,7 @@
         <v>6</v>
       </c>
       <c r="H83" s="32" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="I83" s="34" t="n">
         <v>4500</v>
@@ -10828,13 +10828,13 @@
         <v>27000</v>
       </c>
       <c r="K83" s="34" t="n">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="L83" s="34" t="n">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="M83" s="35" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="N83" s="37" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="O83" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -10853,16 +10853,20 @@
       </c>
       <c r="B84" s="33" t="inlineStr">
         <is>
-          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
-        </is>
-      </c>
-      <c r="C84" s="32" t="inlineStr"/>
+          <t>Клапан штуцерный угловой Ду10 Р160</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>522-03,149</t>
+        </is>
+      </c>
       <c r="D84" s="32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E84" s="32" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F84" s="32" t="inlineStr">
@@ -10871,25 +10875,25 @@
         </is>
       </c>
       <c r="G84" s="34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H84" s="32" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="I84" s="34" t="n">
-        <v>6500</v>
+        <v>4500</v>
       </c>
       <c r="J84" s="34" t="n">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="K84" s="34" t="n">
-        <v>7500</v>
+        <v>4000</v>
       </c>
       <c r="L84" s="34" t="n">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="M84" s="35" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="N84" s="37" t="inlineStr">
         <is>
@@ -10908,20 +10912,16 @@
       </c>
       <c r="B85" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
-        </is>
-      </c>
-      <c r="C85" s="32" t="inlineStr">
-        <is>
-          <t>595-01-010</t>
-        </is>
-      </c>
+          <t>Кран штуцерный спусковой самозапорный проходной Ду15 Ру25</t>
+        </is>
+      </c>
+      <c r="C85" s="32" t="inlineStr"/>
       <c r="D85" s="32" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E85" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="F85" s="32" t="inlineStr">
@@ -10930,20 +10930,26 @@
         </is>
       </c>
       <c r="G85" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H85" s="32" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="I85" s="34" t="n">
-        <v>12800</v>
+        <v>6500</v>
       </c>
       <c r="J85" s="34" t="n">
-        <v>25600</v>
-      </c>
-      <c r="K85" s="34" t="n"/>
-      <c r="L85" s="34" t="n"/>
-      <c r="M85" s="35" t="n"/>
+        <v>26000</v>
+      </c>
+      <c r="K85" s="34" t="n">
+        <v>7500</v>
+      </c>
+      <c r="L85" s="34" t="n">
+        <v>30000</v>
+      </c>
+      <c r="M85" s="35" t="n">
+        <v>0.87</v>
+      </c>
       <c r="N85" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -10951,7 +10957,7 @@
       </c>
       <c r="O85" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -10961,16 +10967,16 @@
       </c>
       <c r="B86" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду65 Ру40</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру16</t>
         </is>
       </c>
       <c r="C86" s="32" t="inlineStr">
         <is>
-          <t>521-03.230</t>
+          <t>595-01-010</t>
         </is>
       </c>
       <c r="D86" s="32" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E86" s="32" t="inlineStr">
         <is>
@@ -10983,16 +10989,16 @@
         </is>
       </c>
       <c r="G86" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" s="32" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="I86" s="34" t="n">
-        <v>25150</v>
+        <v>12800</v>
       </c>
       <c r="J86" s="34" t="n">
-        <v>25150</v>
+        <v>25600</v>
       </c>
       <c r="K86" s="34" t="n"/>
       <c r="L86" s="34" t="n"/>
@@ -11004,7 +11010,7 @@
       </c>
       <c r="O86" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -11014,20 +11020,20 @@
       </c>
       <c r="B87" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
+          <t>Клапан фланцевый угловой Ду65 Ру40</t>
         </is>
       </c>
       <c r="C87" s="32" t="inlineStr">
         <is>
-          <t>529-35.1400-01</t>
+          <t>521-03.230</t>
         </is>
       </c>
       <c r="D87" s="32" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E87" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F87" s="32" t="inlineStr">
@@ -11039,23 +11045,17 @@
         <v>1</v>
       </c>
       <c r="H87" s="32" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="I87" s="34" t="n">
-        <v>25000</v>
+        <v>25150</v>
       </c>
       <c r="J87" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="L87" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M87" s="35" t="n">
-        <v>1</v>
-      </c>
+        <v>25150</v>
+      </c>
+      <c r="K87" s="34" t="n"/>
+      <c r="L87" s="34" t="n"/>
+      <c r="M87" s="35" t="n"/>
       <c r="N87" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -11073,20 +11073,20 @@
       </c>
       <c r="B88" s="33" t="inlineStr">
         <is>
-          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду65 Ру6,3</t>
+          <t>Захлопка фланцевая вертикальная Ду50Ру63</t>
         </is>
       </c>
       <c r="C88" s="32" t="inlineStr">
         <is>
-          <t>521-03-022</t>
+          <t>529-35.1400-01</t>
         </is>
       </c>
       <c r="D88" s="32" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E88" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F88" s="32" t="inlineStr">
@@ -11098,22 +11098,22 @@
         <v>1</v>
       </c>
       <c r="H88" s="32" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="I88" s="34" t="n">
-        <v>24500</v>
+        <v>25000</v>
       </c>
       <c r="J88" s="34" t="n">
-        <v>24500</v>
+        <v>25000</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>35000</v>
+        <v>25000</v>
       </c>
       <c r="L88" s="34" t="n">
-        <v>35000</v>
+        <v>25000</v>
       </c>
       <c r="M88" s="35" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N88" s="37" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
       </c>
       <c r="O88" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -11132,12 +11132,12 @@
       </c>
       <c r="B89" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду65 Ру10</t>
+          <t>Клапан быстрозапор. фланц.проход.с тросиков.приводом Ду65 Ру6,3</t>
         </is>
       </c>
       <c r="C89" s="32" t="inlineStr">
         <is>
-          <t>521-03.488</t>
+          <t>521-03-022</t>
         </is>
       </c>
       <c r="D89" s="32" t="n">
@@ -11157,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="H89" s="32" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I89" s="34" t="n">
         <v>24500</v>
@@ -11166,13 +11166,13 @@
         <v>24500</v>
       </c>
       <c r="K89" s="34" t="n">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="L89" s="34" t="n">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="M89" s="35" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="N89" s="37" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="O89" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11191,10 +11191,14 @@
       </c>
       <c r="B90" s="33" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
-        </is>
-      </c>
-      <c r="C90" s="32" t="inlineStr"/>
+          <t>Клапан фланцевый проходной Ду65 Ру10</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>521-03.488</t>
+        </is>
+      </c>
       <c r="D90" s="32" t="n">
         <v>65</v>
       </c>
@@ -11221,13 +11225,13 @@
         <v>24500</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>18000</v>
+        <v>27000</v>
       </c>
       <c r="L90" s="34" t="n">
-        <v>18000</v>
+        <v>27000</v>
       </c>
       <c r="M90" s="35" t="n">
-        <v>1.36</v>
+        <v>0.91</v>
       </c>
       <c r="N90" s="37" t="inlineStr">
         <is>
@@ -11236,7 +11240,7 @@
       </c>
       <c r="O90" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11246,20 +11250,16 @@
       </c>
       <c r="B91" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду15 Ру160</t>
-        </is>
-      </c>
-      <c r="C91" s="32" t="inlineStr">
-        <is>
-          <t>521-03.387</t>
-        </is>
-      </c>
+          <t>Клапан проходной фланцевый Ду65 КОРПУС - БРАК</t>
+        </is>
+      </c>
+      <c r="C91" s="32" t="inlineStr"/>
       <c r="D91" s="32" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E91" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F91" s="32" t="inlineStr">
@@ -11268,20 +11268,26 @@
         </is>
       </c>
       <c r="G91" s="34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H91" s="32" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="I91" s="34" t="n">
-        <v>6000</v>
+        <v>24500</v>
       </c>
       <c r="J91" s="34" t="n">
-        <v>24000</v>
-      </c>
-      <c r="K91" s="34" t="n"/>
-      <c r="L91" s="34" t="n"/>
-      <c r="M91" s="35" t="n"/>
+        <v>24500</v>
+      </c>
+      <c r="K91" s="34" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L91" s="34" t="n">
+        <v>18000</v>
+      </c>
+      <c r="M91" s="35" t="n">
+        <v>1.36</v>
+      </c>
       <c r="N91" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -11289,7 +11295,7 @@
       </c>
       <c r="O91" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11330,7 @@
         <v>4</v>
       </c>
       <c r="H92" s="32" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="I92" s="34" t="n">
         <v>6000</v>
@@ -11332,15 +11338,9 @@
       <c r="J92" s="34" t="n">
         <v>24000</v>
       </c>
-      <c r="K92" s="34" t="n">
-        <v>9000</v>
-      </c>
-      <c r="L92" s="34" t="n">
-        <v>36000</v>
-      </c>
-      <c r="M92" s="35" t="n">
-        <v>0.67</v>
-      </c>
+      <c r="K92" s="34" t="n"/>
+      <c r="L92" s="34" t="n"/>
+      <c r="M92" s="35" t="n"/>
       <c r="N92" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="O92" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -11358,20 +11358,20 @@
       </c>
       <c r="B93" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Клапан штуцерный угловой Ду15 Ру160</t>
         </is>
       </c>
       <c r="C93" s="32" t="inlineStr">
         <is>
-          <t>536-3м 5</t>
+          <t>521-03.387</t>
         </is>
       </c>
       <c r="D93" s="32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E93" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F93" s="32" t="inlineStr">
@@ -11383,7 +11383,7 @@
         <v>4</v>
       </c>
       <c r="H93" s="32" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="I93" s="34" t="n">
         <v>6000</v>
@@ -11392,13 +11392,13 @@
         <v>24000</v>
       </c>
       <c r="K93" s="34" t="n">
-        <v>6500</v>
+        <v>9000</v>
       </c>
       <c r="L93" s="34" t="n">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="M93" s="35" t="n">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="N93" s="37" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="O93" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -11417,12 +11417,12 @@
       </c>
       <c r="B94" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="C94" s="32" t="inlineStr">
         <is>
-          <t>Без чертежа</t>
+          <t>536-3м 5</t>
         </is>
       </c>
       <c r="D94" s="32" t="n">
@@ -11451,13 +11451,13 @@
         <v>24000</v>
       </c>
       <c r="K94" s="34" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="L94" s="34" t="n">
-        <v>24000</v>
+        <v>26000</v>
       </c>
       <c r="M94" s="35" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="N94" s="37" t="inlineStr">
         <is>
@@ -11476,16 +11476,20 @@
       </c>
       <c r="B95" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
-        </is>
-      </c>
-      <c r="C95" s="32" t="inlineStr"/>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+        </is>
+      </c>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>Без чертежа</t>
+        </is>
+      </c>
       <c r="D95" s="32" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E95" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F95" s="32" t="inlineStr">
@@ -11494,26 +11498,26 @@
         </is>
       </c>
       <c r="G95" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="H95" s="32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I95" s="34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J95" s="34" t="n">
+        <v>24000</v>
+      </c>
+      <c r="K95" s="34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L95" s="34" t="n">
+        <v>24000</v>
+      </c>
+      <c r="M95" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H95" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I95" s="34" t="n">
-        <v>23000</v>
-      </c>
-      <c r="J95" s="34" t="n">
-        <v>23000</v>
-      </c>
-      <c r="K95" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="L95" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M95" s="35" t="n">
-        <v>0.92</v>
-      </c>
       <c r="N95" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -11521,7 +11525,7 @@
       </c>
       <c r="O95" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -11531,14 +11535,10 @@
       </c>
       <c r="B96" s="33" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
-        </is>
-      </c>
-      <c r="C96" s="32" t="inlineStr">
-        <is>
-          <t>595-01.002</t>
-        </is>
-      </c>
+          <t>Клапан фланцевый проходной невозвратный Ду 50 РУ 25 (522-01.164)</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="inlineStr"/>
       <c r="D96" s="32" t="n">
         <v>50</v>
       </c>
@@ -11556,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I96" s="34" t="n">
         <v>23000</v>
@@ -11565,13 +11565,13 @@
         <v>23000</v>
       </c>
       <c r="K96" s="34" t="n">
-        <v>22500</v>
+        <v>25000</v>
       </c>
       <c r="L96" s="34" t="n">
-        <v>22500</v>
+        <v>25000</v>
       </c>
       <c r="M96" s="35" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="N96" s="37" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="O96" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -11590,12 +11590,12 @@
       </c>
       <c r="B97" s="33" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
+          <t>Клапан Пожарный фланцевый проходной Ду50 Ру16</t>
         </is>
       </c>
       <c r="C97" s="32" t="inlineStr">
         <is>
-          <t>без чертежа(527-35.1165)</t>
+          <t>595-01.002</t>
         </is>
       </c>
       <c r="D97" s="32" t="n">
@@ -11603,7 +11603,7 @@
       </c>
       <c r="E97" s="32" t="inlineStr">
         <is>
-          <t>Кингстоны</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F97" s="32" t="inlineStr">
@@ -11615,17 +11615,23 @@
         <v>1</v>
       </c>
       <c r="H97" s="32" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I97" s="34" t="n">
+        <v>23000</v>
+      </c>
+      <c r="J97" s="34" t="n">
+        <v>23000</v>
+      </c>
+      <c r="K97" s="34" t="n">
         <v>22500</v>
       </c>
-      <c r="J97" s="34" t="n">
+      <c r="L97" s="34" t="n">
         <v>22500</v>
       </c>
-      <c r="K97" s="34" t="n"/>
-      <c r="L97" s="34" t="n"/>
-      <c r="M97" s="35" t="n"/>
+      <c r="M97" s="35" t="n">
+        <v>1.02</v>
+      </c>
       <c r="N97" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -11633,7 +11639,7 @@
       </c>
       <c r="O97" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -11643,20 +11649,20 @@
       </c>
       <c r="B98" s="33" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+          <t>Кингстон донный фланцевый Ду50 Ру2,5</t>
         </is>
       </c>
       <c r="C98" s="32" t="inlineStr">
         <is>
-          <t>536-35.696</t>
+          <t>без чертежа(527-35.1165)</t>
         </is>
       </c>
       <c r="D98" s="32" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E98" s="32" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="F98" s="32" t="inlineStr">
@@ -11665,26 +11671,20 @@
         </is>
       </c>
       <c r="G98" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" s="32" t="n">
-        <v>4.1</v>
+        <v>9.4</v>
       </c>
       <c r="I98" s="34" t="n">
-        <v>10800</v>
+        <v>22500</v>
       </c>
       <c r="J98" s="34" t="n">
-        <v>21600</v>
-      </c>
-      <c r="K98" s="34" t="n">
-        <v>6500</v>
-      </c>
-      <c r="L98" s="34" t="n">
-        <v>13000</v>
-      </c>
-      <c r="M98" s="35" t="n">
-        <v>1.66</v>
-      </c>
+        <v>22500</v>
+      </c>
+      <c r="K98" s="34" t="n"/>
+      <c r="L98" s="34" t="n"/>
+      <c r="M98" s="35" t="n"/>
       <c r="N98" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="O98" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -11702,16 +11702,20 @@
       </c>
       <c r="B99" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
-        </is>
-      </c>
-      <c r="C99" s="32" t="inlineStr"/>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="inlineStr">
+        <is>
+          <t>536-35.696</t>
+        </is>
+      </c>
       <c r="D99" s="32" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E99" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="F99" s="32" t="inlineStr">
@@ -11720,20 +11724,26 @@
         </is>
       </c>
       <c r="G99" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H99" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="I99" s="34" t="n">
-        <v>20000</v>
+        <v>10800</v>
       </c>
       <c r="J99" s="34" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K99" s="34" t="n"/>
-      <c r="L99" s="34" t="n"/>
-      <c r="M99" s="35" t="n"/>
+        <v>21600</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>6500</v>
+      </c>
+      <c r="L99" s="34" t="n">
+        <v>13000</v>
+      </c>
+      <c r="M99" s="35" t="n">
+        <v>1.66</v>
+      </c>
       <c r="N99" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -11741,7 +11751,7 @@
       </c>
       <c r="O99" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -11751,16 +11761,12 @@
       </c>
       <c r="B100" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25</t>
-        </is>
-      </c>
-      <c r="C100" s="32" t="inlineStr">
-        <is>
-          <t>521-01.200</t>
-        </is>
-      </c>
+          <t>Клапан фланц. концевой пожарный угловой Ду50</t>
+        </is>
+      </c>
+      <c r="C100" s="32" t="inlineStr"/>
       <c r="D100" s="32" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E100" s="32" t="inlineStr">
         <is>
@@ -11776,7 +11782,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="32" t="n">
-        <v>5.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I100" s="34" t="n">
         <v>20000</v>
@@ -11784,15 +11790,9 @@
       <c r="J100" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="K100" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L100" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="M100" s="35" t="n">
-        <v>1.11</v>
-      </c>
+      <c r="K100" s="34" t="n"/>
+      <c r="L100" s="34" t="n"/>
+      <c r="M100" s="35" t="n"/>
       <c r="N100" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -11800,7 +11800,7 @@
       </c>
       <c r="O100" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -11810,16 +11810,16 @@
       </c>
       <c r="B101" s="33" t="inlineStr">
         <is>
-          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25</t>
         </is>
       </c>
       <c r="C101" s="32" t="inlineStr">
         <is>
-          <t>595-03.008</t>
+          <t>521-01.200</t>
         </is>
       </c>
       <c r="D101" s="32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E101" s="32" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="32" t="n">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="I101" s="34" t="n">
         <v>20000</v>
@@ -11844,13 +11844,13 @@
         <v>20000</v>
       </c>
       <c r="K101" s="34" t="n">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="L101" s="34" t="n">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="M101" s="35" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="N101" s="37" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="O101" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -11869,12 +11869,12 @@
       </c>
       <c r="B102" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
+          <t>Клапан Пожарный фланцевый угловой Ду50 Ру16</t>
         </is>
       </c>
       <c r="C102" s="32" t="inlineStr">
         <is>
-          <t>595-3М-48</t>
+          <t>595-03.008</t>
         </is>
       </c>
       <c r="D102" s="32" t="n">
@@ -11902,9 +11902,15 @@
       <c r="J102" s="34" t="n">
         <v>20000</v>
       </c>
-      <c r="K102" s="34" t="n"/>
-      <c r="L102" s="34" t="n"/>
-      <c r="M102" s="35" t="n"/>
+      <c r="K102" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L102" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M102" s="35" t="n">
+        <v>0.8</v>
+      </c>
       <c r="N102" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -11912,7 +11918,7 @@
       </c>
       <c r="O102" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -11927,7 +11933,7 @@
       </c>
       <c r="C103" s="32" t="inlineStr">
         <is>
-          <t>595-35-021</t>
+          <t>595-3М-48</t>
         </is>
       </c>
       <c r="D103" s="32" t="n">
@@ -11975,20 +11981,20 @@
       </c>
       <c r="B104" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый  Ду15/1</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду50 Ру25</t>
         </is>
       </c>
       <c r="C104" s="32" t="inlineStr">
         <is>
-          <t>521-35.2608-01</t>
+          <t>595-35-021</t>
         </is>
       </c>
       <c r="D104" s="32" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E104" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F104" s="32" t="inlineStr">
@@ -11997,16 +12003,16 @@
         </is>
       </c>
       <c r="G104" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H104" s="32" t="n">
-        <v>5.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I104" s="34" t="n">
-        <v>6500</v>
+        <v>20000</v>
       </c>
       <c r="J104" s="34" t="n">
-        <v>19500</v>
+        <v>20000</v>
       </c>
       <c r="K104" s="34" t="n"/>
       <c r="L104" s="34" t="n"/>
@@ -12018,7 +12024,7 @@
       </c>
       <c r="O104" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12034,7 @@
       </c>
       <c r="B105" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+          <t>Клапан штуцерный проходной бессальниковый  Ду15/1</t>
         </is>
       </c>
       <c r="C105" s="32" t="inlineStr">
@@ -12053,7 +12059,7 @@
         <v>3</v>
       </c>
       <c r="H105" s="32" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="I105" s="34" t="n">
         <v>6500</v>
@@ -12071,7 +12077,7 @@
       </c>
       <c r="O105" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -12081,44 +12087,42 @@
       </c>
       <c r="B106" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная ДУ 80, сталь</t>
-        </is>
-      </c>
-      <c r="C106" s="32" t="inlineStr"/>
+          <t>Клапан штуцерный проходной бессальниковый Ду15/1</t>
+        </is>
+      </c>
+      <c r="C106" s="32" t="inlineStr">
+        <is>
+          <t>521-35.2608-01</t>
+        </is>
+      </c>
       <c r="D106" s="32" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="E106" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F106" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G106" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H106" s="32" t="n">
-        <v>11.7</v>
+        <v>2.6</v>
       </c>
       <c r="I106" s="34" t="n">
-        <v>19000</v>
+        <v>6500</v>
       </c>
       <c r="J106" s="34" t="n">
-        <v>19000</v>
-      </c>
-      <c r="K106" s="34" t="n">
-        <v>22000</v>
-      </c>
-      <c r="L106" s="34" t="n">
-        <v>22000</v>
-      </c>
-      <c r="M106" s="35" t="n">
-        <v>0.86</v>
-      </c>
+        <v>19500</v>
+      </c>
+      <c r="K106" s="34" t="n"/>
+      <c r="L106" s="34" t="n"/>
+      <c r="M106" s="35" t="n"/>
       <c r="N106" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -12126,7 +12130,7 @@
       </c>
       <c r="O106" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -12136,47 +12140,43 @@
       </c>
       <c r="B107" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
-        </is>
-      </c>
-      <c r="C107" s="32" t="inlineStr">
-        <is>
-          <t>522 3м 13</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная ДУ 80, сталь</t>
+        </is>
+      </c>
+      <c r="C107" s="32" t="inlineStr"/>
       <c r="D107" s="32" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E107" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F107" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G107" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H107" s="32" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="I107" s="34" t="n">
-        <v>6000</v>
+        <v>19000</v>
       </c>
       <c r="J107" s="34" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="K107" s="34" t="n">
-        <v>6000</v>
+        <v>22000</v>
       </c>
       <c r="L107" s="34" t="n">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="M107" s="35" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="N107" s="37" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
       </c>
       <c r="O107" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -12195,12 +12195,12 @@
       </c>
       <c r="B108" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C108" s="32" t="inlineStr">
         <is>
-          <t>521-01464-02</t>
+          <t>522 3м 13</t>
         </is>
       </c>
       <c r="D108" s="32" t="n">
@@ -12254,16 +12254,16 @@
       </c>
       <c r="B109" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C109" s="32" t="inlineStr">
         <is>
-          <t>522-01-493</t>
+          <t>521-01464-02</t>
         </is>
       </c>
       <c r="D109" s="32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E109" s="32" t="inlineStr">
         <is>
@@ -12276,25 +12276,25 @@
         </is>
       </c>
       <c r="G109" s="34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H109" s="32" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="I109" s="34" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="J109" s="34" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="K109" s="34" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="L109" s="34" t="n">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="M109" s="35" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N109" s="37" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
       </c>
       <c r="O109" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12313,16 +12313,16 @@
       </c>
       <c r="B110" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
       <c r="C110" s="32" t="inlineStr">
         <is>
-          <t>521. 3м.666</t>
+          <t>522-01-493</t>
         </is>
       </c>
       <c r="D110" s="32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E110" s="32" t="inlineStr">
         <is>
@@ -12335,25 +12335,25 @@
         </is>
       </c>
       <c r="G110" s="34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H110" s="32" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="I110" s="34" t="n">
-        <v>6500</v>
+        <v>3000</v>
       </c>
       <c r="J110" s="34" t="n">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="K110" s="34" t="n">
-        <v>6500</v>
+        <v>4000</v>
       </c>
       <c r="L110" s="34" t="n">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="M110" s="35" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N110" s="37" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="O110" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -12372,12 +12372,12 @@
       </c>
       <c r="B111" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
       <c r="C111" s="32" t="inlineStr">
         <is>
-          <t>522-01.498</t>
+          <t>521. 3м.666</t>
         </is>
       </c>
       <c r="D111" s="32" t="n">
@@ -12431,20 +12431,20 @@
       </c>
       <c r="B112" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 100</t>
         </is>
       </c>
       <c r="C112" s="32" t="inlineStr">
         <is>
-          <t>595-03-006</t>
+          <t>522-01.498</t>
         </is>
       </c>
       <c r="D112" s="32" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E112" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F112" s="32" t="inlineStr">
@@ -12453,20 +12453,26 @@
         </is>
       </c>
       <c r="G112" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I112" s="34" t="n">
+        <v>6500</v>
+      </c>
+      <c r="J112" s="34" t="n">
+        <v>13000</v>
+      </c>
+      <c r="K112" s="34" t="n">
+        <v>6500</v>
+      </c>
+      <c r="L112" s="34" t="n">
+        <v>13000</v>
+      </c>
+      <c r="M112" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="H112" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I112" s="34" t="n">
-        <v>12800</v>
-      </c>
-      <c r="J112" s="34" t="n">
-        <v>12800</v>
-      </c>
-      <c r="K112" s="34" t="n"/>
-      <c r="L112" s="34" t="n"/>
-      <c r="M112" s="35" t="n"/>
       <c r="N112" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -12474,7 +12480,7 @@
       </c>
       <c r="O112" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12484,10 +12490,14 @@
       </c>
       <c r="B113" s="33" t="inlineStr">
         <is>
-          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
-        </is>
-      </c>
-      <c r="C113" s="32" t="inlineStr"/>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
+        </is>
+      </c>
+      <c r="C113" s="32" t="inlineStr">
+        <is>
+          <t>595-03-006</t>
+        </is>
+      </c>
       <c r="D113" s="32" t="n">
         <v>32</v>
       </c>
@@ -12505,7 +12515,7 @@
         <v>1</v>
       </c>
       <c r="H113" s="32" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="I113" s="34" t="n">
         <v>12800</v>
@@ -12513,15 +12523,9 @@
       <c r="J113" s="34" t="n">
         <v>12800</v>
       </c>
-      <c r="K113" s="34" t="n">
-        <v>9600</v>
-      </c>
-      <c r="L113" s="34" t="n">
-        <v>9600</v>
-      </c>
-      <c r="M113" s="35" t="n">
-        <v>1.33</v>
-      </c>
+      <c r="K113" s="34" t="n"/>
+      <c r="L113" s="34" t="n"/>
+      <c r="M113" s="35" t="n"/>
       <c r="N113" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -12529,7 +12533,7 @@
       </c>
       <c r="O113" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -12539,14 +12543,10 @@
       </c>
       <c r="B114" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
-        </is>
-      </c>
-      <c r="C114" s="32" t="inlineStr">
-        <is>
-          <t>595-03-006</t>
-        </is>
-      </c>
+          <t>Клапан предохранит. фланцевый угловой Ду32Ру4 (524-03.090)</t>
+        </is>
+      </c>
+      <c r="C114" s="32" t="inlineStr"/>
       <c r="D114" s="32" t="n">
         <v>32</v>
       </c>
@@ -12564,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="H114" s="32" t="n">
-        <v>5.6</v>
+        <v>9.5</v>
       </c>
       <c r="I114" s="34" t="n">
         <v>12800</v>
@@ -12572,9 +12572,15 @@
       <c r="J114" s="34" t="n">
         <v>12800</v>
       </c>
-      <c r="K114" s="34" t="n"/>
-      <c r="L114" s="34" t="n"/>
-      <c r="M114" s="35" t="n"/>
+      <c r="K114" s="34" t="n">
+        <v>9600</v>
+      </c>
+      <c r="L114" s="34" t="n">
+        <v>9600</v>
+      </c>
+      <c r="M114" s="35" t="n">
+        <v>1.33</v>
+      </c>
       <c r="N114" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -12582,7 +12588,7 @@
       </c>
       <c r="O114" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -12592,20 +12598,20 @@
       </c>
       <c r="B115" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запор.цапковый угловой  под дюрит Ду20Ру6</t>
+          <t>Клапан фланц. концевой пожарный угловой Ду32 Ру10</t>
         </is>
       </c>
       <c r="C115" s="32" t="inlineStr">
         <is>
-          <t>522-03.123</t>
+          <t>595-03-006</t>
         </is>
       </c>
       <c r="D115" s="32" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E115" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F115" s="32" t="inlineStr">
@@ -12614,26 +12620,20 @@
         </is>
       </c>
       <c r="G115" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115" s="32" t="n">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
       <c r="I115" s="34" t="n">
-        <v>6000</v>
+        <v>12800</v>
       </c>
       <c r="J115" s="34" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K115" s="34" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L115" s="34" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M115" s="35" t="n">
-        <v>0.6</v>
-      </c>
+        <v>12800</v>
+      </c>
+      <c r="K115" s="34" t="n"/>
+      <c r="L115" s="34" t="n"/>
+      <c r="M115" s="35" t="n"/>
       <c r="N115" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="O115" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -12651,12 +12651,12 @@
       </c>
       <c r="B116" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан невозв-запор.цапковый угловой  под дюрит Ду20Ру6</t>
         </is>
       </c>
       <c r="C116" s="32" t="inlineStr">
         <is>
-          <t>521 3м 726</t>
+          <t>522-03.123</t>
         </is>
       </c>
       <c r="D116" s="32" t="n">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="E116" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F116" s="32" t="inlineStr">
@@ -12676,7 +12676,7 @@
         <v>2</v>
       </c>
       <c r="H116" s="32" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I116" s="34" t="n">
         <v>6000</v>
@@ -12685,13 +12685,13 @@
         <v>12000</v>
       </c>
       <c r="K116" s="34" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="L116" s="34" t="n">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="M116" s="35" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="N116" s="37" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="O116" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -12710,12 +12710,12 @@
       </c>
       <c r="B117" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C117" s="32" t="inlineStr">
         <is>
-          <t>522-03.123</t>
+          <t>521 3м 726</t>
         </is>
       </c>
       <c r="D117" s="32" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="E117" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F117" s="32" t="inlineStr">
@@ -12744,13 +12744,13 @@
         <v>12000</v>
       </c>
       <c r="K117" s="34" t="n">
-        <v>4800</v>
+        <v>6000</v>
       </c>
       <c r="L117" s="34" t="n">
-        <v>9600</v>
+        <v>12000</v>
       </c>
       <c r="M117" s="35" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="N117" s="37" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="O117" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -12769,20 +12769,20 @@
       </c>
       <c r="B118" s="33" t="inlineStr">
         <is>
-          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
+          <t>Клапан невозв-запор.цапковый угловой под дюрит Ду20Ру6</t>
         </is>
       </c>
       <c r="C118" s="32" t="inlineStr">
         <is>
-          <t>536-35.696</t>
+          <t>522-03.123</t>
         </is>
       </c>
       <c r="D118" s="32" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E118" s="32" t="inlineStr">
         <is>
-          <t>Краны</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F118" s="32" t="inlineStr">
@@ -12791,20 +12791,26 @@
         </is>
       </c>
       <c r="G118" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H118" s="32" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="I118" s="34" t="n">
-        <v>10800</v>
+        <v>6000</v>
       </c>
       <c r="J118" s="34" t="n">
-        <v>10800</v>
-      </c>
-      <c r="K118" s="34" t="n"/>
-      <c r="L118" s="34" t="n"/>
-      <c r="M118" s="35" t="n"/>
+        <v>12000</v>
+      </c>
+      <c r="K118" s="34" t="n">
+        <v>4800</v>
+      </c>
+      <c r="L118" s="34" t="n">
+        <v>9600</v>
+      </c>
+      <c r="M118" s="35" t="n">
+        <v>1.25</v>
+      </c>
       <c r="N118" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -12812,7 +12818,7 @@
       </c>
       <c r="O118" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -12822,20 +12828,20 @@
       </c>
       <c r="B119" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25 Ру 100</t>
+          <t>Кран трехходовой штуцерный Ду32 Ру10</t>
         </is>
       </c>
       <c r="C119" s="32" t="inlineStr">
         <is>
-          <t>521--35.3363</t>
+          <t>536-35.696</t>
         </is>
       </c>
       <c r="D119" s="32" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E119" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Краны</t>
         </is>
       </c>
       <c r="F119" s="32" t="inlineStr">
@@ -12847,23 +12853,17 @@
         <v>1</v>
       </c>
       <c r="H119" s="32" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="I119" s="34" t="n">
-        <v>10000</v>
+        <v>10800</v>
       </c>
       <c r="J119" s="34" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K119" s="34" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L119" s="34" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M119" s="35" t="n">
-        <v>2</v>
-      </c>
+        <v>10800</v>
+      </c>
+      <c r="K119" s="34" t="n"/>
+      <c r="L119" s="34" t="n"/>
+      <c r="M119" s="35" t="n"/>
       <c r="N119" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -12881,12 +12881,12 @@
       </c>
       <c r="B120" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду25</t>
+          <t>Клапан штуцерный угловой Ду25 Ру 100</t>
         </is>
       </c>
       <c r="C120" s="32" t="inlineStr">
         <is>
-          <t>521--01.468-08</t>
+          <t>521--35.3363</t>
         </is>
       </c>
       <c r="D120" s="32" t="n">
@@ -12906,7 +12906,7 @@
         <v>1</v>
       </c>
       <c r="H120" s="32" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="I120" s="34" t="n">
         <v>10000</v>
@@ -12915,13 +12915,13 @@
         <v>10000</v>
       </c>
       <c r="K120" s="34" t="n">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="L120" s="34" t="n">
-        <v>7500</v>
+        <v>5000</v>
       </c>
       <c r="M120" s="35" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="N120" s="37" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="O120" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="C121" s="32" t="inlineStr">
         <is>
-          <t>521--35.3363</t>
+          <t>521--01.468-08</t>
         </is>
       </c>
       <c r="D121" s="32" t="n">
@@ -12999,12 +12999,12 @@
       </c>
       <c r="B122" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ25 ???</t>
+          <t>Клапан штуцерный угловой Ду25</t>
         </is>
       </c>
       <c r="C122" s="32" t="inlineStr">
         <is>
-          <t>с камчатки</t>
+          <t>521--35.3363</t>
         </is>
       </c>
       <c r="D122" s="32" t="n">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="E122" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F122" s="32" t="inlineStr">
@@ -13024,7 +13024,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="32" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="I122" s="34" t="n">
         <v>10000</v>
@@ -13033,13 +13033,13 @@
         <v>10000</v>
       </c>
       <c r="K122" s="34" t="n">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="L122" s="34" t="n">
-        <v>12000</v>
+        <v>7500</v>
       </c>
       <c r="M122" s="35" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="N122" s="37" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="O122" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -13058,16 +13058,20 @@
       </c>
       <c r="B123" s="33" t="inlineStr">
         <is>
-          <t>Сетка на фильтр Ду20 маленькая</t>
-        </is>
-      </c>
-      <c r="C123" s="32" t="inlineStr"/>
+          <t>Клапан фланцевый проходной ДУ25 ???</t>
+        </is>
+      </c>
+      <c r="C123" s="32" t="inlineStr">
+        <is>
+          <t>с камчатки</t>
+        </is>
+      </c>
       <c r="D123" s="32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E123" s="32" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F123" s="32" t="inlineStr">
@@ -13079,22 +13083,22 @@
         <v>1</v>
       </c>
       <c r="H123" s="32" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="I123" s="34" t="n">
-        <v>9600</v>
+        <v>10000</v>
       </c>
       <c r="J123" s="34" t="n">
-        <v>9600</v>
+        <v>10000</v>
       </c>
       <c r="K123" s="34" t="n">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="L123" s="34" t="n">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="M123" s="35" t="n">
-        <v>3.2</v>
+        <v>0.83</v>
       </c>
       <c r="N123" s="37" t="inlineStr">
         <is>
@@ -13103,7 +13107,7 @@
       </c>
       <c r="O123" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -13113,32 +13117,28 @@
       </c>
       <c r="B124" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
-        </is>
-      </c>
-      <c r="C124" s="32" t="inlineStr">
-        <is>
-          <t>521-01.068</t>
-        </is>
-      </c>
+          <t>Сетка на фильтр Ду20 маленькая</t>
+        </is>
+      </c>
+      <c r="C124" s="32" t="inlineStr"/>
       <c r="D124" s="32" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E124" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="F124" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G124" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H124" s="32" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="I124" s="34" t="n">
         <v>9600</v>
@@ -13147,13 +13147,13 @@
         <v>9600</v>
       </c>
       <c r="K124" s="34" t="n">
-        <v>9600</v>
+        <v>3000</v>
       </c>
       <c r="L124" s="34" t="n">
-        <v>9600</v>
+        <v>3000</v>
       </c>
       <c r="M124" s="35" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="N124" s="37" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="O124" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -13172,28 +13172,32 @@
       </c>
       <c r="B125" s="33" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
-        </is>
-      </c>
-      <c r="C125" s="32" t="inlineStr"/>
+          <t>Клапан фланцевый проходной ДУ32 Ру25 (сталь)</t>
+        </is>
+      </c>
+      <c r="C125" s="32" t="inlineStr">
+        <is>
+          <t>521-01.068</t>
+        </is>
+      </c>
       <c r="D125" s="32" t="n">
         <v>32</v>
       </c>
       <c r="E125" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F125" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G125" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H125" s="32" t="n">
-        <v>3.3</v>
+        <v>9.5</v>
       </c>
       <c r="I125" s="34" t="n">
         <v>9600</v>
@@ -13202,13 +13206,13 @@
         <v>9600</v>
       </c>
       <c r="K125" s="34" t="n">
-        <v>1500</v>
+        <v>9600</v>
       </c>
       <c r="L125" s="34" t="n">
-        <v>1500</v>
+        <v>9600</v>
       </c>
       <c r="M125" s="35" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="N125" s="37" t="inlineStr">
         <is>
@@ -13217,7 +13221,7 @@
       </c>
       <c r="O125" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -13227,16 +13231,12 @@
       </c>
       <c r="B126" s="33" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
-        </is>
-      </c>
-      <c r="C126" s="32" t="inlineStr">
-        <is>
-          <t>528-35.176</t>
-        </is>
-      </c>
+          <t>Клапан муфтовый проходной запорный Ду32Ру10</t>
+        </is>
+      </c>
+      <c r="C126" s="32" t="inlineStr"/>
       <c r="D126" s="32" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E126" s="32" t="inlineStr">
         <is>
@@ -13252,22 +13252,22 @@
         <v>1</v>
       </c>
       <c r="H126" s="32" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="I126" s="34" t="n">
-        <v>6500</v>
+        <v>9600</v>
       </c>
       <c r="J126" s="34" t="n">
-        <v>6500</v>
+        <v>9600</v>
       </c>
       <c r="K126" s="34" t="n">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="L126" s="34" t="n">
-        <v>4000</v>
+        <v>1500</v>
       </c>
       <c r="M126" s="35" t="n">
-        <v>1.62</v>
+        <v>6.4</v>
       </c>
       <c r="N126" s="37" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="O126" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="B127" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
         </is>
       </c>
       <c r="C127" s="32" t="inlineStr">
         <is>
-          <t>522-01.501-01</t>
+          <t>528-35.176</t>
         </is>
       </c>
       <c r="D127" s="32" t="n">
@@ -13311,7 +13311,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="32" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="I127" s="34" t="n">
         <v>6500</v>
@@ -13320,13 +13320,13 @@
         <v>6500</v>
       </c>
       <c r="K127" s="34" t="n">
-        <v>6500</v>
+        <v>4000</v>
       </c>
       <c r="L127" s="34" t="n">
-        <v>6500</v>
+        <v>4000</v>
       </c>
       <c r="M127" s="35" t="n">
-        <v>1</v>
+        <v>1.62</v>
       </c>
       <c r="N127" s="37" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="O127" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -13345,12 +13345,12 @@
       </c>
       <c r="B128" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру40</t>
         </is>
       </c>
       <c r="C128" s="32" t="inlineStr">
         <is>
-          <t>521-01.470.02</t>
+          <t>522-01.501-01</t>
         </is>
       </c>
       <c r="D128" s="32" t="n">
@@ -13404,12 +13404,12 @@
       </c>
       <c r="B129" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 15</t>
+          <t>Клапан штуцерный проходной Ду 15 Ру 40</t>
         </is>
       </c>
       <c r="C129" s="32" t="inlineStr">
         <is>
-          <t>521 3м.770</t>
+          <t>521-01.470.02</t>
         </is>
       </c>
       <c r="D129" s="32" t="n">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="C130" s="32" t="inlineStr">
         <is>
-          <t>без чертежа</t>
+          <t>521 3м.770</t>
         </is>
       </c>
       <c r="D130" s="32" t="n">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="B131" s="33" t="inlineStr">
         <is>
-          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
+          <t>Клапан штуцерный проходной Ду 15</t>
         </is>
       </c>
       <c r="C131" s="32" t="inlineStr">
         <is>
-          <t>528-35.176</t>
+          <t>без чертежа</t>
         </is>
       </c>
       <c r="D131" s="32" t="n">
@@ -13555,9 +13555,15 @@
       <c r="J131" s="34" t="n">
         <v>6500</v>
       </c>
-      <c r="K131" s="34" t="n"/>
-      <c r="L131" s="34" t="n"/>
-      <c r="M131" s="35" t="n"/>
+      <c r="K131" s="34" t="n">
+        <v>6500</v>
+      </c>
+      <c r="L131" s="34" t="n">
+        <v>6500</v>
+      </c>
+      <c r="M131" s="35" t="n">
+        <v>1</v>
+      </c>
       <c r="N131" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -13565,7 +13571,7 @@
       </c>
       <c r="O131" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -13575,12 +13581,12 @@
       </c>
       <c r="B132" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду 15</t>
+          <t>(Кнопка)Клапан самозакрывающий проходной муфтовый Ду15Ру3</t>
         </is>
       </c>
       <c r="C132" s="32" t="inlineStr">
         <is>
-          <t>521--01.468-08</t>
+          <t>528-35.176</t>
         </is>
       </c>
       <c r="D132" s="32" t="n">
@@ -13588,7 +13594,7 @@
       </c>
       <c r="E132" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F132" s="32" t="inlineStr">
@@ -13600,23 +13606,17 @@
         <v>1</v>
       </c>
       <c r="H132" s="32" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="I132" s="34" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="J132" s="34" t="n">
-        <v>6000</v>
-      </c>
-      <c r="K132" s="34" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L132" s="34" t="n">
-        <v>5000</v>
-      </c>
-      <c r="M132" s="35" t="n">
-        <v>1.2</v>
-      </c>
+        <v>6500</v>
+      </c>
+      <c r="K132" s="34" t="n"/>
+      <c r="L132" s="34" t="n"/>
+      <c r="M132" s="35" t="n"/>
       <c r="N132" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -13624,7 +13624,7 @@
       </c>
       <c r="O132" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -13634,20 +13634,20 @@
       </c>
       <c r="B133" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20</t>
+          <t>Клапан штуцерный угловой Ду 15</t>
         </is>
       </c>
       <c r="C133" s="32" t="inlineStr">
         <is>
-          <t>536 3м .333</t>
+          <t>521--01.468-08</t>
         </is>
       </c>
       <c r="D133" s="32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E133" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F133" s="32" t="inlineStr">
@@ -13659,7 +13659,7 @@
         <v>1</v>
       </c>
       <c r="H133" s="32" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="I133" s="34" t="n">
         <v>6000</v>
@@ -13668,13 +13668,13 @@
         <v>6000</v>
       </c>
       <c r="K133" s="34" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="L133" s="34" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="M133" s="35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N133" s="37" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
       </c>
       <c r="O133" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -13693,12 +13693,12 @@
       </c>
       <c r="B134" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 20</t>
         </is>
       </c>
       <c r="C134" s="32" t="inlineStr">
         <is>
-          <t>521 3м 30</t>
+          <t>536 3м .333</t>
         </is>
       </c>
       <c r="D134" s="32" t="n">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="B135" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 40</t>
         </is>
       </c>
       <c r="C135" s="32" t="inlineStr">
         <is>
-          <t>522-35 240</t>
+          <t>521 3м 30</t>
         </is>
       </c>
       <c r="D135" s="32" t="n">
@@ -13811,12 +13811,12 @@
       </c>
       <c r="B136" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 64</t>
         </is>
       </c>
       <c r="C136" s="32" t="inlineStr">
         <is>
-          <t>522-01.498.-03</t>
+          <t>522-35 240</t>
         </is>
       </c>
       <c r="D136" s="32" t="n">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="C137" s="32" t="inlineStr">
         <is>
-          <t>425-322710</t>
+          <t>522-01.498.-03</t>
         </is>
       </c>
       <c r="D137" s="32" t="n">
@@ -13929,16 +13929,16 @@
       </c>
       <c r="B138" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
+          <t>Клапан штуцерный проходной Ду 20 Ру 100</t>
         </is>
       </c>
       <c r="C138" s="32" t="inlineStr">
         <is>
-          <t>521-03.420</t>
+          <t>425-322710</t>
         </is>
       </c>
       <c r="D138" s="32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E138" s="32" t="inlineStr">
         <is>
@@ -13951,13 +13951,13 @@
         </is>
       </c>
       <c r="G138" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H138" s="32" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="I138" s="34" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="J138" s="34" t="n">
         <v>6000</v>
@@ -13966,10 +13966,10 @@
         <v>6000</v>
       </c>
       <c r="L138" s="34" t="n">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="M138" s="35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N138" s="37" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="O138" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -13988,20 +13988,20 @@
       </c>
       <c r="B139" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду20 ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру400</t>
         </is>
       </c>
       <c r="C139" s="32" t="inlineStr">
         <is>
-          <t>521-01.465-03</t>
+          <t>521-03.420</t>
         </is>
       </c>
       <c r="D139" s="32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E139" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F139" s="32" t="inlineStr">
@@ -14010,25 +14010,25 @@
         </is>
       </c>
       <c r="G139" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H139" s="32" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="I139" s="34" t="n">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="J139" s="34" t="n">
         <v>6000</v>
       </c>
       <c r="K139" s="34" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="L139" s="34" t="n">
-        <v>4500</v>
+        <v>12000</v>
       </c>
       <c r="M139" s="35" t="n">
-        <v>1.33</v>
+        <v>0.5</v>
       </c>
       <c r="N139" s="37" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="O139" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -14047,12 +14047,12 @@
       </c>
       <c r="B140" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
+          <t>Клапан штуцерный угловой Ду20 ру 40</t>
         </is>
       </c>
       <c r="C140" s="32" t="inlineStr">
         <is>
-          <t>522-3м-9</t>
+          <t>521-01.465-03</t>
         </is>
       </c>
       <c r="D140" s="32" t="n">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="E140" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F140" s="32" t="inlineStr">
@@ -14081,13 +14081,13 @@
         <v>6000</v>
       </c>
       <c r="K140" s="34" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="L140" s="34" t="n">
-        <v>4000</v>
+        <v>4500</v>
       </c>
       <c r="M140" s="35" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="N140" s="37" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="O140" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -14106,10 +14106,14 @@
       </c>
       <c r="B141" s="33" t="inlineStr">
         <is>
-          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
-        </is>
-      </c>
-      <c r="C141" s="32" t="inlineStr"/>
+          <t>Клапан невозвратный штуцерный проходной Ду20 Ру40</t>
+        </is>
+      </c>
+      <c r="C141" s="32" t="inlineStr">
+        <is>
+          <t>522-3м-9</t>
+        </is>
+      </c>
       <c r="D141" s="32" t="n">
         <v>20</v>
       </c>
@@ -14136,13 +14140,13 @@
         <v>6000</v>
       </c>
       <c r="K141" s="34" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="L141" s="34" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="M141" s="35" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="N141" s="37" t="inlineStr">
         <is>
@@ -14161,20 +14165,16 @@
       </c>
       <c r="B142" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Ду10 Ру100</t>
-        </is>
-      </c>
-      <c r="C142" s="32" t="inlineStr">
-        <is>
-          <t>521-01.493-02</t>
-        </is>
-      </c>
+          <t>Клапан муфтовый проходной запорный Ду20Ру16</t>
+        </is>
+      </c>
+      <c r="C142" s="32" t="inlineStr"/>
       <c r="D142" s="32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E142" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная проходная</t>
         </is>
       </c>
       <c r="F142" s="32" t="inlineStr">
@@ -14186,17 +14186,23 @@
         <v>1</v>
       </c>
       <c r="H142" s="32" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="I142" s="34" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="J142" s="34" t="n">
-        <v>4500</v>
-      </c>
-      <c r="K142" s="34" t="n"/>
-      <c r="L142" s="34" t="n"/>
-      <c r="M142" s="35" t="n"/>
+        <v>6000</v>
+      </c>
+      <c r="K142" s="34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L142" s="34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M142" s="35" t="n">
+        <v>6</v>
+      </c>
       <c r="N142" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -14214,16 +14220,16 @@
       </c>
       <c r="B143" s="33" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
+          <t>Клапан штуцерный угловой Ду10 Ру100</t>
         </is>
       </c>
       <c r="C143" s="32" t="inlineStr">
         <is>
-          <t>524-03.004</t>
+          <t>521-01.493-02</t>
         </is>
       </c>
       <c r="D143" s="32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E143" s="32" t="inlineStr">
         <is>
@@ -14239,13 +14245,13 @@
         <v>1</v>
       </c>
       <c r="H143" s="32" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="I143" s="34" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="J143" s="34" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="K143" s="34" t="n"/>
       <c r="L143" s="34" t="n"/>
@@ -14257,7 +14263,7 @@
       </c>
       <c r="O143" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -14267,20 +14273,20 @@
       </c>
       <c r="B144" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
+          <t>Клапан предохранительный штуцерный угловой Ду6,5-9</t>
         </is>
       </c>
       <c r="C144" s="32" t="inlineStr">
         <is>
-          <t>522-01-493-01</t>
+          <t>524-03.004</t>
         </is>
       </c>
       <c r="D144" s="32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E144" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная проходная</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F144" s="32" t="inlineStr">
@@ -14292,23 +14298,17 @@
         <v>1</v>
       </c>
       <c r="H144" s="32" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="I144" s="34" t="n">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="J144" s="34" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K144" s="34" t="n">
-        <v>4000</v>
-      </c>
-      <c r="L144" s="34" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M144" s="35" t="n">
-        <v>0.75</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="K144" s="34" t="n"/>
+      <c r="L144" s="34" t="n"/>
+      <c r="M144" s="35" t="n"/>
       <c r="N144" s="37" t="inlineStr">
         <is>
           <t>по типу и диаметру</t>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="O144" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -14326,12 +14326,12 @@
       </c>
       <c r="B145" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
+          <t>Клапан штуцерный проходной невозвратный Ду10Ру100</t>
         </is>
       </c>
       <c r="C145" s="32" t="inlineStr">
         <is>
-          <t>521-3м-52</t>
+          <t>522-01-493-01</t>
         </is>
       </c>
       <c r="D145" s="32" t="n">
@@ -14360,13 +14360,13 @@
         <v>3000</v>
       </c>
       <c r="K145" s="34" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="L145" s="34" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="M145" s="35" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="N145" s="37" t="inlineStr">
         <is>
@@ -14385,12 +14385,12 @@
       </c>
       <c r="B146" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру6</t>
         </is>
       </c>
       <c r="C146" s="32" t="inlineStr">
         <is>
-          <t>Без чертежа</t>
+          <t>521-3м-52</t>
         </is>
       </c>
       <c r="D146" s="32" t="n">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="O146" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -14444,12 +14444,12 @@
       </c>
       <c r="B147" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру 40</t>
         </is>
       </c>
       <c r="C147" s="32" t="inlineStr">
         <is>
-          <t>521-3м-953</t>
+          <t>Без чертежа</t>
         </is>
       </c>
       <c r="D147" s="32" t="n">
@@ -14462,7 +14462,7 @@
       </c>
       <c r="F147" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G147" s="34" t="n">
@@ -14472,10 +14472,10 @@
         <v>2.3</v>
       </c>
       <c r="I147" s="34" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="J147" s="34" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="K147" s="34" t="n">
         <v>2000</v>
@@ -14484,7 +14484,7 @@
         <v>2000</v>
       </c>
       <c r="M147" s="35" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="N147" s="37" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="O147" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -14503,12 +14503,12 @@
       </c>
       <c r="B148" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
+          <t>Клапан штуцерный проходной Ду 10 Ру25 СТАЛЬ</t>
         </is>
       </c>
       <c r="C148" s="32" t="inlineStr">
         <is>
-          <t>522-03.134</t>
+          <t>521-3м-953</t>
         </is>
       </c>
       <c r="D148" s="32" t="n">
@@ -14556,8 +14556,67 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" s="32" t="n">
+        <v>145</v>
+      </c>
+      <c r="B149" s="33" t="inlineStr">
+        <is>
+          <t>Клапан штуцерный проходной Ду 10 Ру63 СТАЛЬ</t>
+        </is>
+      </c>
+      <c r="C149" s="32" t="inlineStr">
+        <is>
+          <t>522-03.134</t>
+        </is>
+      </c>
+      <c r="D149" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E149" s="32" t="inlineStr">
+        <is>
+          <t>Штуцерная проходная</t>
+        </is>
+      </c>
+      <c r="F149" s="32" t="inlineStr">
+        <is>
+          <t>сталь</t>
+        </is>
+      </c>
+      <c r="G149" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I149" s="34" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J149" s="34" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K149" s="34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L149" s="34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M149" s="35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N149" s="37" t="inlineStr">
+        <is>
+          <t>по типу и диаметру</t>
+        </is>
+      </c>
+      <c r="O149" s="32" t="inlineStr">
+        <is>
+          <t>Склад 2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O148"/>
+  <autoFilter ref="A4:O149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14568,7 +14627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14982,10 +15041,10 @@
         <v>5.5</v>
       </c>
       <c r="I10" s="34" t="n">
-        <v>9910</v>
+        <v>9808</v>
       </c>
       <c r="J10" s="34" t="n">
-        <v>614414</v>
+        <v>608068</v>
       </c>
       <c r="K10" s="34" t="n">
         <v>15000</v>
@@ -14994,7 +15053,7 @@
         <v>930000</v>
       </c>
       <c r="M10" s="35" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N10" s="38" t="inlineStr">
         <is>
@@ -15068,48 +15127,42 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуц.проход.односедельный Ду20Ру400 у входа</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>525-03.044</t>
+          <t>(541-03.218)</t>
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
-          <t>Редукционные клапаны</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G12" s="34" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H12" s="32" t="n">
-        <v>27</v>
+        <v>11.2</v>
       </c>
       <c r="I12" s="34" t="n">
-        <v>48649</v>
+        <v>19972</v>
       </c>
       <c r="J12" s="34" t="n">
-        <v>437838</v>
-      </c>
-      <c r="K12" s="34" t="n">
-        <v>35000</v>
-      </c>
-      <c r="L12" s="34" t="n">
-        <v>315000</v>
-      </c>
-      <c r="M12" s="35" t="n">
-        <v>1.39</v>
-      </c>
+        <v>379463</v>
+      </c>
+      <c r="K12" s="34" t="n"/>
+      <c r="L12" s="34" t="n"/>
+      <c r="M12" s="35" t="n"/>
       <c r="N12" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15117,7 +15170,7 @@
       </c>
       <c r="O12" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -15127,42 +15180,48 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>(541-03.218)</t>
+          <t>522-03.122-04</t>
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G13" s="34" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H13" s="32" t="n">
-        <v>11.2</v>
+        <v>5.5</v>
       </c>
       <c r="I13" s="34" t="n">
-        <v>20180</v>
+        <v>37311</v>
       </c>
       <c r="J13" s="34" t="n">
-        <v>383423</v>
-      </c>
-      <c r="K13" s="34" t="n"/>
-      <c r="L13" s="34" t="n"/>
-      <c r="M13" s="35" t="n"/>
+        <v>373106</v>
+      </c>
+      <c r="K13" s="34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L13" s="34" t="n">
+        <v>200000</v>
+      </c>
+      <c r="M13" s="35" t="n">
+        <v>1.87</v>
+      </c>
       <c r="N13" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15170,7 +15229,7 @@
       </c>
       <c r="O13" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -15180,20 +15239,16 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
-        </is>
-      </c>
-      <c r="C14" s="32" t="inlineStr">
-        <is>
-          <t>522-03.122-04</t>
-        </is>
-      </c>
+          <t>Клинкет  Ду 350</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr"/>
       <c r="D14" s="32" t="n">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="E14" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F14" s="32" t="inlineStr">
@@ -15202,25 +15257,25 @@
         </is>
       </c>
       <c r="G14" s="34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H14" s="32" t="n">
-        <v>5.5</v>
+        <v>228</v>
       </c>
       <c r="I14" s="34" t="n">
-        <v>37311</v>
+        <v>350234</v>
       </c>
       <c r="J14" s="34" t="n">
-        <v>373106</v>
+        <v>350234</v>
       </c>
       <c r="K14" s="34" t="n">
-        <v>20000</v>
+        <v>300000</v>
       </c>
       <c r="L14" s="34" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="M14" s="35" t="n">
-        <v>1.87</v>
+        <v>1.17</v>
       </c>
       <c r="N14" s="38" t="inlineStr">
         <is>
@@ -15239,16 +15294,16 @@
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>Клинкет  Ду 350</t>
+          <t>Клапан проходной ДУ 125 корпус</t>
         </is>
       </c>
       <c r="C15" s="32" t="inlineStr"/>
       <c r="D15" s="32" t="n">
-        <v>350</v>
+        <v>125</v>
       </c>
       <c r="E15" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F15" s="32" t="inlineStr">
@@ -15260,22 +15315,22 @@
         <v>1</v>
       </c>
       <c r="H15" s="32" t="n">
-        <v>228</v>
+        <v>135.3</v>
       </c>
       <c r="I15" s="34" t="n">
-        <v>350234</v>
+        <v>241182</v>
       </c>
       <c r="J15" s="34" t="n">
-        <v>350234</v>
+        <v>241182</v>
       </c>
       <c r="K15" s="34" t="n">
-        <v>300000</v>
+        <v>37000</v>
       </c>
       <c r="L15" s="34" t="n">
-        <v>300000</v>
+        <v>37000</v>
       </c>
       <c r="M15" s="35" t="n">
-        <v>1.17</v>
+        <v>6.52</v>
       </c>
       <c r="N15" s="38" t="inlineStr">
         <is>
@@ -15284,7 +15339,7 @@
       </c>
       <c r="O15" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -15294,16 +15349,16 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>Клапан проходной ДУ 125 корпус</t>
+          <t>Клапан фланцевый проходной Ду200</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr"/>
       <c r="D16" s="32" t="n">
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="E16" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F16" s="32" t="inlineStr">
@@ -15315,22 +15370,22 @@
         <v>1</v>
       </c>
       <c r="H16" s="32" t="n">
-        <v>135.3</v>
+        <v>110</v>
       </c>
       <c r="I16" s="34" t="n">
-        <v>243699</v>
+        <v>213834</v>
       </c>
       <c r="J16" s="34" t="n">
-        <v>243699</v>
+        <v>213834</v>
       </c>
       <c r="K16" s="34" t="n">
-        <v>37000</v>
+        <v>150000</v>
       </c>
       <c r="L16" s="34" t="n">
-        <v>37000</v>
+        <v>150000</v>
       </c>
       <c r="M16" s="35" t="n">
-        <v>6.59</v>
+        <v>1.43</v>
       </c>
       <c r="N16" s="38" t="inlineStr">
         <is>
@@ -15349,16 +15404,16 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый проходной Ду200</t>
+          <t>Фильтр заборной воды ДУ 80</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr"/>
       <c r="D17" s="32" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="E17" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="F17" s="32" t="inlineStr">
@@ -15367,26 +15422,20 @@
         </is>
       </c>
       <c r="G17" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17" s="32" t="n">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="I17" s="34" t="n">
-        <v>213834</v>
+        <v>40246</v>
       </c>
       <c r="J17" s="34" t="n">
-        <v>213834</v>
-      </c>
-      <c r="K17" s="34" t="n">
-        <v>150000</v>
-      </c>
-      <c r="L17" s="34" t="n">
-        <v>150000</v>
-      </c>
-      <c r="M17" s="35" t="n">
-        <v>1.43</v>
-      </c>
+        <v>201228</v>
+      </c>
+      <c r="K17" s="34" t="n"/>
+      <c r="L17" s="34" t="n"/>
+      <c r="M17" s="35" t="n"/>
       <c r="N17" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15394,7 +15443,7 @@
       </c>
       <c r="O17" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -15404,34 +15453,38 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 80</t>
-        </is>
-      </c>
-      <c r="C18" s="32" t="inlineStr"/>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка)</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>(541-03.220)</t>
+        </is>
+      </c>
       <c r="D18" s="32" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E18" s="32" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G18" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="32" t="n">
-        <v>22</v>
+        <v>18.2</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>40246</v>
+        <v>32454</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>201228</v>
+        <v>194724</v>
       </c>
       <c r="K18" s="34" t="n"/>
       <c r="L18" s="34" t="n"/>
@@ -15443,7 +15496,7 @@
       </c>
       <c r="O18" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -15453,42 +15506,48 @@
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду125 (без поплавка)</t>
+          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
         <is>
-          <t>(541-03.220)</t>
+          <t>529-03.074</t>
         </is>
       </c>
       <c r="D19" s="32" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G19" s="34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H19" s="32" t="n">
-        <v>18.2</v>
+        <v>22</v>
       </c>
       <c r="I19" s="34" t="n">
-        <v>32793</v>
+        <v>50691</v>
       </c>
       <c r="J19" s="34" t="n">
-        <v>196757</v>
-      </c>
-      <c r="K19" s="34" t="n"/>
-      <c r="L19" s="34" t="n"/>
-      <c r="M19" s="35" t="n"/>
+        <v>152074</v>
+      </c>
+      <c r="K19" s="34" t="n">
+        <v>40000</v>
+      </c>
+      <c r="L19" s="34" t="n">
+        <v>120000</v>
+      </c>
+      <c r="M19" s="35" t="n">
+        <v>1.27</v>
+      </c>
       <c r="N19" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15496,7 +15555,7 @@
       </c>
       <c r="O19" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -15506,20 +15565,20 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
+          <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
         <is>
-          <t>529-03.074</t>
+          <t>587-03.082</t>
         </is>
       </c>
       <c r="D20" s="32" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Пусковые клапаны</t>
         </is>
       </c>
       <c r="F20" s="32" t="inlineStr">
@@ -15528,25 +15587,25 @@
         </is>
       </c>
       <c r="G20" s="34" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H20" s="32" t="n">
-        <v>22</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20" s="34" t="n">
-        <v>50691</v>
+        <v>15692</v>
       </c>
       <c r="J20" s="34" t="n">
-        <v>152074</v>
+        <v>125537</v>
       </c>
       <c r="K20" s="34" t="n">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="L20" s="34" t="n">
-        <v>120000</v>
+        <v>240000</v>
       </c>
       <c r="M20" s="35" t="n">
-        <v>1.27</v>
+        <v>0.52</v>
       </c>
       <c r="N20" s="38" t="inlineStr">
         <is>
@@ -15565,20 +15624,20 @@
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду32Ру125</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
-          <t>587-03.082</t>
+          <t>521-3М539</t>
         </is>
       </c>
       <c r="D21" s="32" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>Пусковые клапаны</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F21" s="32" t="inlineStr">
@@ -15587,25 +15646,25 @@
         </is>
       </c>
       <c r="G21" s="34" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H21" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="I21" s="34" t="n">
-        <v>15856</v>
+        <v>7614</v>
       </c>
       <c r="J21" s="34" t="n">
-        <v>126847</v>
+        <v>98980</v>
       </c>
       <c r="K21" s="34" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="L21" s="34" t="n">
-        <v>240000</v>
+        <v>260000</v>
       </c>
       <c r="M21" s="35" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="N21" s="38" t="inlineStr">
         <is>
@@ -15648,10 +15707,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I22" s="34" t="n">
-        <v>16517</v>
+        <v>16346</v>
       </c>
       <c r="J22" s="34" t="n">
-        <v>99099</v>
+        <v>98075</v>
       </c>
       <c r="K22" s="34" t="n">
         <v>7500</v>
@@ -15660,7 +15719,7 @@
         <v>45000</v>
       </c>
       <c r="M22" s="35" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="N22" s="38" t="inlineStr">
         <is>
@@ -15679,20 +15738,16 @@
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
-        </is>
-      </c>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>521-3М539</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr"/>
       <c r="D23" s="32" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
@@ -15701,25 +15756,25 @@
         </is>
       </c>
       <c r="G23" s="34" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H23" s="32" t="n">
-        <v>5.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I23" s="34" t="n">
-        <v>7614</v>
+        <v>13423</v>
       </c>
       <c r="J23" s="34" t="n">
-        <v>98980</v>
+        <v>93962</v>
       </c>
       <c r="K23" s="34" t="n">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="L23" s="34" t="n">
-        <v>260000</v>
+        <v>189000</v>
       </c>
       <c r="M23" s="35" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="N23" s="38" t="inlineStr">
         <is>
@@ -15728,7 +15783,7 @@
       </c>
       <c r="O23" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -15738,16 +15793,18 @@
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
-        </is>
-      </c>
-      <c r="C24" s="32" t="inlineStr"/>
-      <c r="D24" s="32" t="n">
-        <v>70</v>
-      </c>
+          <t>Клапан для манометра штуцерный сальниковый</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>521-34.3404-03</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="n"/>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F24" s="32" t="inlineStr">
@@ -15756,25 +15813,25 @@
         </is>
       </c>
       <c r="G24" s="34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H24" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>13423</v>
+        <v>8581</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>93962</v>
+        <v>85814</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>27000</v>
+        <v>6000</v>
       </c>
       <c r="L24" s="34" t="n">
-        <v>189000</v>
+        <v>60000</v>
       </c>
       <c r="M24" s="35" t="n">
-        <v>0.5</v>
+        <v>1.43</v>
       </c>
       <c r="N24" s="38" t="inlineStr">
         <is>
@@ -15783,7 +15840,7 @@
       </c>
       <c r="O24" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -15793,18 +15850,20 @@
       </c>
       <c r="B25" s="33" t="inlineStr">
         <is>
-          <t>Клапан для манометра штуцерный сальниковый</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="C25" s="32" t="inlineStr">
         <is>
-          <t>521-34.3404-03</t>
-        </is>
-      </c>
-      <c r="D25" s="32" t="n"/>
+          <t>527-03.055</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="n">
+        <v>80</v>
+      </c>
       <c r="E25" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="F25" s="32" t="inlineStr">
@@ -15813,25 +15872,25 @@
         </is>
       </c>
       <c r="G25" s="34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H25" s="32" t="n">
-        <v>1.3</v>
+        <v>19</v>
       </c>
       <c r="I25" s="34" t="n">
-        <v>8581</v>
+        <v>40587</v>
       </c>
       <c r="J25" s="34" t="n">
-        <v>85814</v>
+        <v>81174</v>
       </c>
       <c r="K25" s="34" t="n">
-        <v>6000</v>
+        <v>30000</v>
       </c>
       <c r="L25" s="34" t="n">
         <v>60000</v>
       </c>
       <c r="M25" s="35" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="N25" s="38" t="inlineStr">
         <is>
@@ -15840,7 +15899,7 @@
       </c>
       <c r="O25" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -15850,47 +15909,41 @@
       </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="C26" s="32" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
-      <c r="D26" s="32" t="n">
-        <v>80</v>
-      </c>
+          <t>Клапан проходной фланцевый сталь</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr"/>
+      <c r="D26" s="32" t="n"/>
       <c r="E26" s="32" t="inlineStr">
         <is>
-          <t>Кингстоны</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F26" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G26" s="34" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I26" s="34" t="n">
-        <v>40587</v>
+        <v>38879</v>
       </c>
       <c r="J26" s="34" t="n">
-        <v>81174</v>
+        <v>77758</v>
       </c>
       <c r="K26" s="34" t="n">
-        <v>30000</v>
+        <v>18000</v>
       </c>
       <c r="L26" s="34" t="n">
-        <v>60000</v>
+        <v>36000</v>
       </c>
       <c r="M26" s="35" t="n">
-        <v>1.35</v>
+        <v>2.16</v>
       </c>
       <c r="N26" s="38" t="inlineStr">
         <is>
@@ -15899,7 +15952,7 @@
       </c>
       <c r="O26" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -15909,42 +15962,42 @@
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый сталь</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr"/>
-      <c r="D27" s="32" t="n"/>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>529-03.003</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="n">
+        <v>100</v>
+      </c>
       <c r="E27" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G27" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="32" t="n">
-        <v>20</v>
+        <v>33.7</v>
       </c>
       <c r="I27" s="34" t="n">
-        <v>38879</v>
+        <v>77650</v>
       </c>
       <c r="J27" s="34" t="n">
-        <v>77758</v>
-      </c>
-      <c r="K27" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L27" s="34" t="n">
-        <v>36000</v>
-      </c>
-      <c r="M27" s="35" t="n">
-        <v>2.16</v>
-      </c>
+        <v>77650</v>
+      </c>
+      <c r="K27" s="34" t="n"/>
+      <c r="L27" s="34" t="n"/>
+      <c r="M27" s="35" t="n"/>
       <c r="N27" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15952,7 +16005,7 @@
       </c>
       <c r="O27" s="32" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -15962,20 +16015,20 @@
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
+          <t>Клапан пусковой Ду20Ру125</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
         <is>
-          <t>529-03.003</t>
+          <t>587-03.080</t>
         </is>
       </c>
       <c r="D28" s="32" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E28" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Пусковые клапаны</t>
         </is>
       </c>
       <c r="F28" s="32" t="inlineStr">
@@ -15984,20 +16037,26 @@
         </is>
       </c>
       <c r="G28" s="34" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H28" s="32" t="n">
-        <v>33.7</v>
+        <v>5.6</v>
       </c>
       <c r="I28" s="34" t="n">
-        <v>77650</v>
+        <v>9986</v>
       </c>
       <c r="J28" s="34" t="n">
-        <v>77650</v>
-      </c>
-      <c r="K28" s="34" t="n"/>
-      <c r="L28" s="34" t="n"/>
-      <c r="M28" s="35" t="n"/>
+        <v>69901</v>
+      </c>
+      <c r="K28" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L28" s="34" t="n">
+        <v>175000</v>
+      </c>
+      <c r="M28" s="35" t="n">
+        <v>0.4</v>
+      </c>
       <c r="N28" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16005,7 +16064,7 @@
       </c>
       <c r="O28" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16015,12 +16074,12 @@
       </c>
       <c r="B29" s="33" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду20Ру125</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
         <is>
-          <t>587-03.080</t>
+          <t>554-03.905-06</t>
         </is>
       </c>
       <c r="D29" s="32" t="n">
@@ -16028,7 +16087,7 @@
       </c>
       <c r="E29" s="32" t="inlineStr">
         <is>
-          <t>Пусковые клапаны</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="F29" s="32" t="inlineStr">
@@ -16037,26 +16096,20 @@
         </is>
       </c>
       <c r="G29" s="34" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="H29" s="32" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="I29" s="34" t="n">
-        <v>10090</v>
+        <v>2675</v>
       </c>
       <c r="J29" s="34" t="n">
-        <v>70631</v>
-      </c>
-      <c r="K29" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="L29" s="34" t="n">
-        <v>175000</v>
-      </c>
-      <c r="M29" s="35" t="n">
-        <v>0.4</v>
-      </c>
+        <v>69544</v>
+      </c>
+      <c r="K29" s="34" t="n"/>
+      <c r="L29" s="34" t="n"/>
+      <c r="M29" s="35" t="n"/>
       <c r="N29" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16064,7 +16117,7 @@
       </c>
       <c r="O29" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -16074,20 +16127,14 @@
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="inlineStr">
-        <is>
-          <t>554-03.905-06</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="n">
-        <v>20</v>
-      </c>
+          <t>Электропривод к задвижке</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr"/>
+      <c r="D30" s="32" t="n"/>
       <c r="E30" s="32" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F30" s="32" t="inlineStr">
@@ -16096,20 +16143,26 @@
         </is>
       </c>
       <c r="G30" s="34" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="H30" s="32" t="n">
-        <v>1.5</v>
+        <v>40</v>
       </c>
       <c r="I30" s="34" t="n">
-        <v>2703</v>
+        <v>61445</v>
       </c>
       <c r="J30" s="34" t="n">
-        <v>70270</v>
-      </c>
-      <c r="K30" s="34" t="n"/>
-      <c r="L30" s="34" t="n"/>
-      <c r="M30" s="35" t="n"/>
+        <v>61445</v>
+      </c>
+      <c r="K30" s="34" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L30" s="34" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M30" s="35" t="n">
+        <v>1.23</v>
+      </c>
       <c r="N30" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16117,7 +16170,7 @@
       </c>
       <c r="O30" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -16127,14 +16180,16 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr"/>
-      <c r="D31" s="32" t="n"/>
+      <c r="D31" s="32" t="n">
+        <v>65</v>
+      </c>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Фланцевая, угол или проход не указан</t>
         </is>
       </c>
       <c r="F31" s="32" t="inlineStr">
@@ -16143,25 +16198,25 @@
         </is>
       </c>
       <c r="G31" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="32" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I31" s="34" t="n">
-        <v>61445</v>
+        <v>30314</v>
       </c>
       <c r="J31" s="34" t="n">
-        <v>61445</v>
+        <v>60628</v>
       </c>
       <c r="K31" s="34" t="n">
-        <v>50000</v>
+        <v>9750</v>
       </c>
       <c r="L31" s="34" t="n">
-        <v>50000</v>
+        <v>19500</v>
       </c>
       <c r="M31" s="35" t="n">
-        <v>1.23</v>
+        <v>3.11</v>
       </c>
       <c r="N31" s="38" t="inlineStr">
         <is>
@@ -16170,7 +16225,7 @@
       </c>
       <c r="O31" s="32" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -16180,16 +16235,20 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="inlineStr"/>
+          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>529-35-1405-01</t>
+        </is>
+      </c>
       <c r="D32" s="32" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="E32" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая, угол или проход не указан</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F32" s="32" t="inlineStr">
@@ -16198,25 +16257,25 @@
         </is>
       </c>
       <c r="G32" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="32" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="I32" s="34" t="n">
-        <v>30631</v>
+        <v>59908</v>
       </c>
       <c r="J32" s="34" t="n">
-        <v>61261</v>
+        <v>59908</v>
       </c>
       <c r="K32" s="34" t="n">
-        <v>9750</v>
+        <v>40000</v>
       </c>
       <c r="L32" s="34" t="n">
-        <v>19500</v>
+        <v>40000</v>
       </c>
       <c r="M32" s="35" t="n">
-        <v>3.14</v>
+        <v>1.5</v>
       </c>
       <c r="N32" s="38" t="inlineStr">
         <is>
@@ -16225,7 +16284,7 @@
       </c>
       <c r="O32" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16235,47 +16294,47 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
+          <t>Клапан паровой Ду65Ру10</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
         <is>
-          <t>529-35-1405-01</t>
+          <t>581-03.034</t>
         </is>
       </c>
       <c r="D33" s="32" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Паровые клапаны</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G33" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="32" t="n">
-        <v>26</v>
+        <v>32.6</v>
       </c>
       <c r="I33" s="34" t="n">
-        <v>59908</v>
+        <v>58132</v>
       </c>
       <c r="J33" s="34" t="n">
-        <v>59908</v>
+        <v>58132</v>
       </c>
       <c r="K33" s="34" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="L33" s="34" t="n">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="M33" s="35" t="n">
-        <v>1.5</v>
+        <v>0.97</v>
       </c>
       <c r="N33" s="38" t="inlineStr">
         <is>
@@ -16294,47 +16353,41 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="inlineStr">
-        <is>
-          <t>581-03.034</t>
-        </is>
-      </c>
-      <c r="D34" s="32" t="n">
-        <v>65</v>
-      </c>
+          <t>Коробка 2-х клапанная корпус</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr"/>
+      <c r="D34" s="32" t="n"/>
       <c r="E34" s="32" t="inlineStr">
         <is>
-          <t>Паровые клапаны</t>
+          <t>Коробки клапанные</t>
         </is>
       </c>
       <c r="F34" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G34" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="32" t="n">
-        <v>32.6</v>
+        <v>40</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>58739</v>
+        <v>57434</v>
       </c>
       <c r="J34" s="34" t="n">
-        <v>58739</v>
+        <v>57434</v>
       </c>
       <c r="K34" s="34" t="n">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="L34" s="34" t="n">
-        <v>60000</v>
+        <v>20000</v>
       </c>
       <c r="M34" s="35" t="n">
-        <v>0.98</v>
+        <v>2.87</v>
       </c>
       <c r="N34" s="38" t="inlineStr">
         <is>
@@ -16343,7 +16396,7 @@
       </c>
       <c r="O34" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -16353,14 +16406,20 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
-        </is>
-      </c>
-      <c r="C35" s="32" t="inlineStr"/>
-      <c r="D35" s="32" t="n"/>
+          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>529-35.1406-01</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="n">
+        <v>100</v>
+      </c>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Коробки клапанные</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
@@ -16372,22 +16431,22 @@
         <v>1</v>
       </c>
       <c r="H35" s="32" t="n">
-        <v>40</v>
+        <v>23.6</v>
       </c>
       <c r="I35" s="34" t="n">
-        <v>57434</v>
+        <v>54378</v>
       </c>
       <c r="J35" s="34" t="n">
-        <v>57434</v>
+        <v>54378</v>
       </c>
       <c r="K35" s="34" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="L35" s="34" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="M35" s="35" t="n">
-        <v>2.87</v>
+        <v>1.36</v>
       </c>
       <c r="N35" s="38" t="inlineStr">
         <is>
@@ -16396,7 +16455,7 @@
       </c>
       <c r="O35" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16406,20 +16465,20 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
+          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
         </is>
       </c>
       <c r="C36" s="32" t="inlineStr">
         <is>
-          <t>529-35.1406-01</t>
+          <t>527-03.055</t>
         </is>
       </c>
       <c r="D36" s="32" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E36" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Кингстоны</t>
         </is>
       </c>
       <c r="F36" s="32" t="inlineStr">
@@ -16431,23 +16490,17 @@
         <v>1</v>
       </c>
       <c r="H36" s="32" t="n">
-        <v>23.6</v>
+        <v>19</v>
       </c>
       <c r="I36" s="34" t="n">
-        <v>54378</v>
+        <v>40587</v>
       </c>
       <c r="J36" s="34" t="n">
-        <v>54378</v>
-      </c>
-      <c r="K36" s="34" t="n">
-        <v>40000</v>
-      </c>
-      <c r="L36" s="34" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M36" s="35" t="n">
-        <v>1.36</v>
-      </c>
+        <v>40587</v>
+      </c>
+      <c r="K36" s="34" t="n"/>
+      <c r="L36" s="34" t="n"/>
+      <c r="M36" s="35" t="n"/>
       <c r="N36" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16465,20 +16518,14 @@
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>Кингстон донный фланцевый Ду80 Ру2,5</t>
-        </is>
-      </c>
-      <c r="C37" s="32" t="inlineStr">
-        <is>
-          <t>527-03.055</t>
-        </is>
-      </c>
-      <c r="D37" s="32" t="n">
-        <v>80</v>
-      </c>
+          <t>Клапан электромагнитный б/у</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr"/>
+      <c r="D37" s="32" t="n"/>
       <c r="E37" s="32" t="inlineStr">
         <is>
-          <t>Кингстоны</t>
+          <t>Электромагнитные клапаны</t>
         </is>
       </c>
       <c r="F37" s="32" t="inlineStr">
@@ -16487,16 +16534,16 @@
         </is>
       </c>
       <c r="G37" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37" s="32" t="n">
-        <v>19</v>
+        <v>12.3</v>
       </c>
       <c r="I37" s="34" t="n">
-        <v>40587</v>
+        <v>12724</v>
       </c>
       <c r="J37" s="34" t="n">
-        <v>40587</v>
+        <v>38172</v>
       </c>
       <c r="K37" s="34" t="n"/>
       <c r="L37" s="34" t="n"/>
@@ -16508,7 +16555,7 @@
       </c>
       <c r="O37" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -16518,14 +16565,18 @@
       </c>
       <c r="B38" s="33" t="inlineStr">
         <is>
-          <t>Клапан электромагнитный б/у</t>
-        </is>
-      </c>
-      <c r="C38" s="32" t="inlineStr"/>
+          <t>Клапан штуцерный угловой Рр150/10</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>521-ц22п</t>
+        </is>
+      </c>
       <c r="D38" s="32" t="n"/>
       <c r="E38" s="32" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F38" s="32" t="inlineStr">
@@ -16534,20 +16585,26 @@
         </is>
       </c>
       <c r="G38" s="34" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H38" s="32" t="n">
-        <v>12.3</v>
+        <v>1.3</v>
       </c>
       <c r="I38" s="34" t="n">
-        <v>12724</v>
+        <v>3954</v>
       </c>
       <c r="J38" s="34" t="n">
-        <v>38172</v>
-      </c>
-      <c r="K38" s="34" t="n"/>
-      <c r="L38" s="34" t="n"/>
-      <c r="M38" s="35" t="n"/>
+        <v>31636</v>
+      </c>
+      <c r="K38" s="34" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L38" s="34" t="n">
+        <v>32000</v>
+      </c>
+      <c r="M38" s="35" t="n">
+        <v>0.99</v>
+      </c>
       <c r="N38" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16555,7 +16612,7 @@
       </c>
       <c r="O38" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -16565,18 +16622,16 @@
       </c>
       <c r="B39" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
-        </is>
-      </c>
-      <c r="C39" s="32" t="inlineStr">
-        <is>
-          <t>521-ц22п</t>
-        </is>
-      </c>
-      <c r="D39" s="32" t="n"/>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr"/>
+      <c r="D39" s="32" t="n">
+        <v>65</v>
+      </c>
       <c r="E39" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Фланцевая, угол или проход не указан</t>
         </is>
       </c>
       <c r="F39" s="32" t="inlineStr">
@@ -16585,25 +16640,25 @@
         </is>
       </c>
       <c r="G39" s="34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H39" s="32" t="n">
-        <v>1.3</v>
+        <v>17</v>
       </c>
       <c r="I39" s="34" t="n">
-        <v>3954</v>
+        <v>30314</v>
       </c>
       <c r="J39" s="34" t="n">
-        <v>31636</v>
+        <v>30314</v>
       </c>
       <c r="K39" s="34" t="n">
-        <v>4000</v>
+        <v>9750</v>
       </c>
       <c r="L39" s="34" t="n">
-        <v>32000</v>
+        <v>9750</v>
       </c>
       <c r="M39" s="35" t="n">
-        <v>0.99</v>
+        <v>3.11</v>
       </c>
       <c r="N39" s="38" t="inlineStr">
         <is>
@@ -16612,7 +16667,7 @@
       </c>
       <c r="O39" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -16622,16 +16677,14 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-35.4044-01)</t>
+          <t>Клапан фреоновый саленоидный</t>
         </is>
       </c>
       <c r="C40" s="32" t="inlineStr"/>
-      <c r="D40" s="32" t="n">
-        <v>65</v>
-      </c>
+      <c r="D40" s="32" t="n"/>
       <c r="E40" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая, угол или проход не указан</t>
+          <t>Электромагнитные клапаны</t>
         </is>
       </c>
       <c r="F40" s="32" t="inlineStr">
@@ -16640,26 +16693,20 @@
         </is>
       </c>
       <c r="G40" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="32" t="n">
-        <v>17</v>
+        <v>12.3</v>
       </c>
       <c r="I40" s="34" t="n">
-        <v>30631</v>
+        <v>12724</v>
       </c>
       <c r="J40" s="34" t="n">
-        <v>30631</v>
-      </c>
-      <c r="K40" s="34" t="n">
-        <v>9750</v>
-      </c>
-      <c r="L40" s="34" t="n">
-        <v>9750</v>
-      </c>
-      <c r="M40" s="35" t="n">
-        <v>3.14</v>
-      </c>
+        <v>25448</v>
+      </c>
+      <c r="K40" s="34" t="n"/>
+      <c r="L40" s="34" t="n"/>
+      <c r="M40" s="35" t="n"/>
       <c r="N40" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16667,7 +16714,7 @@
       </c>
       <c r="O40" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -16677,14 +16724,18 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
-        </is>
-      </c>
-      <c r="C41" s="32" t="inlineStr"/>
+          <t>Клапан штуцерный угловой Рр150/10</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>521-ц22п</t>
+        </is>
+      </c>
       <c r="D41" s="32" t="n"/>
       <c r="E41" s="32" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F41" s="32" t="inlineStr">
@@ -16693,20 +16744,26 @@
         </is>
       </c>
       <c r="G41" s="34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H41" s="32" t="n">
-        <v>12.3</v>
+        <v>1</v>
       </c>
       <c r="I41" s="34" t="n">
-        <v>12724</v>
+        <v>3126</v>
       </c>
       <c r="J41" s="34" t="n">
-        <v>25448</v>
-      </c>
-      <c r="K41" s="34" t="n"/>
-      <c r="L41" s="34" t="n"/>
-      <c r="M41" s="35" t="n"/>
+        <v>25008</v>
+      </c>
+      <c r="K41" s="34" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L41" s="34" t="n">
+        <v>24000</v>
+      </c>
+      <c r="M41" s="35" t="n">
+        <v>1.04</v>
+      </c>
       <c r="N41" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16714,7 +16771,7 @@
       </c>
       <c r="O41" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16724,18 +16781,20 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
         <is>
-          <t>521-ц22п</t>
-        </is>
-      </c>
-      <c r="D42" s="32" t="n"/>
+          <t>524-35.2423-01</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="n">
+        <v>6</v>
+      </c>
       <c r="E42" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F42" s="32" t="inlineStr">
@@ -16744,25 +16803,25 @@
         </is>
       </c>
       <c r="G42" s="34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H42" s="32" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="I42" s="34" t="n">
-        <v>3126</v>
+        <v>23743</v>
       </c>
       <c r="J42" s="34" t="n">
-        <v>25008</v>
+        <v>23743</v>
       </c>
       <c r="K42" s="34" t="n">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="L42" s="34" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="M42" s="35" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="N42" s="38" t="inlineStr">
         <is>
@@ -16781,48 +16840,42 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
         <is>
-          <t>524-35.2423-01</t>
+          <t>(541-03.232)</t>
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E43" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F43" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G43" s="34" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H43" s="32" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="I43" s="34" t="n">
-        <v>23743</v>
+        <v>2853</v>
       </c>
       <c r="J43" s="34" t="n">
-        <v>23743</v>
-      </c>
-      <c r="K43" s="34" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L43" s="34" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M43" s="35" t="n">
-        <v>1.19</v>
-      </c>
+        <v>22825</v>
+      </c>
+      <c r="K43" s="34" t="n"/>
+      <c r="L43" s="34" t="n"/>
+      <c r="M43" s="35" t="n"/>
       <c r="N43" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16830,7 +16883,7 @@
       </c>
       <c r="O43" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -16840,16 +16893,16 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
+          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
         <is>
-          <t>(541-03.232)</t>
+          <t>(541-03.316-04)</t>
         </is>
       </c>
       <c r="D44" s="32" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="E44" s="32" t="inlineStr">
         <is>
@@ -16858,20 +16911,20 @@
       </c>
       <c r="F44" s="32" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G44" s="34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H44" s="32" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="I44" s="34" t="n">
-        <v>2883</v>
+        <v>8381</v>
       </c>
       <c r="J44" s="34" t="n">
-        <v>23063</v>
+        <v>16762</v>
       </c>
       <c r="K44" s="34" t="n"/>
       <c r="L44" s="34" t="n"/>
@@ -16893,42 +16946,48 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
+          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
         </is>
       </c>
       <c r="C45" s="32" t="inlineStr">
         <is>
-          <t>(541-03.316-04)</t>
+          <t>521-03.445-04</t>
         </is>
       </c>
       <c r="D45" s="32" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="E45" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F45" s="32" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G45" s="34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H45" s="32" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="I45" s="34" t="n">
-        <v>8468</v>
+        <v>4064</v>
       </c>
       <c r="J45" s="34" t="n">
-        <v>16937</v>
-      </c>
-      <c r="K45" s="34" t="n"/>
-      <c r="L45" s="34" t="n"/>
-      <c r="M45" s="35" t="n"/>
+        <v>16255</v>
+      </c>
+      <c r="K45" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L45" s="34" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M45" s="35" t="n">
+        <v>0.27</v>
+      </c>
       <c r="N45" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16936,7 +16995,7 @@
       </c>
       <c r="O45" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16946,47 +17005,47 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
+          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
         </is>
       </c>
       <c r="C46" s="32" t="inlineStr">
         <is>
-          <t>521-03.445-04</t>
+          <t>522-35.445-19</t>
         </is>
       </c>
       <c r="D46" s="32" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E46" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F46" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G46" s="34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H46" s="32" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="I46" s="34" t="n">
-        <v>4064</v>
+        <v>7767</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>16255</v>
+        <v>15534</v>
       </c>
       <c r="K46" s="34" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="L46" s="34" t="n">
-        <v>60000</v>
+        <v>36000</v>
       </c>
       <c r="M46" s="35" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="N46" s="38" t="inlineStr">
         <is>
@@ -16995,7 +17054,7 @@
       </c>
       <c r="O46" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -17033,10 +17092,10 @@
         <v>2.9</v>
       </c>
       <c r="I47" s="34" t="n">
-        <v>5225</v>
+        <v>5171</v>
       </c>
       <c r="J47" s="34" t="n">
-        <v>15676</v>
+        <v>15514</v>
       </c>
       <c r="K47" s="34" t="n"/>
       <c r="L47" s="34" t="n"/>
@@ -17058,48 +17117,42 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
+          <t>Клапан Ду20/10</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
         <is>
-          <t>522-35.445-19</t>
+          <t>581-С6.73</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E48" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F48" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G48" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H48" s="32" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="I48" s="34" t="n">
-        <v>7767</v>
+        <v>4280</v>
       </c>
       <c r="J48" s="34" t="n">
-        <v>15534</v>
-      </c>
-      <c r="K48" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L48" s="34" t="n">
-        <v>36000</v>
-      </c>
-      <c r="M48" s="35" t="n">
-        <v>0.43</v>
-      </c>
+        <v>12839</v>
+      </c>
+      <c r="K48" s="34" t="n"/>
+      <c r="L48" s="34" t="n"/>
+      <c r="M48" s="35" t="n"/>
       <c r="N48" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17107,7 +17160,7 @@
       </c>
       <c r="O48" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17117,48 +17170,40 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Клапан с электромагнитным ручным управлением</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
         <is>
-          <t>525-35.2634</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="n">
-        <v>10</v>
-      </c>
+          <t>587-182.126</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="n"/>
       <c r="E49" s="32" t="inlineStr">
         <is>
-          <t>Редукционные клапаны</t>
+          <t>Электромагнитные клапаны</t>
         </is>
       </c>
       <c r="F49" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G49" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="32" t="n">
-        <v>7.5</v>
+        <v>12.3</v>
       </c>
       <c r="I49" s="34" t="n">
-        <v>13514</v>
+        <v>12724</v>
       </c>
       <c r="J49" s="34" t="n">
-        <v>13514</v>
-      </c>
-      <c r="K49" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="L49" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M49" s="35" t="n">
-        <v>0.9</v>
-      </c>
+        <v>12724</v>
+      </c>
+      <c r="K49" s="34" t="n"/>
+      <c r="L49" s="34" t="n"/>
+      <c r="M49" s="35" t="n"/>
       <c r="N49" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17166,7 +17211,7 @@
       </c>
       <c r="O49" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17176,48 +17221,40 @@
       </c>
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="C50" s="32" t="inlineStr">
         <is>
-          <t>525-35.2634-04</t>
-        </is>
-      </c>
-      <c r="D50" s="32" t="n">
-        <v>10</v>
-      </c>
+          <t>2619802505</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="n"/>
       <c r="E50" s="32" t="inlineStr">
         <is>
-          <t>Редукционные клапаны</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F50" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G50" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="32" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="I50" s="34" t="n">
-        <v>13514</v>
+        <v>12126</v>
       </c>
       <c r="J50" s="34" t="n">
-        <v>13514</v>
-      </c>
-      <c r="K50" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="L50" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M50" s="35" t="n">
-        <v>0.9</v>
-      </c>
+        <v>12126</v>
+      </c>
+      <c r="K50" s="34" t="n"/>
+      <c r="L50" s="34" t="n"/>
+      <c r="M50" s="35" t="n"/>
       <c r="N50" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17225,7 +17262,7 @@
       </c>
       <c r="O50" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17235,17 +17272,11 @@
       </c>
       <c r="B51" s="33" t="inlineStr">
         <is>
-          <t>Клапан Ду20/10</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>581-С6.73</t>
-        </is>
-      </c>
-      <c r="D51" s="32" t="n">
-        <v>20</v>
-      </c>
+          <t>Судовая запорная арматура</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr"/>
+      <c r="D51" s="32" t="n"/>
       <c r="E51" s="32" t="inlineStr">
         <is>
           <t>Без описания — уточнить</t>
@@ -17257,20 +17288,26 @@
         </is>
       </c>
       <c r="G51" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H51" s="32" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="I51" s="34" t="n">
-        <v>4324</v>
+        <v>12126</v>
       </c>
       <c r="J51" s="34" t="n">
-        <v>12973</v>
-      </c>
-      <c r="K51" s="34" t="n"/>
-      <c r="L51" s="34" t="n"/>
-      <c r="M51" s="35" t="n"/>
+        <v>12126</v>
+      </c>
+      <c r="K51" s="34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L51" s="34" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M51" s="35" t="n">
+        <v>1.21</v>
+      </c>
       <c r="N51" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17278,7 +17315,7 @@
       </c>
       <c r="O51" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -17288,7 +17325,7 @@
       </c>
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением</t>
+          <t>Клапан</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
@@ -17299,7 +17336,7 @@
       <c r="D52" s="32" t="n"/>
       <c r="E52" s="32" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F52" s="32" t="inlineStr">
@@ -17311,13 +17348,13 @@
         <v>1</v>
       </c>
       <c r="H52" s="32" t="n">
-        <v>12.3</v>
+        <v>6.8</v>
       </c>
       <c r="I52" s="34" t="n">
-        <v>12724</v>
+        <v>12126</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>12724</v>
+        <v>12126</v>
       </c>
       <c r="K52" s="34" t="n"/>
       <c r="L52" s="34" t="n"/>
@@ -17329,7 +17366,7 @@
       </c>
       <c r="O52" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -17365,10 +17402,10 @@
         <v>6.8</v>
       </c>
       <c r="I53" s="34" t="n">
-        <v>12252</v>
+        <v>12126</v>
       </c>
       <c r="J53" s="34" t="n">
-        <v>12252</v>
+        <v>12126</v>
       </c>
       <c r="K53" s="34" t="n"/>
       <c r="L53" s="34" t="n"/>
@@ -17380,7 +17417,7 @@
       </c>
       <c r="O53" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -17390,14 +17427,20 @@
       </c>
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>Судовая запорная арматура</t>
-        </is>
-      </c>
-      <c r="C54" s="32" t="inlineStr"/>
-      <c r="D54" s="32" t="n"/>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>522-03.124-04</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="n">
+        <v>50</v>
+      </c>
       <c r="E54" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F54" s="32" t="inlineStr">
@@ -17409,22 +17452,22 @@
         <v>1</v>
       </c>
       <c r="H54" s="32" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="I54" s="34" t="n">
-        <v>12252</v>
+        <v>10311</v>
       </c>
       <c r="J54" s="34" t="n">
-        <v>12252</v>
+        <v>10311</v>
       </c>
       <c r="K54" s="34" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="L54" s="34" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M54" s="35" t="n">
-        <v>1.23</v>
+        <v>0.52</v>
       </c>
       <c r="N54" s="38" t="inlineStr">
         <is>
@@ -17433,7 +17476,7 @@
       </c>
       <c r="O54" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -17443,18 +17486,20 @@
       </c>
       <c r="B55" s="33" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Клапан педальный Ду25</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
         <is>
-          <t>587-182.126</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="n"/>
+          <t>М528-03.001</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="n">
+        <v>25</v>
+      </c>
       <c r="E55" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Педальные клапаны</t>
         </is>
       </c>
       <c r="F55" s="32" t="inlineStr">
@@ -17466,17 +17511,23 @@
         <v>1</v>
       </c>
       <c r="H55" s="32" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="I55" s="34" t="n">
-        <v>12252</v>
+        <v>9808</v>
       </c>
       <c r="J55" s="34" t="n">
-        <v>12252</v>
-      </c>
-      <c r="K55" s="34" t="n"/>
-      <c r="L55" s="34" t="n"/>
-      <c r="M55" s="35" t="n"/>
+        <v>9808</v>
+      </c>
+      <c r="K55" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L55" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M55" s="35" t="n">
+        <v>0.65</v>
+      </c>
       <c r="N55" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17484,7 +17535,7 @@
       </c>
       <c r="O55" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -17494,36 +17545,38 @@
       </c>
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
+          <t>Грибки АМГ Ду 150 (нижние)</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
         <is>
-          <t>2619802505</t>
-        </is>
-      </c>
-      <c r="D56" s="32" t="n"/>
+          <t>(541-03.316-02)</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="n">
+        <v>150</v>
+      </c>
       <c r="E56" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F56" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G56" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" s="32" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="I56" s="34" t="n">
-        <v>12252</v>
+        <v>4815</v>
       </c>
       <c r="J56" s="34" t="n">
-        <v>12252</v>
+        <v>9629</v>
       </c>
       <c r="K56" s="34" t="n"/>
       <c r="L56" s="34" t="n"/>
@@ -17535,7 +17588,7 @@
       </c>
       <c r="O56" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17545,20 +17598,16 @@
       </c>
       <c r="B57" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
-        </is>
-      </c>
-      <c r="C57" s="32" t="inlineStr">
-        <is>
-          <t>522-03.124-04</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду60</t>
+        </is>
+      </c>
+      <c r="C57" s="32" t="inlineStr"/>
       <c r="D57" s="32" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E57" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F57" s="32" t="inlineStr">
@@ -17570,22 +17619,22 @@
         <v>1</v>
       </c>
       <c r="H57" s="32" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="I57" s="34" t="n">
-        <v>10311</v>
+        <v>9563</v>
       </c>
       <c r="J57" s="34" t="n">
-        <v>10311</v>
+        <v>9563</v>
       </c>
       <c r="K57" s="34" t="n">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="L57" s="34" t="n">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="M57" s="35" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="N57" s="38" t="inlineStr">
         <is>
@@ -17594,7 +17643,7 @@
       </c>
       <c r="O57" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -17604,20 +17653,16 @@
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25</t>
-        </is>
-      </c>
-      <c r="C58" s="32" t="inlineStr">
-        <is>
-          <t>М528-03.001</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду60</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr"/>
       <c r="D58" s="32" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>Педальные клапаны</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -17629,22 +17674,22 @@
         <v>1</v>
       </c>
       <c r="H58" s="32" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I58" s="34" t="n">
-        <v>9910</v>
+        <v>9563</v>
       </c>
       <c r="J58" s="34" t="n">
-        <v>9910</v>
+        <v>9563</v>
       </c>
       <c r="K58" s="34" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="L58" s="34" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="M58" s="35" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="N58" s="38" t="inlineStr">
         <is>
@@ -17653,7 +17698,7 @@
       </c>
       <c r="O58" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -17663,38 +17708,38 @@
       </c>
       <c r="B59" s="33" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 150 (нижние)</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>(541-03.316-02)</t>
+          <t>554-03.909-03</t>
         </is>
       </c>
       <c r="D59" s="32" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G59" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H59" s="32" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="I59" s="34" t="n">
-        <v>4865</v>
+        <v>3031</v>
       </c>
       <c r="J59" s="34" t="n">
-        <v>9730</v>
+        <v>9094</v>
       </c>
       <c r="K59" s="34" t="n"/>
       <c r="L59" s="34" t="n"/>
@@ -17716,16 +17761,20 @@
       </c>
       <c r="B60" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
-        </is>
-      </c>
-      <c r="C60" s="32" t="inlineStr"/>
+          <t>Стакан переборочный Ду25Ру100</t>
+        </is>
+      </c>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>554-35.156</t>
+        </is>
+      </c>
       <c r="D60" s="32" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E60" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="F60" s="32" t="inlineStr">
@@ -17734,26 +17783,20 @@
         </is>
       </c>
       <c r="G60" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" s="32" t="n">
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="I60" s="34" t="n">
-        <v>9563</v>
+        <v>4458</v>
       </c>
       <c r="J60" s="34" t="n">
-        <v>9563</v>
-      </c>
-      <c r="K60" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L60" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="M60" s="35" t="n">
-        <v>0.53</v>
-      </c>
+        <v>8916</v>
+      </c>
+      <c r="K60" s="34" t="n"/>
+      <c r="L60" s="34" t="n"/>
+      <c r="M60" s="35" t="n"/>
       <c r="N60" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17761,7 +17804,7 @@
       </c>
       <c r="O60" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17771,44 +17814,42 @@
       </c>
       <c r="B61" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
-        </is>
-      </c>
-      <c r="C61" s="32" t="inlineStr"/>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
+        </is>
+      </c>
+      <c r="C61" s="32" t="inlineStr">
+        <is>
+          <t>541-03.224</t>
+        </is>
+      </c>
       <c r="D61" s="32" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F61" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G61" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H61" s="32" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="I61" s="34" t="n">
-        <v>9563</v>
+        <v>2675</v>
       </c>
       <c r="J61" s="34" t="n">
-        <v>9563</v>
-      </c>
-      <c r="K61" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L61" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="M61" s="35" t="n">
-        <v>0.53</v>
-      </c>
+        <v>8024</v>
+      </c>
+      <c r="K61" s="34" t="n"/>
+      <c r="L61" s="34" t="n"/>
+      <c r="M61" s="35" t="n"/>
       <c r="N61" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17816,7 +17857,7 @@
       </c>
       <c r="O61" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17826,20 +17867,20 @@
       </c>
       <c r="B62" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C62" s="32" t="inlineStr">
         <is>
-          <t>554-03.909-03</t>
+          <t>521-3М.123</t>
         </is>
       </c>
       <c r="D62" s="32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E62" s="32" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F62" s="32" t="inlineStr">
@@ -17848,16 +17889,16 @@
         </is>
       </c>
       <c r="G62" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62" s="32" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="I62" s="34" t="n">
-        <v>3063</v>
+        <v>7614</v>
       </c>
       <c r="J62" s="34" t="n">
-        <v>9189</v>
+        <v>7614</v>
       </c>
       <c r="K62" s="34" t="n"/>
       <c r="L62" s="34" t="n"/>
@@ -17869,7 +17910,7 @@
       </c>
       <c r="O62" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -17879,12 +17920,12 @@
       </c>
       <c r="B63" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду25Ру100</t>
+          <t>Клапан фланцевый угловой Ду25</t>
         </is>
       </c>
       <c r="C63" s="32" t="inlineStr">
         <is>
-          <t>554-35.156</t>
+          <t>521-3М539</t>
         </is>
       </c>
       <c r="D63" s="32" t="n">
@@ -17892,7 +17933,7 @@
       </c>
       <c r="E63" s="32" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F63" s="32" t="inlineStr">
@@ -17901,20 +17942,26 @@
         </is>
       </c>
       <c r="G63" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" s="32" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="I63" s="34" t="n">
-        <v>4505</v>
+        <v>7614</v>
       </c>
       <c r="J63" s="34" t="n">
-        <v>9009</v>
-      </c>
-      <c r="K63" s="34" t="n"/>
-      <c r="L63" s="34" t="n"/>
-      <c r="M63" s="35" t="n"/>
+        <v>7614</v>
+      </c>
+      <c r="K63" s="34" t="n">
+        <v>9600</v>
+      </c>
+      <c r="L63" s="34" t="n">
+        <v>9600</v>
+      </c>
+      <c r="M63" s="35" t="n">
+        <v>0.79</v>
+      </c>
       <c r="N63" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17922,7 +17969,7 @@
       </c>
       <c r="O63" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -17932,38 +17979,32 @@
       </c>
       <c r="B64" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
-        </is>
-      </c>
-      <c r="C64" s="32" t="inlineStr">
-        <is>
-          <t>541-03.224</t>
-        </is>
-      </c>
-      <c r="D64" s="32" t="n">
-        <v>32</v>
-      </c>
+          <t>Эжектор ВЭЖ 6,3</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr"/>
+      <c r="D64" s="32" t="n"/>
       <c r="E64" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Эжекторы</t>
         </is>
       </c>
       <c r="F64" s="32" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G64" s="34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H64" s="32" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="I64" s="34" t="n">
-        <v>2703</v>
+        <v>7133</v>
       </c>
       <c r="J64" s="34" t="n">
-        <v>8108</v>
+        <v>7133</v>
       </c>
       <c r="K64" s="34" t="n"/>
       <c r="L64" s="34" t="n"/>
@@ -17985,20 +18026,16 @@
       </c>
       <c r="B65" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
-        </is>
-      </c>
-      <c r="C65" s="32" t="inlineStr">
-        <is>
-          <t>521-3М.123</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду 50, без клиньев</t>
+        </is>
+      </c>
+      <c r="C65" s="32" t="inlineStr"/>
       <c r="D65" s="32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E65" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F65" s="32" t="inlineStr">
@@ -18010,17 +18047,23 @@
         <v>1</v>
       </c>
       <c r="H65" s="32" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="I65" s="34" t="n">
-        <v>7614</v>
+        <v>6403</v>
       </c>
       <c r="J65" s="34" t="n">
-        <v>7614</v>
-      </c>
-      <c r="K65" s="34" t="n"/>
-      <c r="L65" s="34" t="n"/>
-      <c r="M65" s="35" t="n"/>
+        <v>6403</v>
+      </c>
+      <c r="K65" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L65" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M65" s="35" t="n">
+        <v>0.26</v>
+      </c>
       <c r="N65" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -18028,7 +18071,7 @@
       </c>
       <c r="O65" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -18038,20 +18081,20 @@
       </c>
       <c r="B66" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
+          <t>Стакан переборочный Ду10Ру100</t>
         </is>
       </c>
       <c r="C66" s="32" t="inlineStr">
         <is>
-          <t>521-3М539</t>
+          <t>554-35.265</t>
         </is>
       </c>
       <c r="D66" s="32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E66" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="F66" s="32" t="inlineStr">
@@ -18060,26 +18103,20 @@
         </is>
       </c>
       <c r="G66" s="34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H66" s="32" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="I66" s="34" t="n">
-        <v>7614</v>
+        <v>1070</v>
       </c>
       <c r="J66" s="34" t="n">
-        <v>7614</v>
-      </c>
-      <c r="K66" s="34" t="n">
-        <v>9600</v>
-      </c>
-      <c r="L66" s="34" t="n">
-        <v>9600</v>
-      </c>
-      <c r="M66" s="35" t="n">
-        <v>0.79</v>
-      </c>
+        <v>5350</v>
+      </c>
+      <c r="K66" s="34" t="n"/>
+      <c r="L66" s="34" t="n"/>
+      <c r="M66" s="35" t="n"/>
       <c r="N66" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -18087,7 +18124,7 @@
       </c>
       <c r="O66" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -18097,32 +18134,36 @@
       </c>
       <c r="B67" s="33" t="inlineStr">
         <is>
-          <t>Эжектор ВЭЖ 6,3</t>
-        </is>
-      </c>
-      <c r="C67" s="32" t="inlineStr"/>
+          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
+        </is>
+      </c>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>521-03.472-01</t>
+        </is>
+      </c>
       <c r="D67" s="32" t="n"/>
       <c r="E67" s="32" t="inlineStr">
         <is>
-          <t>Эжекторы</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F67" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>нержавейка</t>
         </is>
       </c>
       <c r="G67" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="32" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="I67" s="34" t="n">
-        <v>7207</v>
+        <v>3954</v>
       </c>
       <c r="J67" s="34" t="n">
-        <v>7207</v>
+        <v>3954</v>
       </c>
       <c r="K67" s="34" t="n"/>
       <c r="L67" s="34" t="n"/>
@@ -18134,7 +18175,7 @@
       </c>
       <c r="O67" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -18144,43 +18185,47 @@
       </c>
       <c r="B68" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 50, без клиньев</t>
-        </is>
-      </c>
-      <c r="C68" s="32" t="inlineStr"/>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>525-35.2634</t>
+        </is>
+      </c>
       <c r="D68" s="32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E68" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Редукционные клапаны</t>
         </is>
       </c>
       <c r="F68" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G68" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="32" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="I68" s="34" t="n">
-        <v>6403</v>
+        <v>1667</v>
       </c>
       <c r="J68" s="34" t="n">
-        <v>6403</v>
+        <v>1667</v>
       </c>
       <c r="K68" s="34" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="L68" s="34" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="M68" s="35" t="n">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="N68" s="38" t="inlineStr">
         <is>
@@ -18189,7 +18234,7 @@
       </c>
       <c r="O68" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -18199,12 +18244,12 @@
       </c>
       <c r="B69" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду10Ру100</t>
+          <t>Клапан редукционный штуцерный угловой Ду10Ру200…30 с манометром</t>
         </is>
       </c>
       <c r="C69" s="32" t="inlineStr">
         <is>
-          <t>554-35.265</t>
+          <t>525-35.2634-04</t>
         </is>
       </c>
       <c r="D69" s="32" t="n">
@@ -18212,29 +18257,35 @@
       </c>
       <c r="E69" s="32" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Редукционные клапаны</t>
         </is>
       </c>
       <c r="F69" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G69" s="34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H69" s="32" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="I69" s="34" t="n">
-        <v>1081</v>
+        <v>1667</v>
       </c>
       <c r="J69" s="34" t="n">
-        <v>5405</v>
-      </c>
-      <c r="K69" s="34" t="n"/>
-      <c r="L69" s="34" t="n"/>
-      <c r="M69" s="35" t="n"/>
+        <v>1667</v>
+      </c>
+      <c r="K69" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L69" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="M69" s="35" t="n">
+        <v>0.11</v>
+      </c>
       <c r="N69" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -18242,63 +18293,12 @@
       </c>
       <c r="O69" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="32" t="n">
-        <v>66</v>
-      </c>
-      <c r="B70" s="33" t="inlineStr">
-        <is>
-          <t>Клапан штуцерный угловой Ду НЕРЖ</t>
-        </is>
-      </c>
-      <c r="C70" s="32" t="inlineStr">
-        <is>
-          <t>521-03.472-01</t>
-        </is>
-      </c>
-      <c r="D70" s="32" t="n"/>
-      <c r="E70" s="32" t="inlineStr">
-        <is>
-          <t>Штуцерная угловая</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>нержавейка</t>
-        </is>
-      </c>
-      <c r="G70" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I70" s="34" t="n">
-        <v>3954</v>
-      </c>
-      <c r="J70" s="34" t="n">
-        <v>3954</v>
-      </c>
-      <c r="K70" s="34" t="n"/>
-      <c r="L70" s="34" t="n"/>
-      <c r="M70" s="35" t="n"/>
-      <c r="N70" s="38" t="inlineStr">
-        <is>
-          <t>оценка по цене килограмма</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O70"/>
+  <autoFilter ref="A4:O69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
+++ b/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="По группам" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Цена по чертежу" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Цена по типу" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Оценка по килограмму" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По группам" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цена по чертежу" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цена по типу" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Оценка по килограмму" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Цена по чертежу'!$A$4:$O$80</definedName>
@@ -629,13 +629,13 @@
         <v>1387</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>3264</v>
+        <v>3289</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>7542925</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>0.1547868514052207</v>
+        <v>0.158443736700291</v>
       </c>
     </row>
     <row r="7">
@@ -651,13 +651,13 @@
         <v>1184</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>17360</v>
+        <v>18922</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>29233750</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.5998999217501658</v>
+        <v>0.614072735412606</v>
       </c>
     </row>
     <row r="8">
@@ -673,13 +673,13 @@
         <v>331</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>6671</v>
+        <v>6781</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>11954369.86280412</v>
+        <v>10829656.16263881</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.245313226844614</v>
+        <v>0.2274835278871031</v>
       </c>
     </row>
     <row r="9">
@@ -717,10 +717,10 @@
         <v>2902</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>27295</v>
+        <v>28992</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>48731044.8628041</v>
+        <v>47606331.16263881</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>48731045</v>
+        <v>47606331</v>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B15" s="18" t="n">
-        <v>8687295</v>
+        <v>7562581</v>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B16" s="21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B17" s="18" t="n">
-        <v>1783</v>
+        <v>1656</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>12948348</v>
+        <v>13775052</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>16377129</v>
+        <v>17395267</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -904,13 +904,13 @@
         <v>401000</v>
       </c>
       <c r="C25" s="23" t="n">
-        <v>48731045</v>
+        <v>47606331</v>
       </c>
       <c r="D25" s="24" t="n">
-        <v>0.008228840590817684</v>
+        <v>0.008423249391557874</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>14.7</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="26">
@@ -923,13 +923,13 @@
         <v>632000</v>
       </c>
       <c r="C26" s="27" t="n">
-        <v>48731045</v>
+        <v>47606331</v>
       </c>
       <c r="D26" s="28" t="n">
-        <v>0.01296914527031615</v>
+        <v>0.01327554517572214</v>
       </c>
       <c r="E26" s="29" t="n">
-        <v>23.2</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="27">
@@ -942,19 +942,19 @@
         <v>541000</v>
       </c>
       <c r="C27" s="27" t="n">
-        <v>48731045</v>
+        <v>47606331</v>
       </c>
       <c r="D27" s="28" t="n">
-        <v>0.01110175251778645</v>
+        <v>0.01136403471529379</v>
       </c>
       <c r="E27" s="29" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>За базу взят весь перечень — 27.30 т на 48.7 млн. В усиленный контейнер входит 26,35 т из них, на долю логистики эта разница не влияет.</t>
+          <t>За базу взят весь перечень — 28.99 т на 47.6 млн. В усиленный контейнер входит 26,35 т из них, на долю логистики эта разница не влияет.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>— Вся арматура и фильтры на складе по ценам конкурента — 48.7 млн руб при весе 27.3 т. По нашим учетным ценам те же позиции стоят 40.0 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
+          <t>— Вся арматура и фильтры на складе по ценам конкурента — 47.6 млн руб при весе 29.0 т. По нашим учетным ценам те же позиции стоят 40.0 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="30" t="inlineStr">
         <is>
-          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 783 руб  а довезти его до Петербурга стоит 14.7 руб. Отсюда и доля.</t>
+          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 656 руб  а довезти его до Петербурга стоит 13.8 руб. Отсюда и доля.</t>
         </is>
       </c>
     </row>
@@ -1185,10 +1185,10 @@
         <v>100</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>1748</v>
+        <v>1788</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>2419192</v>
+        <v>2428645</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>2087200</v>
@@ -1197,7 +1197,7 @@
         <v>1.16</v>
       </c>
       <c r="H7" s="27" t="n">
-        <v>1384</v>
+        <v>1358</v>
       </c>
       <c r="I7" s="26" t="n">
         <v>3</v>
@@ -1216,19 +1216,19 @@
         <v>300</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>4199</v>
+        <v>4257</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>8161695</v>
+        <v>8147206</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>6826600</v>
       </c>
       <c r="G8" s="31" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H8" s="27" t="n">
-        <v>1944</v>
+        <v>1914</v>
       </c>
       <c r="I8" s="26" t="n">
         <v>7</v>
@@ -1250,16 +1250,16 @@
         <v>106</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>189018</v>
+        <v>175509</v>
       </c>
       <c r="F9" s="27" t="n">
         <v>74250</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="H9" s="27" t="n">
-        <v>1783</v>
+        <v>1656</v>
       </c>
       <c r="I9" s="26" t="n">
         <v>0</v>
@@ -1278,19 +1278,19 @@
         <v>225</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>10703</v>
+        <v>12294</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>16440392</v>
+        <v>15474969</v>
       </c>
       <c r="F10" s="27" t="n">
         <v>12761000</v>
       </c>
       <c r="G10" s="31" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="H10" s="27" t="n">
-        <v>1536</v>
+        <v>1259</v>
       </c>
       <c r="I10" s="26" t="n">
         <v>0</v>
@@ -1309,10 +1309,10 @@
         <v>28</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>1828</v>
+        <v>1834</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>3343718</v>
+        <v>3340257</v>
       </c>
       <c r="F11" s="27" t="n">
         <v>2338000</v>
@@ -1321,7 +1321,7 @@
         <v>1.43</v>
       </c>
       <c r="H11" s="27" t="n">
-        <v>1829</v>
+        <v>1821</v>
       </c>
       <c r="I11" s="26" t="n">
         <v>0</v>
@@ -1374,14 +1374,14 @@
         <v>363</v>
       </c>
       <c r="E13" s="27" t="n">
-        <v>646941</v>
+        <v>600706</v>
       </c>
       <c r="F13" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="31" t="n"/>
       <c r="H13" s="27" t="n">
-        <v>1783</v>
+        <v>1656</v>
       </c>
       <c r="I13" s="26" t="n">
         <v>0</v>
@@ -1503,7 +1503,7 @@
         <v>0.86</v>
       </c>
       <c r="H17" s="27" t="n">
-        <v>3093</v>
+        <v>3096</v>
       </c>
       <c r="I17" s="26" t="n">
         <v>1</v>
@@ -1525,14 +1525,14 @@
         <v>52</v>
       </c>
       <c r="E18" s="27" t="n">
-        <v>92904</v>
+        <v>86265</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="31" t="n"/>
       <c r="H18" s="27" t="n">
-        <v>1783</v>
+        <v>1656</v>
       </c>
       <c r="I18" s="26" t="n">
         <v>0</v>
@@ -1554,16 +1554,16 @@
         <v>110</v>
       </c>
       <c r="E19" s="27" t="n">
-        <v>195438</v>
+        <v>181470</v>
       </c>
       <c r="F19" s="27" t="n">
         <v>415000</v>
       </c>
       <c r="G19" s="31" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="H19" s="27" t="n">
-        <v>1783</v>
+        <v>1656</v>
       </c>
       <c r="I19" s="26" t="n">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>33</v>
       </c>
       <c r="E21" s="27" t="n">
-        <v>58132</v>
+        <v>53977</v>
       </c>
       <c r="F21" s="27" t="n">
         <v>60000</v>
       </c>
       <c r="G21" s="31" t="n">
-        <v>0.97</v>
+        <v>0.9</v>
       </c>
       <c r="H21" s="27" t="n">
-        <v>1783</v>
+        <v>1656</v>
       </c>
       <c r="I21" s="26" t="n">
         <v>0</v>
@@ -1678,16 +1678,16 @@
         <v>346</v>
       </c>
       <c r="E23" s="27" t="n">
-        <v>617875</v>
+        <v>573717</v>
       </c>
       <c r="F23" s="27" t="n">
         <v>945000</v>
       </c>
       <c r="G23" s="31" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="H23" s="27" t="n">
-        <v>1783</v>
+        <v>1656</v>
       </c>
       <c r="I23" s="26" t="n">
         <v>0</v>
@@ -1709,14 +1709,14 @@
         <v>4</v>
       </c>
       <c r="E24" s="27" t="n">
-        <v>7133</v>
+        <v>6623</v>
       </c>
       <c r="F24" s="27" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="31" t="n"/>
       <c r="H24" s="27" t="n">
-        <v>1783</v>
+        <v>1656</v>
       </c>
       <c r="I24" s="26" t="n">
         <v>0</v>
@@ -1738,16 +1738,16 @@
         <v>170</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>302524</v>
+        <v>280903</v>
       </c>
       <c r="F25" s="27" t="n">
         <v>47000</v>
       </c>
       <c r="G25" s="31" t="n">
-        <v>6.44</v>
+        <v>5.98</v>
       </c>
       <c r="H25" s="27" t="n">
-        <v>1783</v>
+        <v>1656</v>
       </c>
       <c r="I25" s="26" t="n">
         <v>0</v>
@@ -2732,7 +2732,7 @@
         <v>5</v>
       </c>
       <c r="H19" s="32" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I19" s="34" t="n">
         <v>24500</v>
@@ -3322,7 +3322,7 @@
         <v>2</v>
       </c>
       <c r="H29" s="32" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I29" s="34" t="n">
         <v>24500</v>
@@ -3670,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="32" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I35" s="34" t="n">
         <v>20000</v>
@@ -6679,7 +6679,7 @@
         <v>43</v>
       </c>
       <c r="H9" s="32" t="n">
-        <v>19.2</v>
+        <v>32</v>
       </c>
       <c r="I9" s="34" t="n">
         <v>37500</v>
@@ -6734,7 +6734,7 @@
         <v>44</v>
       </c>
       <c r="H10" s="32" t="n">
-        <v>11.7</v>
+        <v>24</v>
       </c>
       <c r="I10" s="34" t="n">
         <v>30000</v>
@@ -7221,7 +7221,7 @@
         <v>18</v>
       </c>
       <c r="H19" s="32" t="n">
-        <v>11.7</v>
+        <v>24</v>
       </c>
       <c r="I19" s="34" t="n">
         <v>30000</v>
@@ -7276,7 +7276,7 @@
         <v>16</v>
       </c>
       <c r="H20" s="32" t="n">
-        <v>7.4</v>
+        <v>17.9</v>
       </c>
       <c r="I20" s="34" t="n">
         <v>31250</v>
@@ -7441,7 +7441,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="32" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I23" s="34" t="n">
         <v>37500</v>
@@ -7594,7 +7594,7 @@
         <v>2</v>
       </c>
       <c r="H26" s="32" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="I26" s="34" t="n">
         <v>150000</v>
@@ -7873,7 +7873,7 @@
         <v>6</v>
       </c>
       <c r="H31" s="32" t="n">
-        <v>19.2</v>
+        <v>32</v>
       </c>
       <c r="I31" s="34" t="n">
         <v>37500</v>
@@ -7928,7 +7928,7 @@
         <v>13</v>
       </c>
       <c r="H32" s="32" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I32" s="34" t="n">
         <v>16000</v>
@@ -8826,7 +8826,7 @@
         <v>8</v>
       </c>
       <c r="H48" s="32" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I48" s="34" t="n">
         <v>11000</v>
@@ -8940,7 +8940,7 @@
         <v>6</v>
       </c>
       <c r="H50" s="32" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I50" s="34" t="n">
         <v>14000</v>
@@ -8995,7 +8995,7 @@
         <v>6</v>
       </c>
       <c r="H51" s="32" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I51" s="34" t="n">
         <v>14000</v>
@@ -9109,7 +9109,7 @@
         <v>2</v>
       </c>
       <c r="H53" s="32" t="n">
-        <v>19.2</v>
+        <v>32</v>
       </c>
       <c r="I53" s="34" t="n">
         <v>37500</v>
@@ -9500,7 +9500,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="32" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="I60" s="34" t="n">
         <v>60000</v>
@@ -9559,7 +9559,7 @@
         <v>1</v>
       </c>
       <c r="H61" s="32" t="n">
-        <v>68.7</v>
+        <v>75</v>
       </c>
       <c r="I61" s="34" t="n">
         <v>60000</v>
@@ -9724,7 +9724,7 @@
         <v>3</v>
       </c>
       <c r="H64" s="32" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I64" s="34" t="n">
         <v>20000</v>
@@ -9779,7 +9779,7 @@
         <v>2</v>
       </c>
       <c r="H65" s="32" t="n">
-        <v>11.7</v>
+        <v>24</v>
       </c>
       <c r="I65" s="34" t="n">
         <v>30000</v>
@@ -10005,7 +10005,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="32" t="n">
-        <v>7.8</v>
+        <v>14</v>
       </c>
       <c r="I69" s="34" t="n">
         <v>47500</v>
@@ -10351,7 +10351,7 @@
         <v>2</v>
       </c>
       <c r="H75" s="32" t="n">
-        <v>19.2</v>
+        <v>32</v>
       </c>
       <c r="I75" s="34" t="n">
         <v>20000</v>
@@ -10465,7 +10465,7 @@
         <v>1</v>
       </c>
       <c r="H77" s="32" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I77" s="34" t="n">
         <v>37500</v>
@@ -10760,7 +10760,7 @@
         <v>2</v>
       </c>
       <c r="H82" s="32" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I82" s="34" t="n">
         <v>14000</v>
@@ -11835,7 +11835,7 @@
         <v>1</v>
       </c>
       <c r="H101" s="32" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="I101" s="34" t="n">
         <v>20000</v>
@@ -12161,7 +12161,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="32" t="n">
-        <v>11.7</v>
+        <v>24</v>
       </c>
       <c r="I107" s="34" t="n">
         <v>19000</v>
@@ -12564,7 +12564,7 @@
         <v>1</v>
       </c>
       <c r="H114" s="32" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I114" s="34" t="n">
         <v>12800</v>
@@ -13197,7 +13197,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="32" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="I125" s="34" t="n">
         <v>9600</v>
@@ -14768,10 +14768,10 @@
         <v>192</v>
       </c>
       <c r="I5" s="34" t="n">
-        <v>294934</v>
+        <v>241680</v>
       </c>
       <c r="J5" s="34" t="n">
-        <v>3834142</v>
+        <v>3141845</v>
       </c>
       <c r="K5" s="34" t="n">
         <v>200000</v>
@@ -14780,7 +14780,7 @@
         <v>2600000</v>
       </c>
       <c r="M5" s="35" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="N5" s="38" t="inlineStr">
         <is>
@@ -14799,16 +14799,20 @@
       </c>
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>Клинкет Ду 300</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="inlineStr"/>
+          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>ИШТЛ 491112-003-04</t>
+        </is>
+      </c>
       <c r="D6" s="32" t="n">
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F6" s="32" t="inlineStr">
@@ -14817,25 +14821,25 @@
         </is>
       </c>
       <c r="G6" s="34" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>192</v>
+        <v>5.7</v>
       </c>
       <c r="I6" s="34" t="n">
-        <v>294934</v>
+        <v>38667</v>
       </c>
       <c r="J6" s="34" t="n">
-        <v>884802</v>
+        <v>773347</v>
       </c>
       <c r="K6" s="34" t="n">
-        <v>250000</v>
+        <v>30000</v>
       </c>
       <c r="L6" s="34" t="n">
-        <v>750000</v>
+        <v>600000</v>
       </c>
       <c r="M6" s="35" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="N6" s="38" t="inlineStr">
         <is>
@@ -14844,7 +14848,7 @@
       </c>
       <c r="O6" s="32" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -14854,15 +14858,13 @@
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>Задвижки (желтая) ок. крышек</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>544-03.046</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="n"/>
+          <t>Клинкет Ду 300</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr"/>
+      <c r="D7" s="32" t="n">
+        <v>300</v>
+      </c>
       <c r="E7" s="32" t="inlineStr">
         <is>
           <t>Клинкеты</t>
@@ -14870,24 +14872,30 @@
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G7" s="34" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H7" s="32" t="n">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="I7" s="34" t="n">
-        <v>61445</v>
+        <v>241680</v>
       </c>
       <c r="J7" s="34" t="n">
-        <v>798780</v>
-      </c>
-      <c r="K7" s="34" t="n"/>
-      <c r="L7" s="34" t="n"/>
-      <c r="M7" s="35" t="n"/>
+        <v>725041</v>
+      </c>
+      <c r="K7" s="34" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L7" s="34" t="n">
+        <v>750000</v>
+      </c>
+      <c r="M7" s="35" t="n">
+        <v>0.97</v>
+      </c>
       <c r="N7" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -14895,7 +14903,7 @@
       </c>
       <c r="O7" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -14905,48 +14913,40 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>Клапан запорн.с присоед.под дюрит прох. Ду65</t>
+          <t>Задвижки (желтая) ок. крышек</t>
         </is>
       </c>
       <c r="C8" s="32" t="inlineStr">
         <is>
-          <t>ИШТЛ 491112-003-04</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="n">
-        <v>65</v>
-      </c>
+          <t>544-03.046</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="n"/>
       <c r="E8" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F8" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G8" s="34" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H8" s="32" t="n">
-        <v>5.7</v>
+        <v>40</v>
       </c>
       <c r="I8" s="34" t="n">
-        <v>38667</v>
+        <v>50350</v>
       </c>
       <c r="J8" s="34" t="n">
-        <v>773347</v>
-      </c>
-      <c r="K8" s="34" t="n">
-        <v>30000</v>
-      </c>
-      <c r="L8" s="34" t="n">
-        <v>600000</v>
-      </c>
-      <c r="M8" s="35" t="n">
-        <v>1.29</v>
-      </c>
+        <v>654551</v>
+      </c>
+      <c r="K8" s="34" t="n"/>
+      <c r="L8" s="34" t="n"/>
+      <c r="M8" s="35" t="n"/>
       <c r="N8" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -14954,7 +14954,7 @@
       </c>
       <c r="O8" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -14988,10 +14988,10 @@
         <v>110</v>
       </c>
       <c r="I9" s="34" t="n">
-        <v>213834</v>
+        <v>210514</v>
       </c>
       <c r="J9" s="34" t="n">
-        <v>641503</v>
+        <v>631542</v>
       </c>
       <c r="K9" s="34" t="n"/>
       <c r="L9" s="34" t="n"/>
@@ -15013,20 +15013,16 @@
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25 новый приход</t>
-        </is>
-      </c>
-      <c r="C10" s="32" t="inlineStr">
-        <is>
-          <t>М528-03.001</t>
-        </is>
-      </c>
+          <t>Фильтр заборной воды ДУ 150</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr"/>
       <c r="D10" s="32" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="E10" s="32" t="inlineStr">
         <is>
-          <t>Педальные клапаны</t>
+          <t>Фильтры забортной воды</t>
         </is>
       </c>
       <c r="F10" s="32" t="inlineStr">
@@ -15035,25 +15031,25 @@
         </is>
       </c>
       <c r="G10" s="34" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="H10" s="32" t="n">
-        <v>5.5</v>
+        <v>64</v>
       </c>
       <c r="I10" s="34" t="n">
-        <v>9808</v>
+        <v>116563</v>
       </c>
       <c r="J10" s="34" t="n">
-        <v>608068</v>
+        <v>582815</v>
       </c>
       <c r="K10" s="34" t="n">
-        <v>15000</v>
+        <v>90000</v>
       </c>
       <c r="L10" s="34" t="n">
-        <v>930000</v>
+        <v>450000</v>
       </c>
       <c r="M10" s="35" t="n">
-        <v>0.65</v>
+        <v>1.3</v>
       </c>
       <c r="N10" s="38" t="inlineStr">
         <is>
@@ -15072,16 +15068,20 @@
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>Фильтр заборной воды ДУ 150</t>
-        </is>
-      </c>
-      <c r="C11" s="32" t="inlineStr"/>
+          <t>Клапан педальный Ду25 новый приход</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
       <c r="D11" s="32" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="E11" s="32" t="inlineStr">
         <is>
-          <t>Фильтры забортной воды</t>
+          <t>Педальные клапаны</t>
         </is>
       </c>
       <c r="F11" s="32" t="inlineStr">
@@ -15090,25 +15090,25 @@
         </is>
       </c>
       <c r="G11" s="34" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="H11" s="32" t="n">
-        <v>64</v>
+        <v>5.5</v>
       </c>
       <c r="I11" s="34" t="n">
-        <v>117078</v>
+        <v>9107</v>
       </c>
       <c r="J11" s="34" t="n">
-        <v>585390</v>
+        <v>564610</v>
       </c>
       <c r="K11" s="34" t="n">
-        <v>90000</v>
+        <v>15000</v>
       </c>
       <c r="L11" s="34" t="n">
-        <v>450000</v>
+        <v>930000</v>
       </c>
       <c r="M11" s="35" t="n">
-        <v>1.3</v>
+        <v>0.61</v>
       </c>
       <c r="N11" s="38" t="inlineStr">
         <is>
@@ -15127,42 +15127,48 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
         </is>
       </c>
       <c r="C12" s="32" t="inlineStr">
         <is>
-          <t>(541-03.218)</t>
+          <t>522-03.122-04</t>
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E12" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G12" s="34" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H12" s="32" t="n">
-        <v>11.2</v>
+        <v>5.5</v>
       </c>
       <c r="I12" s="34" t="n">
-        <v>19972</v>
+        <v>37311</v>
       </c>
       <c r="J12" s="34" t="n">
-        <v>379463</v>
-      </c>
-      <c r="K12" s="34" t="n"/>
-      <c r="L12" s="34" t="n"/>
-      <c r="M12" s="35" t="n"/>
+        <v>373106</v>
+      </c>
+      <c r="K12" s="34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L12" s="34" t="n">
+        <v>200000</v>
+      </c>
+      <c r="M12" s="35" t="n">
+        <v>1.87</v>
+      </c>
       <c r="N12" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15170,7 +15176,7 @@
       </c>
       <c r="O12" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -15180,48 +15186,42 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду80</t>
         </is>
       </c>
       <c r="C13" s="32" t="inlineStr">
         <is>
-          <t>522-03.122-04</t>
+          <t>(541-03.218)</t>
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E13" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G13" s="34" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H13" s="32" t="n">
-        <v>5.5</v>
+        <v>11.2</v>
       </c>
       <c r="I13" s="34" t="n">
-        <v>37311</v>
+        <v>18544</v>
       </c>
       <c r="J13" s="34" t="n">
-        <v>373106</v>
-      </c>
-      <c r="K13" s="34" t="n">
-        <v>20000</v>
-      </c>
-      <c r="L13" s="34" t="n">
-        <v>200000</v>
-      </c>
-      <c r="M13" s="35" t="n">
-        <v>1.87</v>
-      </c>
+        <v>352343</v>
+      </c>
+      <c r="K13" s="34" t="n"/>
+      <c r="L13" s="34" t="n"/>
+      <c r="M13" s="35" t="n"/>
       <c r="N13" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="O13" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -15263,10 +15263,10 @@
         <v>228</v>
       </c>
       <c r="I14" s="34" t="n">
-        <v>350234</v>
+        <v>286995</v>
       </c>
       <c r="J14" s="34" t="n">
-        <v>350234</v>
+        <v>286995</v>
       </c>
       <c r="K14" s="34" t="n">
         <v>300000</v>
@@ -15275,7 +15275,7 @@
         <v>300000</v>
       </c>
       <c r="M14" s="35" t="n">
-        <v>1.17</v>
+        <v>0.96</v>
       </c>
       <c r="N14" s="38" t="inlineStr">
         <is>
@@ -15318,10 +15318,10 @@
         <v>135.3</v>
       </c>
       <c r="I15" s="34" t="n">
-        <v>241182</v>
+        <v>223945</v>
       </c>
       <c r="J15" s="34" t="n">
-        <v>241182</v>
+        <v>223945</v>
       </c>
       <c r="K15" s="34" t="n">
         <v>37000</v>
@@ -15330,7 +15330,7 @@
         <v>37000</v>
       </c>
       <c r="M15" s="35" t="n">
-        <v>6.52</v>
+        <v>6.05</v>
       </c>
       <c r="N15" s="38" t="inlineStr">
         <is>
@@ -15373,10 +15373,10 @@
         <v>110</v>
       </c>
       <c r="I16" s="34" t="n">
-        <v>213834</v>
+        <v>210514</v>
       </c>
       <c r="J16" s="34" t="n">
-        <v>213834</v>
+        <v>210514</v>
       </c>
       <c r="K16" s="34" t="n">
         <v>150000</v>
@@ -15385,7 +15385,7 @@
         <v>150000</v>
       </c>
       <c r="M16" s="35" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="N16" s="38" t="inlineStr">
         <is>
@@ -15428,10 +15428,10 @@
         <v>22</v>
       </c>
       <c r="I17" s="34" t="n">
-        <v>40246</v>
+        <v>40069</v>
       </c>
       <c r="J17" s="34" t="n">
-        <v>201228</v>
+        <v>200343</v>
       </c>
       <c r="K17" s="34" t="n"/>
       <c r="L17" s="34" t="n"/>
@@ -15481,10 +15481,10 @@
         <v>18.2</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>32454</v>
+        <v>30135</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>194724</v>
+        <v>180808</v>
       </c>
       <c r="K18" s="34" t="n"/>
       <c r="L18" s="34" t="n"/>
@@ -15506,20 +15506,16 @@
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
-        </is>
-      </c>
-      <c r="C19" s="32" t="inlineStr">
-        <is>
-          <t>529-03.074</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr"/>
       <c r="D19" s="32" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="E19" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F19" s="32" t="inlineStr">
@@ -15528,25 +15524,25 @@
         </is>
       </c>
       <c r="G19" s="34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H19" s="32" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I19" s="34" t="n">
-        <v>50691</v>
+        <v>25175</v>
       </c>
       <c r="J19" s="34" t="n">
-        <v>152074</v>
+        <v>176225</v>
       </c>
       <c r="K19" s="34" t="n">
-        <v>40000</v>
+        <v>27000</v>
       </c>
       <c r="L19" s="34" t="n">
-        <v>120000</v>
+        <v>189000</v>
       </c>
       <c r="M19" s="35" t="n">
-        <v>1.27</v>
+        <v>0.93</v>
       </c>
       <c r="N19" s="38" t="inlineStr">
         <is>
@@ -15555,7 +15551,7 @@
       </c>
       <c r="O19" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -15565,20 +15561,20 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>Клапан пусковой Ду32Ру125</t>
+          <t>Захлопка фланцевая горизон. Ду100 Ру10</t>
         </is>
       </c>
       <c r="C20" s="32" t="inlineStr">
         <is>
-          <t>587-03.082</t>
+          <t>529-03.074</t>
         </is>
       </c>
       <c r="D20" s="32" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="E20" s="32" t="inlineStr">
         <is>
-          <t>Пусковые клапаны</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F20" s="32" t="inlineStr">
@@ -15587,25 +15583,25 @@
         </is>
       </c>
       <c r="G20" s="34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H20" s="32" t="n">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="I20" s="34" t="n">
-        <v>15692</v>
+        <v>50691</v>
       </c>
       <c r="J20" s="34" t="n">
-        <v>125537</v>
+        <v>152074</v>
       </c>
       <c r="K20" s="34" t="n">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="L20" s="34" t="n">
-        <v>240000</v>
+        <v>120000</v>
       </c>
       <c r="M20" s="35" t="n">
-        <v>0.52</v>
+        <v>1.27</v>
       </c>
       <c r="N20" s="38" t="inlineStr">
         <is>
@@ -15624,20 +15620,20 @@
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду25</t>
+          <t>Клапан пусковой Ду32Ру125</t>
         </is>
       </c>
       <c r="C21" s="32" t="inlineStr">
         <is>
-          <t>521-3М539</t>
+          <t>587-03.082</t>
         </is>
       </c>
       <c r="D21" s="32" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E21" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Пусковые клапаны</t>
         </is>
       </c>
       <c r="F21" s="32" t="inlineStr">
@@ -15646,25 +15642,25 @@
         </is>
       </c>
       <c r="G21" s="34" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H21" s="32" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I21" s="34" t="n">
-        <v>7614</v>
+        <v>14571</v>
       </c>
       <c r="J21" s="34" t="n">
-        <v>98980</v>
+        <v>116565</v>
       </c>
       <c r="K21" s="34" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="L21" s="34" t="n">
-        <v>260000</v>
+        <v>240000</v>
       </c>
       <c r="M21" s="35" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="N21" s="38" t="inlineStr">
         <is>
@@ -15683,16 +15679,20 @@
       </c>
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
-        </is>
-      </c>
-      <c r="C22" s="32" t="inlineStr"/>
+          <t>Клапан фланцевый угловой Ду25</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>521-3М539</t>
+        </is>
+      </c>
       <c r="D22" s="32" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E22" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая, угол или проход не указан</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F22" s="32" t="inlineStr">
@@ -15701,25 +15701,25 @@
         </is>
       </c>
       <c r="G22" s="34" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H22" s="32" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="I22" s="34" t="n">
-        <v>16346</v>
+        <v>7469</v>
       </c>
       <c r="J22" s="34" t="n">
-        <v>98075</v>
+        <v>97097</v>
       </c>
       <c r="K22" s="34" t="n">
-        <v>7500</v>
+        <v>20000</v>
       </c>
       <c r="L22" s="34" t="n">
-        <v>45000</v>
+        <v>260000</v>
       </c>
       <c r="M22" s="35" t="n">
-        <v>2.18</v>
+        <v>0.37</v>
       </c>
       <c r="N22" s="38" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
       </c>
       <c r="O22" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -15738,16 +15738,16 @@
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная фланцевая Ду70 Ру6</t>
+          <t>Клапан невозвратно-приемный фланцевый Ду 50 Ру1 (522-35.4043-01)</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr"/>
       <c r="D23" s="32" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E23" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Фланцевая, угол или проход не указан</t>
         </is>
       </c>
       <c r="F23" s="32" t="inlineStr">
@@ -15756,25 +15756,25 @@
         </is>
       </c>
       <c r="G23" s="34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H23" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I23" s="34" t="n">
-        <v>13423</v>
+        <v>15178</v>
       </c>
       <c r="J23" s="34" t="n">
-        <v>93962</v>
+        <v>91066</v>
       </c>
       <c r="K23" s="34" t="n">
-        <v>27000</v>
+        <v>7500</v>
       </c>
       <c r="L23" s="34" t="n">
-        <v>189000</v>
+        <v>45000</v>
       </c>
       <c r="M23" s="35" t="n">
-        <v>0.5</v>
+        <v>2.02</v>
       </c>
       <c r="N23" s="38" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
       </c>
       <c r="O23" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -15909,42 +15909,42 @@
       </c>
       <c r="B26" s="33" t="inlineStr">
         <is>
-          <t>Клапан проходной фланцевый сталь</t>
-        </is>
-      </c>
-      <c r="C26" s="32" t="inlineStr"/>
-      <c r="D26" s="32" t="n"/>
+          <t>Захлопка фланцевая вертикальная Ду100</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>529-03.003</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="n">
+        <v>100</v>
+      </c>
       <c r="E26" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая проходная</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F26" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G26" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="32" t="n">
-        <v>20</v>
+        <v>33.7</v>
       </c>
       <c r="I26" s="34" t="n">
-        <v>38879</v>
+        <v>77650</v>
       </c>
       <c r="J26" s="34" t="n">
-        <v>77758</v>
-      </c>
-      <c r="K26" s="34" t="n">
-        <v>18000</v>
-      </c>
-      <c r="L26" s="34" t="n">
-        <v>36000</v>
-      </c>
-      <c r="M26" s="35" t="n">
-        <v>2.16</v>
-      </c>
+        <v>77650</v>
+      </c>
+      <c r="K26" s="34" t="n"/>
+      <c r="L26" s="34" t="n"/>
+      <c r="M26" s="35" t="n"/>
       <c r="N26" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -15952,7 +15952,7 @@
       </c>
       <c r="O26" s="32" t="inlineStr">
         <is>
-          <t>Фойе</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -15962,42 +15962,42 @@
       </c>
       <c r="B27" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая вертикальная Ду100</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>529-03.003</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="n">
-        <v>100</v>
-      </c>
+          <t>Клапан проходной фланцевый сталь</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr"/>
+      <c r="D27" s="32" t="n"/>
       <c r="E27" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Фланцевая проходная</t>
         </is>
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G27" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="32" t="n">
-        <v>33.7</v>
+        <v>20</v>
       </c>
       <c r="I27" s="34" t="n">
-        <v>77650</v>
+        <v>38275</v>
       </c>
       <c r="J27" s="34" t="n">
-        <v>77650</v>
-      </c>
-      <c r="K27" s="34" t="n"/>
-      <c r="L27" s="34" t="n"/>
-      <c r="M27" s="35" t="n"/>
+        <v>76551</v>
+      </c>
+      <c r="K27" s="34" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L27" s="34" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M27" s="35" t="n">
+        <v>2.13</v>
+      </c>
       <c r="N27" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16005,7 +16005,7 @@
       </c>
       <c r="O27" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Фойе</t>
         </is>
       </c>
     </row>
@@ -16043,10 +16043,10 @@
         <v>5.6</v>
       </c>
       <c r="I28" s="34" t="n">
-        <v>9986</v>
+        <v>9272</v>
       </c>
       <c r="J28" s="34" t="n">
-        <v>69901</v>
+        <v>64905</v>
       </c>
       <c r="K28" s="34" t="n">
         <v>25000</v>
@@ -16055,7 +16055,7 @@
         <v>175000</v>
       </c>
       <c r="M28" s="35" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="N28" s="38" t="inlineStr">
         <is>
@@ -16102,10 +16102,10 @@
         <v>1.5</v>
       </c>
       <c r="I29" s="34" t="n">
-        <v>2675</v>
+        <v>2484</v>
       </c>
       <c r="J29" s="34" t="n">
-        <v>69544</v>
+        <v>64574</v>
       </c>
       <c r="K29" s="34" t="n"/>
       <c r="L29" s="34" t="n"/>
@@ -16127,14 +16127,20 @@
       </c>
       <c r="B30" s="33" t="inlineStr">
         <is>
-          <t>Электропривод к задвижке</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="inlineStr"/>
-      <c r="D30" s="32" t="n"/>
+          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>529-35-1405-01</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>100</v>
+      </c>
       <c r="E30" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F30" s="32" t="inlineStr">
@@ -16146,22 +16152,22 @@
         <v>1</v>
       </c>
       <c r="H30" s="32" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="I30" s="34" t="n">
-        <v>61445</v>
+        <v>59908</v>
       </c>
       <c r="J30" s="34" t="n">
-        <v>61445</v>
+        <v>59908</v>
       </c>
       <c r="K30" s="34" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="L30" s="34" t="n">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="M30" s="35" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="N30" s="38" t="inlineStr">
         <is>
@@ -16170,7 +16176,7 @@
       </c>
       <c r="O30" s="32" t="inlineStr">
         <is>
-          <t>Гараж 2</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16180,16 +16186,14 @@
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+          <t>Коробка 2-х клапанная корпус</t>
         </is>
       </c>
       <c r="C31" s="32" t="inlineStr"/>
-      <c r="D31" s="32" t="n">
-        <v>65</v>
-      </c>
+      <c r="D31" s="32" t="n"/>
       <c r="E31" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая, угол или проход не указан</t>
+          <t>Коробки клапанные</t>
         </is>
       </c>
       <c r="F31" s="32" t="inlineStr">
@@ -16198,25 +16202,25 @@
         </is>
       </c>
       <c r="G31" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="32" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="I31" s="34" t="n">
-        <v>30314</v>
+        <v>57434</v>
       </c>
       <c r="J31" s="34" t="n">
-        <v>60628</v>
+        <v>57434</v>
       </c>
       <c r="K31" s="34" t="n">
-        <v>9750</v>
+        <v>20000</v>
       </c>
       <c r="L31" s="34" t="n">
-        <v>19500</v>
+        <v>20000</v>
       </c>
       <c r="M31" s="35" t="n">
-        <v>3.11</v>
+        <v>2.87</v>
       </c>
       <c r="N31" s="38" t="inlineStr">
         <is>
@@ -16235,20 +16239,16 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая угловая Ду100Ру6,3</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="inlineStr">
-        <is>
-          <t>529-35-1405-01</t>
-        </is>
-      </c>
+          <t>Клапан невозвратно-приемный фланцевый Ду 65 Ру1 (522-03.023)</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr"/>
       <c r="D32" s="32" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E32" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Фланцевая, угол или проход не указан</t>
         </is>
       </c>
       <c r="F32" s="32" t="inlineStr">
@@ -16257,25 +16257,25 @@
         </is>
       </c>
       <c r="G32" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="32" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I32" s="34" t="n">
-        <v>59908</v>
+        <v>28148</v>
       </c>
       <c r="J32" s="34" t="n">
-        <v>59908</v>
+        <v>56295</v>
       </c>
       <c r="K32" s="34" t="n">
-        <v>40000</v>
+        <v>9750</v>
       </c>
       <c r="L32" s="34" t="n">
-        <v>40000</v>
+        <v>19500</v>
       </c>
       <c r="M32" s="35" t="n">
-        <v>1.5</v>
+        <v>2.89</v>
       </c>
       <c r="N32" s="38" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="O32" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -16294,47 +16294,47 @@
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>Клапан паровой Ду65Ру10</t>
+          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
         </is>
       </c>
       <c r="C33" s="32" t="inlineStr">
         <is>
-          <t>581-03.034</t>
+          <t>529-35.1406-01</t>
         </is>
       </c>
       <c r="D33" s="32" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="E33" s="32" t="inlineStr">
         <is>
-          <t>Паровые клапаны</t>
+          <t>Захлопки</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G33" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="32" t="n">
-        <v>32.6</v>
+        <v>23.6</v>
       </c>
       <c r="I33" s="34" t="n">
-        <v>58132</v>
+        <v>54378</v>
       </c>
       <c r="J33" s="34" t="n">
-        <v>58132</v>
+        <v>54378</v>
       </c>
       <c r="K33" s="34" t="n">
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="L33" s="34" t="n">
-        <v>60000</v>
+        <v>40000</v>
       </c>
       <c r="M33" s="35" t="n">
-        <v>0.97</v>
+        <v>1.36</v>
       </c>
       <c r="N33" s="38" t="inlineStr">
         <is>
@@ -16353,41 +16353,47 @@
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>Коробка 2-х клапанная корпус</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="inlineStr"/>
-      <c r="D34" s="32" t="n"/>
+          <t>Клапан паровой Ду65Ру10</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>581-03.034</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="n">
+        <v>65</v>
+      </c>
       <c r="E34" s="32" t="inlineStr">
         <is>
-          <t>Коробки клапанные</t>
+          <t>Паровые клапаны</t>
         </is>
       </c>
       <c r="F34" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G34" s="34" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="32" t="n">
-        <v>40</v>
+        <v>32.6</v>
       </c>
       <c r="I34" s="34" t="n">
-        <v>57434</v>
+        <v>53977</v>
       </c>
       <c r="J34" s="34" t="n">
-        <v>57434</v>
+        <v>53977</v>
       </c>
       <c r="K34" s="34" t="n">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="L34" s="34" t="n">
-        <v>20000</v>
+        <v>60000</v>
       </c>
       <c r="M34" s="35" t="n">
-        <v>2.87</v>
+        <v>0.9</v>
       </c>
       <c r="N34" s="38" t="inlineStr">
         <is>
@@ -16396,7 +16402,7 @@
       </c>
       <c r="O34" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16406,20 +16412,14 @@
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>Захлопка фланцевая проходная Ду100Ру6,3</t>
-        </is>
-      </c>
-      <c r="C35" s="32" t="inlineStr">
-        <is>
-          <t>529-35.1406-01</t>
-        </is>
-      </c>
-      <c r="D35" s="32" t="n">
-        <v>100</v>
-      </c>
+          <t>Электропривод к задвижке</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr"/>
+      <c r="D35" s="32" t="n"/>
       <c r="E35" s="32" t="inlineStr">
         <is>
-          <t>Захлопки</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F35" s="32" t="inlineStr">
@@ -16431,22 +16431,22 @@
         <v>1</v>
       </c>
       <c r="H35" s="32" t="n">
-        <v>23.6</v>
+        <v>40</v>
       </c>
       <c r="I35" s="34" t="n">
-        <v>54378</v>
+        <v>50350</v>
       </c>
       <c r="J35" s="34" t="n">
-        <v>54378</v>
+        <v>50350</v>
       </c>
       <c r="K35" s="34" t="n">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="L35" s="34" t="n">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="M35" s="35" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="N35" s="38" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
       </c>
       <c r="O35" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Гараж 2</t>
         </is>
       </c>
     </row>
@@ -16646,10 +16646,10 @@
         <v>17</v>
       </c>
       <c r="I39" s="34" t="n">
-        <v>30314</v>
+        <v>28148</v>
       </c>
       <c r="J39" s="34" t="n">
-        <v>30314</v>
+        <v>28148</v>
       </c>
       <c r="K39" s="34" t="n">
         <v>9750</v>
@@ -16658,7 +16658,7 @@
         <v>9750</v>
       </c>
       <c r="M39" s="35" t="n">
-        <v>3.11</v>
+        <v>2.89</v>
       </c>
       <c r="N39" s="38" t="inlineStr">
         <is>
@@ -16677,36 +16677,48 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>Клапан фреоновый саленоидный</t>
-        </is>
-      </c>
-      <c r="C40" s="32" t="inlineStr"/>
-      <c r="D40" s="32" t="n"/>
+          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>522-35.445-19</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="n">
+        <v>40</v>
+      </c>
       <c r="E40" s="32" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Фланцевая угловая</t>
         </is>
       </c>
       <c r="F40" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>сталь</t>
         </is>
       </c>
       <c r="G40" s="34" t="n">
         <v>2</v>
       </c>
       <c r="H40" s="32" t="n">
-        <v>12.3</v>
+        <v>10</v>
       </c>
       <c r="I40" s="34" t="n">
-        <v>12724</v>
+        <v>13580</v>
       </c>
       <c r="J40" s="34" t="n">
-        <v>25448</v>
-      </c>
-      <c r="K40" s="34" t="n"/>
-      <c r="L40" s="34" t="n"/>
-      <c r="M40" s="35" t="n"/>
+        <v>27160</v>
+      </c>
+      <c r="K40" s="34" t="n">
+        <v>18000</v>
+      </c>
+      <c r="L40" s="34" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M40" s="35" t="n">
+        <v>0.75</v>
+      </c>
       <c r="N40" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16724,18 +16736,14 @@
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>Клапан штуцерный угловой Рр150/10</t>
-        </is>
-      </c>
-      <c r="C41" s="32" t="inlineStr">
-        <is>
-          <t>521-ц22п</t>
-        </is>
-      </c>
+          <t>Клапан фреоновый саленоидный</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr"/>
       <c r="D41" s="32" t="n"/>
       <c r="E41" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Электромагнитные клапаны</t>
         </is>
       </c>
       <c r="F41" s="32" t="inlineStr">
@@ -16744,26 +16752,20 @@
         </is>
       </c>
       <c r="G41" s="34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H41" s="32" t="n">
-        <v>1</v>
+        <v>12.3</v>
       </c>
       <c r="I41" s="34" t="n">
-        <v>3126</v>
+        <v>12724</v>
       </c>
       <c r="J41" s="34" t="n">
-        <v>25008</v>
-      </c>
-      <c r="K41" s="34" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L41" s="34" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M41" s="35" t="n">
-        <v>1.04</v>
-      </c>
+        <v>25448</v>
+      </c>
+      <c r="K41" s="34" t="n"/>
+      <c r="L41" s="34" t="n"/>
+      <c r="M41" s="35" t="n"/>
       <c r="N41" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16771,7 +16773,7 @@
       </c>
       <c r="O41" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -16781,20 +16783,18 @@
       </c>
       <c r="B42" s="33" t="inlineStr">
         <is>
-          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
+          <t>Клапан штуцерный угловой Рр150/10</t>
         </is>
       </c>
       <c r="C42" s="32" t="inlineStr">
         <is>
-          <t>524-35.2423-01</t>
-        </is>
-      </c>
-      <c r="D42" s="32" t="n">
-        <v>6</v>
-      </c>
+          <t>521-ц22п</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="n"/>
       <c r="E42" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F42" s="32" t="inlineStr">
@@ -16803,25 +16803,25 @@
         </is>
       </c>
       <c r="G42" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="H42" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="32" t="n">
-        <v>3.5</v>
-      </c>
       <c r="I42" s="34" t="n">
-        <v>23743</v>
+        <v>3126</v>
       </c>
       <c r="J42" s="34" t="n">
-        <v>23743</v>
+        <v>25008</v>
       </c>
       <c r="K42" s="34" t="n">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="L42" s="34" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="M42" s="35" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="N42" s="38" t="inlineStr">
         <is>
@@ -16840,42 +16840,48 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
+          <t>Клапан предохранительный штуцерный сигнальный Ду6 Ру100-230</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
         <is>
-          <t>(541-03.232)</t>
+          <t>524-35.2423-01</t>
         </is>
       </c>
       <c r="D43" s="32" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E43" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F43" s="32" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G43" s="34" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H43" s="32" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="I43" s="34" t="n">
-        <v>2853</v>
+        <v>23743</v>
       </c>
       <c r="J43" s="34" t="n">
-        <v>22825</v>
-      </c>
-      <c r="K43" s="34" t="n"/>
-      <c r="L43" s="34" t="n"/>
-      <c r="M43" s="35" t="n"/>
+        <v>23743</v>
+      </c>
+      <c r="K43" s="34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L43" s="34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M43" s="35" t="n">
+        <v>1.19</v>
+      </c>
       <c r="N43" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -16883,7 +16889,7 @@
       </c>
       <c r="O43" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -16893,16 +16899,16 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду25</t>
         </is>
       </c>
       <c r="C44" s="32" t="inlineStr">
         <is>
-          <t>(541-03.316-04)</t>
+          <t>(541-03.232)</t>
         </is>
       </c>
       <c r="D44" s="32" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="E44" s="32" t="inlineStr">
         <is>
@@ -16911,20 +16917,20 @@
       </c>
       <c r="F44" s="32" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G44" s="34" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H44" s="32" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="I44" s="34" t="n">
-        <v>8381</v>
+        <v>2649</v>
       </c>
       <c r="J44" s="34" t="n">
-        <v>16762</v>
+        <v>21194</v>
       </c>
       <c r="K44" s="34" t="n"/>
       <c r="L44" s="34" t="n"/>
@@ -16946,20 +16952,16 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
-        </is>
-      </c>
-      <c r="C45" s="32" t="inlineStr">
-        <is>
-          <t>521-03.445-04</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду60</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="inlineStr"/>
       <c r="D45" s="32" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E45" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная угловая</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F45" s="32" t="inlineStr">
@@ -16968,25 +16970,25 @@
         </is>
       </c>
       <c r="G45" s="34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H45" s="32" t="n">
-        <v>1.3</v>
+        <v>14</v>
       </c>
       <c r="I45" s="34" t="n">
-        <v>4064</v>
+        <v>17623</v>
       </c>
       <c r="J45" s="34" t="n">
-        <v>16255</v>
+        <v>17623</v>
       </c>
       <c r="K45" s="34" t="n">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="L45" s="34" t="n">
-        <v>60000</v>
+        <v>18000</v>
       </c>
       <c r="M45" s="35" t="n">
-        <v>0.27</v>
+        <v>0.98</v>
       </c>
       <c r="N45" s="38" t="inlineStr">
         <is>
@@ -16995,7 +16997,7 @@
       </c>
       <c r="O45" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 3</t>
         </is>
       </c>
     </row>
@@ -17005,47 +17007,43 @@
       </c>
       <c r="B46" s="33" t="inlineStr">
         <is>
-          <t>Клапан фланцевый угловой Ду40 Ру25 сталь ок.входа</t>
-        </is>
-      </c>
-      <c r="C46" s="32" t="inlineStr">
-        <is>
-          <t>522-35.445-19</t>
-        </is>
-      </c>
+          <t>Задвижка клинкетная Ду60</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="inlineStr"/>
       <c r="D46" s="32" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E46" s="32" t="inlineStr">
         <is>
-          <t>Фланцевая угловая</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F46" s="32" t="inlineStr">
         <is>
-          <t>сталь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G46" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" s="32" t="n">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="I46" s="34" t="n">
-        <v>7767</v>
+        <v>17623</v>
       </c>
       <c r="J46" s="34" t="n">
-        <v>15534</v>
+        <v>17623</v>
       </c>
       <c r="K46" s="34" t="n">
         <v>18000</v>
       </c>
       <c r="L46" s="34" t="n">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="M46" s="35" t="n">
-        <v>0.43</v>
+        <v>0.98</v>
       </c>
       <c r="N46" s="38" t="inlineStr">
         <is>
@@ -17054,7 +17052,7 @@
       </c>
       <c r="O46" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -17064,42 +17062,48 @@
       </c>
       <c r="B47" s="33" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 150 (верхние)</t>
+          <t>Клапан угловой с присоединением под дюрит Ду50Ру4</t>
         </is>
       </c>
       <c r="C47" s="32" t="inlineStr">
         <is>
-          <t>(541-03.315-02)</t>
+          <t>521-03.445-04</t>
         </is>
       </c>
       <c r="D47" s="32" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="E47" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Штуцерная угловая</t>
         </is>
       </c>
       <c r="F47" s="32" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G47" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H47" s="32" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="I47" s="34" t="n">
-        <v>5171</v>
+        <v>4064</v>
       </c>
       <c r="J47" s="34" t="n">
-        <v>15514</v>
-      </c>
-      <c r="K47" s="34" t="n"/>
-      <c r="L47" s="34" t="n"/>
-      <c r="M47" s="35" t="n"/>
+        <v>16255</v>
+      </c>
+      <c r="K47" s="34" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L47" s="34" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M47" s="35" t="n">
+        <v>0.27</v>
+      </c>
       <c r="N47" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17107,7 +17111,7 @@
       </c>
       <c r="O47" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -17117,38 +17121,38 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>Клапан Ду20/10</t>
+          <t>Грибки АМГ Ду 200 с нижнем приводом</t>
         </is>
       </c>
       <c r="C48" s="32" t="inlineStr">
         <is>
-          <t>581-С6.73</t>
+          <t>(541-03.316-04)</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E48" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F48" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G48" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="32" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="I48" s="34" t="n">
-        <v>4280</v>
+        <v>7782</v>
       </c>
       <c r="J48" s="34" t="n">
-        <v>12839</v>
+        <v>15564</v>
       </c>
       <c r="K48" s="34" t="n"/>
       <c r="L48" s="34" t="n"/>
@@ -17170,36 +17174,38 @@
       </c>
       <c r="B49" s="33" t="inlineStr">
         <is>
-          <t>Клапан с электромагнитным ручным управлением</t>
+          <t>Грибки АМГ Ду 150 (верхние)</t>
         </is>
       </c>
       <c r="C49" s="32" t="inlineStr">
         <is>
-          <t>587-182.126</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="n"/>
+          <t>(541-03.315-02)</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="n">
+        <v>150</v>
+      </c>
       <c r="E49" s="32" t="inlineStr">
         <is>
-          <t>Электромагнитные клапаны</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F49" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G49" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H49" s="32" t="n">
-        <v>12.3</v>
+        <v>2.9</v>
       </c>
       <c r="I49" s="34" t="n">
-        <v>12724</v>
+        <v>4802</v>
       </c>
       <c r="J49" s="34" t="n">
-        <v>12724</v>
+        <v>14405</v>
       </c>
       <c r="K49" s="34" t="n"/>
       <c r="L49" s="34" t="n"/>
@@ -17221,18 +17227,16 @@
       </c>
       <c r="B50" s="33" t="inlineStr">
         <is>
-          <t>Кланан Рр18-2 45/25</t>
-        </is>
-      </c>
-      <c r="C50" s="32" t="inlineStr">
-        <is>
-          <t>2619802505</t>
-        </is>
-      </c>
-      <c r="D50" s="32" t="n"/>
+          <t>Задвижка клинкетная Ду 50, без клиньев</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr"/>
+      <c r="D50" s="32" t="n">
+        <v>50</v>
+      </c>
       <c r="E50" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Клинкеты</t>
         </is>
       </c>
       <c r="F50" s="32" t="inlineStr">
@@ -17244,17 +17248,23 @@
         <v>1</v>
       </c>
       <c r="H50" s="32" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="I50" s="34" t="n">
-        <v>12126</v>
+        <v>13217</v>
       </c>
       <c r="J50" s="34" t="n">
-        <v>12126</v>
-      </c>
-      <c r="K50" s="34" t="n"/>
-      <c r="L50" s="34" t="n"/>
-      <c r="M50" s="35" t="n"/>
+        <v>13217</v>
+      </c>
+      <c r="K50" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L50" s="34" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M50" s="35" t="n">
+        <v>0.53</v>
+      </c>
       <c r="N50" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17262,7 +17272,7 @@
       </c>
       <c r="O50" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 1А/1Б</t>
         </is>
       </c>
     </row>
@@ -17272,14 +17282,18 @@
       </c>
       <c r="B51" s="33" t="inlineStr">
         <is>
-          <t>Судовая запорная арматура</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr"/>
+          <t>Клапан с электромагнитным ручным управлением</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>587-182.126</t>
+        </is>
+      </c>
       <c r="D51" s="32" t="n"/>
       <c r="E51" s="32" t="inlineStr">
         <is>
-          <t>Без описания — уточнить</t>
+          <t>Электромагнитные клапаны</t>
         </is>
       </c>
       <c r="F51" s="32" t="inlineStr">
@@ -17291,23 +17305,17 @@
         <v>1</v>
       </c>
       <c r="H51" s="32" t="n">
-        <v>6.8</v>
+        <v>12.3</v>
       </c>
       <c r="I51" s="34" t="n">
-        <v>12126</v>
+        <v>12724</v>
       </c>
       <c r="J51" s="34" t="n">
-        <v>12126</v>
-      </c>
-      <c r="K51" s="34" t="n">
-        <v>10000</v>
-      </c>
-      <c r="L51" s="34" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M51" s="35" t="n">
-        <v>1.21</v>
-      </c>
+        <v>12724</v>
+      </c>
+      <c r="K51" s="34" t="n"/>
+      <c r="L51" s="34" t="n"/>
+      <c r="M51" s="35" t="n"/>
       <c r="N51" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17315,7 +17323,7 @@
       </c>
       <c r="O51" s="32" t="inlineStr">
         <is>
-          <t>Менеджерская</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17325,15 +17333,17 @@
       </c>
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>Клапан</t>
+          <t>Клапан Ду20/10</t>
         </is>
       </c>
       <c r="C52" s="32" t="inlineStr">
         <is>
-          <t>587-182.126</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="n"/>
+          <t>581-С6.73</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="n">
+        <v>20</v>
+      </c>
       <c r="E52" s="32" t="inlineStr">
         <is>
           <t>Без описания — уточнить</t>
@@ -17345,16 +17355,16 @@
         </is>
       </c>
       <c r="G52" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52" s="32" t="n">
-        <v>6.8</v>
+        <v>2.4</v>
       </c>
       <c r="I52" s="34" t="n">
-        <v>12126</v>
+        <v>3974</v>
       </c>
       <c r="J52" s="34" t="n">
-        <v>12126</v>
+        <v>11921</v>
       </c>
       <c r="K52" s="34" t="n"/>
       <c r="L52" s="34" t="n"/>
@@ -17366,7 +17376,7 @@
       </c>
       <c r="O52" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17402,10 +17412,10 @@
         <v>6.8</v>
       </c>
       <c r="I53" s="34" t="n">
-        <v>12126</v>
+        <v>11259</v>
       </c>
       <c r="J53" s="34" t="n">
-        <v>12126</v>
+        <v>11259</v>
       </c>
       <c r="K53" s="34" t="n"/>
       <c r="L53" s="34" t="n"/>
@@ -17417,7 +17427,7 @@
       </c>
       <c r="O53" s="32" t="inlineStr">
         <is>
-          <t>Склад 2</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -17427,20 +17437,14 @@
       </c>
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
-        </is>
-      </c>
-      <c r="C54" s="32" t="inlineStr">
-        <is>
-          <t>522-03.124-04</t>
-        </is>
-      </c>
-      <c r="D54" s="32" t="n">
-        <v>50</v>
-      </c>
+          <t>Судовая запорная арматура</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr"/>
+      <c r="D54" s="32" t="n"/>
       <c r="E54" s="32" t="inlineStr">
         <is>
-          <t>Штуцерная, угол или проход не указан</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F54" s="32" t="inlineStr">
@@ -17452,22 +17456,22 @@
         <v>1</v>
       </c>
       <c r="H54" s="32" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="I54" s="34" t="n">
-        <v>10311</v>
+        <v>11259</v>
       </c>
       <c r="J54" s="34" t="n">
-        <v>10311</v>
+        <v>11259</v>
       </c>
       <c r="K54" s="34" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="L54" s="34" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="M54" s="35" t="n">
-        <v>0.52</v>
+        <v>1.13</v>
       </c>
       <c r="N54" s="38" t="inlineStr">
         <is>
@@ -17476,7 +17480,7 @@
       </c>
       <c r="O54" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Менеджерская</t>
         </is>
       </c>
     </row>
@@ -17486,20 +17490,18 @@
       </c>
       <c r="B55" s="33" t="inlineStr">
         <is>
-          <t>Клапан педальный Ду25</t>
+          <t>Клапан</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
         <is>
-          <t>М528-03.001</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="n">
-        <v>25</v>
-      </c>
+          <t>587-182.126</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="n"/>
       <c r="E55" s="32" t="inlineStr">
         <is>
-          <t>Педальные клапаны</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F55" s="32" t="inlineStr">
@@ -17511,23 +17513,17 @@
         <v>1</v>
       </c>
       <c r="H55" s="32" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="I55" s="34" t="n">
-        <v>9808</v>
+        <v>11259</v>
       </c>
       <c r="J55" s="34" t="n">
-        <v>9808</v>
-      </c>
-      <c r="K55" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="L55" s="34" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M55" s="35" t="n">
-        <v>0.65</v>
-      </c>
+        <v>11259</v>
+      </c>
+      <c r="K55" s="34" t="n"/>
+      <c r="L55" s="34" t="n"/>
+      <c r="M55" s="35" t="n"/>
       <c r="N55" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -17535,7 +17531,7 @@
       </c>
       <c r="O55" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 2</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -17545,38 +17541,36 @@
       </c>
       <c r="B56" s="33" t="inlineStr">
         <is>
-          <t>Грибки АМГ Ду 150 (нижние)</t>
+          <t>Кланан Рр18-2 45/25</t>
         </is>
       </c>
       <c r="C56" s="32" t="inlineStr">
         <is>
-          <t>(541-03.316-02)</t>
-        </is>
-      </c>
-      <c r="D56" s="32" t="n">
-        <v>150</v>
-      </c>
+          <t>2619802505</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="n"/>
       <c r="E56" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Без описания — уточнить</t>
         </is>
       </c>
       <c r="F56" s="32" t="inlineStr">
         <is>
-          <t>алюминий</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G56" s="34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" s="32" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="I56" s="34" t="n">
-        <v>4815</v>
+        <v>11259</v>
       </c>
       <c r="J56" s="34" t="n">
-        <v>9629</v>
+        <v>11259</v>
       </c>
       <c r="K56" s="34" t="n"/>
       <c r="L56" s="34" t="n"/>
@@ -17588,7 +17582,7 @@
       </c>
       <c r="O56" s="32" t="inlineStr">
         <is>
-          <t>список менеджера, Прил. 3</t>
+          <t>Склад 2</t>
         </is>
       </c>
     </row>
@@ -17598,16 +17592,20 @@
       </c>
       <c r="B57" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
-        </is>
-      </c>
-      <c r="C57" s="32" t="inlineStr"/>
+          <t>Клапан невозв-запорн.с присоед.под дюрит прох. Ду 50 Ру6</t>
+        </is>
+      </c>
+      <c r="C57" s="32" t="inlineStr">
+        <is>
+          <t>522-03.124-04</t>
+        </is>
+      </c>
       <c r="D57" s="32" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E57" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Штуцерная, угол или проход не указан</t>
         </is>
       </c>
       <c r="F57" s="32" t="inlineStr">
@@ -17619,22 +17617,22 @@
         <v>1</v>
       </c>
       <c r="H57" s="32" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="I57" s="34" t="n">
-        <v>9563</v>
+        <v>10311</v>
       </c>
       <c r="J57" s="34" t="n">
-        <v>9563</v>
+        <v>10311</v>
       </c>
       <c r="K57" s="34" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="L57" s="34" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="M57" s="35" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="N57" s="38" t="inlineStr">
         <is>
@@ -17643,7 +17641,7 @@
       </c>
       <c r="O57" s="32" t="inlineStr">
         <is>
-          <t>Склад 3</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -17653,16 +17651,20 @@
       </c>
       <c r="B58" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду60</t>
-        </is>
-      </c>
-      <c r="C58" s="32" t="inlineStr"/>
+          <t>Клапан педальный Ду25</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>М528-03.001</t>
+        </is>
+      </c>
       <c r="D58" s="32" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Педальные клапаны</t>
         </is>
       </c>
       <c r="F58" s="32" t="inlineStr">
@@ -17674,22 +17676,22 @@
         <v>1</v>
       </c>
       <c r="H58" s="32" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="I58" s="34" t="n">
-        <v>9563</v>
+        <v>9107</v>
       </c>
       <c r="J58" s="34" t="n">
-        <v>9563</v>
+        <v>9107</v>
       </c>
       <c r="K58" s="34" t="n">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="L58" s="34" t="n">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="M58" s="35" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="N58" s="38" t="inlineStr">
         <is>
@@ -17698,7 +17700,7 @@
       </c>
       <c r="O58" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 2</t>
         </is>
       </c>
     </row>
@@ -17708,38 +17710,38 @@
       </c>
       <c r="B59" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду20Ру100</t>
+          <t>Грибки АМГ Ду 150 (нижние)</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
         <is>
-          <t>554-03.909-03</t>
+          <t>(541-03.316-02)</t>
         </is>
       </c>
       <c r="D59" s="32" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="E59" s="32" t="inlineStr">
         <is>
-          <t>Стаканы переборочные</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>алюминий</t>
         </is>
       </c>
       <c r="G59" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" s="32" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="I59" s="34" t="n">
-        <v>3031</v>
+        <v>4471</v>
       </c>
       <c r="J59" s="34" t="n">
-        <v>9094</v>
+        <v>8941</v>
       </c>
       <c r="K59" s="34" t="n"/>
       <c r="L59" s="34" t="n"/>
@@ -17761,16 +17763,16 @@
       </c>
       <c r="B60" s="33" t="inlineStr">
         <is>
-          <t>Стакан переборочный Ду25Ру100</t>
+          <t>Стакан переборочный Ду20Ру100</t>
         </is>
       </c>
       <c r="C60" s="32" t="inlineStr">
         <is>
-          <t>554-35.156</t>
+          <t>554-03.909-03</t>
         </is>
       </c>
       <c r="D60" s="32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E60" s="32" t="inlineStr">
         <is>
@@ -17783,16 +17785,16 @@
         </is>
       </c>
       <c r="G60" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H60" s="32" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="I60" s="34" t="n">
-        <v>4458</v>
+        <v>2815</v>
       </c>
       <c r="J60" s="34" t="n">
-        <v>8916</v>
+        <v>8444</v>
       </c>
       <c r="K60" s="34" t="n"/>
       <c r="L60" s="34" t="n"/>
@@ -17814,38 +17816,38 @@
       </c>
       <c r="B61" s="33" t="inlineStr">
         <is>
-          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
+          <t>Стакан переборочный Ду25Ру100</t>
         </is>
       </c>
       <c r="C61" s="32" t="inlineStr">
         <is>
-          <t>541-03.224</t>
+          <t>554-35.156</t>
         </is>
       </c>
       <c r="D61" s="32" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E61" s="32" t="inlineStr">
         <is>
-          <t>Головки вентиляционные</t>
+          <t>Стаканы переборочные</t>
         </is>
       </c>
       <c r="F61" s="32" t="inlineStr">
         <is>
-          <t>латунь</t>
+          <t>бронза/латунь</t>
         </is>
       </c>
       <c r="G61" s="34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61" s="32" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I61" s="34" t="n">
-        <v>2675</v>
+        <v>4139</v>
       </c>
       <c r="J61" s="34" t="n">
-        <v>8024</v>
+        <v>8279</v>
       </c>
       <c r="K61" s="34" t="n"/>
       <c r="L61" s="34" t="n"/>
@@ -17895,10 +17897,10 @@
         <v>5.5</v>
       </c>
       <c r="I62" s="34" t="n">
-        <v>7614</v>
+        <v>7469</v>
       </c>
       <c r="J62" s="34" t="n">
-        <v>7614</v>
+        <v>7469</v>
       </c>
       <c r="K62" s="34" t="n"/>
       <c r="L62" s="34" t="n"/>
@@ -17948,10 +17950,10 @@
         <v>5.5</v>
       </c>
       <c r="I63" s="34" t="n">
-        <v>7614</v>
+        <v>7469</v>
       </c>
       <c r="J63" s="34" t="n">
-        <v>7614</v>
+        <v>7469</v>
       </c>
       <c r="K63" s="34" t="n">
         <v>9600</v>
@@ -17960,7 +17962,7 @@
         <v>9600</v>
       </c>
       <c r="M63" s="35" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="N63" s="38" t="inlineStr">
         <is>
@@ -17979,32 +17981,38 @@
       </c>
       <c r="B64" s="33" t="inlineStr">
         <is>
-          <t>Эжектор ВЭЖ 6,3</t>
-        </is>
-      </c>
-      <c r="C64" s="32" t="inlineStr"/>
-      <c r="D64" s="32" t="n"/>
+          <t>Головка воздушно-квадрат.(поплавковая) Ду32</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>541-03.224</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>32</v>
+      </c>
       <c r="E64" s="32" t="inlineStr">
         <is>
-          <t>Эжекторы</t>
+          <t>Головки вентиляционные</t>
         </is>
       </c>
       <c r="F64" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>латунь</t>
         </is>
       </c>
       <c r="G64" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H64" s="32" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="I64" s="34" t="n">
-        <v>7133</v>
+        <v>2484</v>
       </c>
       <c r="J64" s="34" t="n">
-        <v>7133</v>
+        <v>7451</v>
       </c>
       <c r="K64" s="34" t="n"/>
       <c r="L64" s="34" t="n"/>
@@ -18026,16 +18034,14 @@
       </c>
       <c r="B65" s="33" t="inlineStr">
         <is>
-          <t>Задвижка клинкетная Ду 50, без клиньев</t>
+          <t>Эжектор ВЭЖ 6,3</t>
         </is>
       </c>
       <c r="C65" s="32" t="inlineStr"/>
-      <c r="D65" s="32" t="n">
-        <v>50</v>
-      </c>
+      <c r="D65" s="32" t="n"/>
       <c r="E65" s="32" t="inlineStr">
         <is>
-          <t>Клинкеты</t>
+          <t>Эжекторы</t>
         </is>
       </c>
       <c r="F65" s="32" t="inlineStr">
@@ -18047,23 +18053,17 @@
         <v>1</v>
       </c>
       <c r="H65" s="32" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I65" s="34" t="n">
-        <v>6403</v>
+        <v>6623</v>
       </c>
       <c r="J65" s="34" t="n">
-        <v>6403</v>
-      </c>
-      <c r="K65" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="L65" s="34" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M65" s="35" t="n">
-        <v>0.26</v>
-      </c>
+        <v>6623</v>
+      </c>
+      <c r="K65" s="34" t="n"/>
+      <c r="L65" s="34" t="n"/>
+      <c r="M65" s="35" t="n"/>
       <c r="N65" s="38" t="inlineStr">
         <is>
           <t>оценка по цене килограмма</t>
@@ -18071,7 +18071,7 @@
       </c>
       <c r="O65" s="32" t="inlineStr">
         <is>
-          <t>Склад 1А/1Б</t>
+          <t>список менеджера, Прил. 3</t>
         </is>
       </c>
     </row>
@@ -18109,10 +18109,10 @@
         <v>0.6</v>
       </c>
       <c r="I66" s="34" t="n">
-        <v>1070</v>
+        <v>993</v>
       </c>
       <c r="J66" s="34" t="n">
-        <v>5350</v>
+        <v>4967</v>
       </c>
       <c r="K66" s="34" t="n"/>
       <c r="L66" s="34" t="n"/>

--- a/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
+++ b/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -807,194 +807,209 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>13775052</v>
+        <v>20507504</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>латунь 500, бронза 600, сталь 9 руб за кг. Считаем по латуни — осторожнее</t>
+          <t>бронза 745, латунь 635, сталь 19 руб за кг. Класс «бронза/латунь» считаем по бронзе</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>Он же по бронзе 600 руб за кг</t>
+          <t>Он же по латуни 635 руб за кг</t>
         </is>
       </c>
       <c r="B19" s="18" t="n">
-        <v>17395267</v>
+        <v>18409991</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>верхняя граница лома</t>
+          <t>нижняя граница, если часть окажется латунью</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Во сколько раз рынок дороже лома</t>
+          <t>Закуп от лома, лом на 2.5, руб</t>
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>3.5</v>
+        <v>51268761</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>запас между ценой приемки и ценой рынка</t>
+          <t>цена по договору и есть лом с коэффициентом: бронза 1 862.50 руб за кг</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
+          <t>Во сколько раз рынок дороже лома</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>запас между ценой приемки и ценой рынка</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
           <t>Позиций без согласованной цены у нас</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n">
+      <c r="B22" s="18" t="n">
         <v>58</v>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>вес у них есть, а рублей в учете нет — наша сумма занижена именно на них</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Отгрузка в Петербург: сколько съедает логистика</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Вариант</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Расходы на доставку, руб</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Везем товара на, руб</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Доля логистики</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Руб на килограмм товара</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Усиленный двадцатифутовый, 27 т</t>
         </is>
       </c>
-      <c r="B25" s="23" t="n">
+      <c r="B26" s="23" t="n">
         <v>401000</v>
       </c>
-      <c r="C25" s="23" t="n">
+      <c r="C26" s="23" t="n">
         <v>47606331</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D26" s="24" t="n">
         <v>0.008423249391557874</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E26" s="25" t="n">
         <v>13.8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>Два двадцатифутовых по 22 т</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="n">
-        <v>632000</v>
-      </c>
-      <c r="C26" s="27" t="n">
-        <v>47606331</v>
-      </c>
-      <c r="D26" s="28" t="n">
-        <v>0.01327554517572214</v>
-      </c>
-      <c r="E26" s="29" t="n">
-        <v>21.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>Один сорокафутовый</t>
+          <t>Два двадцатифутовых по 22 т</t>
         </is>
       </c>
       <c r="B27" s="27" t="n">
-        <v>541000</v>
+        <v>632000</v>
       </c>
       <c r="C27" s="27" t="n">
         <v>47606331</v>
       </c>
       <c r="D27" s="28" t="n">
+        <v>0.01327554517572214</v>
+      </c>
+      <c r="E27" s="29" t="n">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>Один сорокафутовый</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n">
+        <v>541000</v>
+      </c>
+      <c r="C28" s="27" t="n">
+        <v>47606331</v>
+      </c>
+      <c r="D28" s="28" t="n">
         <v>0.01136403471529379</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E28" s="29" t="n">
         <v>18.7</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>За базу взят весь перечень — 28.99 т на 47.6 млн. В усиленный контейнер входит 26,35 т из них, на долю логистики эта разница не влияет.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Что из этого следует</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>— Вся арматура и фильтры на складе по ценам конкурента — 47.6 млн руб при весе 29.0 т. По нашим учетным ценам те же позиции стоят 40.0 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>— Доставка в Петербург стоит от 401 000 руб и съедает 0.8% стоимости отгружаемого товара. Для товара  который едет через всю страну  это немного: транспортная компания на том же весе взяла бы в несколько раз больше.</t>
+          <t>— Вся арматура и фильтры на складе по ценам конкурента — 47.6 млн руб при весе 29.0 т. По нашим учетным ценам те же позиции стоят 40.0 млн, но у 58 позиций цена в договоре записана как «по согласованию», и в нашу сумму они входят нулем. Настоящий разрыв меньше.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="30" t="inlineStr">
         <is>
-          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 656 руб  а довезти его до Петербурга стоит 13.8 руб. Отсюда и доля.</t>
+          <t>— Доставка в Петербург стоит от 401 000 руб и съедает 0.8% стоимости отгружаемого товара. Для товара  который едет через всю страну  это немного: транспортная компания на том же весе взяла бы в несколько раз больше.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t>— Твердая часть оценки — 221 позиция на 36.8 млн, это цены по чертежу и по типу. Остальное оценено по цене килограмма и годится для прикидки, а не для переговоров.</t>
+          <t>— Килограмм арматуры по конкуренту стоит в среднем 1 656 руб  а довезти его до Петербурга стоит 13.8 руб. Отсюда и доля.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>— Твердая часть оценки — 221 позиция на 36.8 млн, это цены по чертежу и по типу. Остальное оценено по цене килограмма и годится для прикидки, а не для переговоров.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>— Цены конкурента — это его прайс, а не сделки. Реальная цена продажи обычно ниже прайса, и до инвентаризации эти суммы покупателю не называем.</t>
         </is>

--- a/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
+++ b/outputs/marine_equipment/Оценка_по_конкуренту.xlsx
@@ -1914,7 +1914,7 @@
       </c>
       <c r="F5" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G5" s="34" t="n">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="F6" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G6" s="34" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G7" s="34" t="n">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="F8" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G8" s="34" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G9" s="34" t="n">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G10" s="34" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G11" s="34" t="n">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G12" s="34" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G13" s="34" t="n">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G14" s="34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G15" s="34" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G16" s="34" t="n">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G17" s="34" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G18" s="34" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G19" s="34" t="n">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G20" s="34" t="n">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G21" s="34" t="n">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G22" s="34" t="n">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G23" s="34" t="n">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G24" s="34" t="n">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G25" s="34" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="F26" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G26" s="34" t="n">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G27" s="34" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G28" s="34" t="n">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G29" s="34" t="n">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F30" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G30" s="34" t="n">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G31" s="34" t="n">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="F32" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G32" s="34" t="n">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G33" s="34" t="n">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="F34" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G34" s="34" t="n">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G35" s="34" t="n">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="F36" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G36" s="34" t="n">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F37" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G37" s="34" t="n">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="F38" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G38" s="34" t="n">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="F39" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G39" s="34" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="F40" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G40" s="34" t="n">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F41" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G41" s="34" t="n">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="F42" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G42" s="34" t="n">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="F43" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G43" s="34" t="n">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="F44" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G44" s="34" t="n">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="F45" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G45" s="34" t="n">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="F46" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G46" s="34" t="n">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="F47" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G47" s="34" t="n">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F48" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G48" s="34" t="n">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="F49" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G49" s="34" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="F50" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G50" s="34" t="n">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="F51" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G51" s="34" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="F52" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G52" s="34" t="n">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F53" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G53" s="34" t="n">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="F54" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G54" s="34" t="n">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="F55" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G55" s="34" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="F56" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G56" s="34" t="n">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="F57" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G57" s="34" t="n">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="F58" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G58" s="34" t="n">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="F60" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G60" s="34" t="n">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="F61" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G61" s="34" t="n">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="F62" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G62" s="34" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="F63" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G63" s="34" t="n">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="F64" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G64" s="34" t="n">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="F65" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G65" s="34" t="n">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="F66" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G66" s="34" t="n">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="F67" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G67" s="34" t="n">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="F68" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G68" s="34" t="n">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="F69" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G69" s="34" t="n">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="F70" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G70" s="34" t="n">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="F71" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G71" s="34" t="n">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="F72" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G72" s="34" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="F73" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G73" s="34" t="n">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="F74" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G74" s="34" t="n">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="F75" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G75" s="34" t="n">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F76" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G76" s="34" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="F77" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G77" s="34" t="n">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="F78" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G78" s="34" t="n">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="F79" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G79" s="34" t="n">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="F80" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G80" s="34" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="F5" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G5" s="34" t="n">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="F6" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G6" s="34" t="n">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G7" s="34" t="n">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="F8" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G8" s="34" t="n">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G9" s="34" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G10" s="34" t="n">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G11" s="34" t="n">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G12" s="34" t="n">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="F13" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G13" s="34" t="n">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G14" s="34" t="n">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G15" s="34" t="n">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G16" s="34" t="n">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G17" s="34" t="n">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="F18" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G18" s="34" t="n">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G19" s="34" t="n">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G20" s="34" t="n">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G21" s="34" t="n">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G22" s="34" t="n">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G23" s="34" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G24" s="34" t="n">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G25" s="34" t="n">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="F26" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G26" s="34" t="n">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="F27" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G27" s="34" t="n">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G28" s="34" t="n">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G29" s="34" t="n">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="F30" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G30" s="34" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G31" s="34" t="n">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="F32" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G32" s="34" t="n">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G33" s="34" t="n">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="F34" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G34" s="34" t="n">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G35" s="34" t="n">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F36" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G36" s="34" t="n">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="F37" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G37" s="34" t="n">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="F38" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G38" s="34" t="n">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="F40" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G40" s="34" t="n">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="F41" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G41" s="34" t="n">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="F42" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G42" s="34" t="n">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="F45" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G45" s="34" t="n">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="F46" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G46" s="34" t="n">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="F47" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G47" s="34" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="F48" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G48" s="34" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="F49" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G49" s="34" t="n">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="F50" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G50" s="34" t="n">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="F51" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G51" s="34" t="n">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="F52" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G52" s="34" t="n">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="F53" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G53" s="34" t="n">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="F54" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G54" s="34" t="n">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="F55" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G55" s="34" t="n">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="F56" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G56" s="34" t="n">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="F57" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G57" s="34" t="n">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="F58" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G58" s="34" t="n">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="F59" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G59" s="34" t="n">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="F60" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G60" s="34" t="n">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="F61" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G61" s="34" t="n">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="F62" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G62" s="34" t="n">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="F63" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G63" s="34" t="n">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="F64" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G64" s="34" t="n">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="F65" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G65" s="34" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="F67" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G67" s="34" t="n">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="F68" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G68" s="34" t="n">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="F69" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G69" s="34" t="n">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="F70" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G70" s="34" t="n">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="F71" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G71" s="34" t="n">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="F72" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G72" s="34" t="n">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="F73" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G73" s="34" t="n">
@@ -10418,7 +10418,7 @@
       </c>
       <c r="F76" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G76" s="34" t="n">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="F77" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G77" s="34" t="n">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="F79" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G79" s="34" t="n">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="F80" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G80" s="34" t="n">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="F81" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G81" s="34" t="n">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="F82" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G82" s="34" t="n">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="F83" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G83" s="34" t="n">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="F84" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G84" s="34" t="n">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="F85" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G85" s="34" t="n">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="F86" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G86" s="34" t="n">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="F87" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G87" s="34" t="n">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="F88" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G88" s="34" t="n">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="F89" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G89" s="34" t="n">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="F90" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G90" s="34" t="n">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="F91" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G91" s="34" t="n">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="F92" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G92" s="34" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="F93" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G93" s="34" t="n">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="F94" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G94" s="34" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="F95" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G95" s="34" t="n">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="F96" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G96" s="34" t="n">
@@ -11623,7 +11623,7 @@
       </c>
       <c r="F97" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G97" s="34" t="n">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="F98" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G98" s="34" t="n">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F99" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G99" s="34" t="n">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="F100" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G100" s="34" t="n">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="F101" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G101" s="34" t="n">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F102" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G102" s="34" t="n">
@@ -11961,7 +11961,7 @@
       </c>
       <c r="F103" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G103" s="34" t="n">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F104" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G104" s="34" t="n">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="F105" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G105" s="34" t="n">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="F106" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G106" s="34" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="F108" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G108" s="34" t="n">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="F109" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G109" s="34" t="n">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="F110" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G110" s="34" t="n">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="F111" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G111" s="34" t="n">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="F112" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G112" s="34" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="F113" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G113" s="34" t="n">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="F114" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G114" s="34" t="n">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="F115" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G115" s="34" t="n">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="F116" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G116" s="34" t="n">
@@ -12743,7 +12743,7 @@
       </c>
       <c r="F117" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G117" s="34" t="n">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="F118" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G118" s="34" t="n">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="F119" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G119" s="34" t="n">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="F120" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G120" s="34" t="n">
@@ -12973,7 +12973,7 @@
       </c>
       <c r="F121" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G121" s="34" t="n">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F122" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G122" s="34" t="n">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F123" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G123" s="34" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="F124" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G124" s="34" t="n">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="F126" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G126" s="34" t="n">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="F127" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G127" s="34" t="n">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="F128" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G128" s="34" t="n">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="F129" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G129" s="34" t="n">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="F130" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G130" s="34" t="n">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F131" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G131" s="34" t="n">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="F132" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G132" s="34" t="n">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="F133" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G133" s="34" t="n">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="F134" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G134" s="34" t="n">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="F135" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G135" s="34" t="n">
@@ -13844,7 +13844,7 @@
       </c>
       <c r="F136" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G136" s="34" t="n">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="F137" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G137" s="34" t="n">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="F138" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G138" s="34" t="n">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="F139" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G139" s="34" t="n">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="F140" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G140" s="34" t="n">
@@ -14139,7 +14139,7 @@
       </c>
       <c r="F141" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G141" s="34" t="n">
@@ -14194,7 +14194,7 @@
       </c>
       <c r="F142" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G142" s="34" t="n">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="F143" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G143" s="34" t="n">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="F144" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G144" s="34" t="n">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="F145" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G145" s="34" t="n">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="F146" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G146" s="34" t="n">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="F147" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G147" s="34" t="n">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="F5" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G5" s="34" t="n">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="F6" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G6" s="34" t="n">
@@ -14887,7 +14887,7 @@
       </c>
       <c r="F7" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G7" s="34" t="n">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="F9" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G9" s="34" t="n">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="F10" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G10" s="34" t="n">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="F11" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G11" s="34" t="n">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="F12" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G12" s="34" t="n">
@@ -15268,7 +15268,7 @@
       </c>
       <c r="F14" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G14" s="34" t="n">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="F15" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G15" s="34" t="n">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="F16" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G16" s="34" t="n">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="F17" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G17" s="34" t="n">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="F19" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G19" s="34" t="n">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="F20" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G20" s="34" t="n">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G21" s="34" t="n">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="F22" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G22" s="34" t="n">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="F23" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G23" s="34" t="n">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="F24" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G24" s="34" t="n">
@@ -15883,7 +15883,7 @@
       </c>
       <c r="F25" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G25" s="34" t="n">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="F26" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G26" s="34" t="n">
@@ -16048,7 +16048,7 @@
       </c>
       <c r="F28" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G28" s="34" t="n">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="F29" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G29" s="34" t="n">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="F30" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G30" s="34" t="n">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="F31" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G31" s="34" t="n">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="F32" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G32" s="34" t="n">
@@ -16327,7 +16327,7 @@
       </c>
       <c r="F33" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G33" s="34" t="n">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F35" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G35" s="34" t="n">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="F36" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G36" s="34" t="n">
@@ -16545,7 +16545,7 @@
       </c>
       <c r="F37" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G37" s="34" t="n">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="F38" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G38" s="34" t="n">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="F39" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G39" s="34" t="n">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="F41" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G41" s="34" t="n">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="F42" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G42" s="34" t="n">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="F43" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G43" s="34" t="n">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="F45" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G45" s="34" t="n">
@@ -17036,7 +17036,7 @@
       </c>
       <c r="F46" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G46" s="34" t="n">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="F47" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G47" s="34" t="n">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="F50" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G50" s="34" t="n">
@@ -17313,7 +17313,7 @@
       </c>
       <c r="F51" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G51" s="34" t="n">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F52" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G52" s="34" t="n">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="F53" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G53" s="34" t="n">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="F54" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G54" s="34" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="F55" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G55" s="34" t="n">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="F56" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G56" s="34" t="n">
@@ -17625,7 +17625,7 @@
       </c>
       <c r="F57" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G57" s="34" t="n">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="F58" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G58" s="34" t="n">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="F60" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G60" s="34" t="n">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="F61" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G61" s="34" t="n">
@@ -17902,7 +17902,7 @@
       </c>
       <c r="F62" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G62" s="34" t="n">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="F63" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G63" s="34" t="n">
@@ -18061,7 +18061,7 @@
       </c>
       <c r="F65" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G65" s="34" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="F66" s="32" t="inlineStr">
         <is>
-          <t>бронза/латунь</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="G66" s="34" t="n">
